--- a/human_adjudication/human_adjudication_v_2_4_1/2019/human_adjudication_v_2_4_1_2019_R_A.xlsx
+++ b/human_adjudication/human_adjudication_v_2_4_1/2019/human_adjudication_v_2_4_1_2019_R_A.xlsx
@@ -9,26 +9,24 @@
     <sheet name="C_jama.2019.0556" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="C_jama.2019.10517" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="C_jama.2019.12618" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="C_jama.2019.14231" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="C_jama.2019.14630" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="C_jama.2019.14901" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="C_jama.2019.17380" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="C_jama.2019.2210" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="C_jama.2019.4755" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="C_jama.2019.7505" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="Codebook" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="C_jama.2019.14630" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="C_jama.2019.14901" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="C_jama.2019.17380" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="C_jama.2019.2210" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="C_jama.2019.4755" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="C_jama.2019.7505" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="Codebook" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'C_jama.2019.0556'!$A$1:$R$12</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'C_jama.2019.10517'!$A$1:$R$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'C_jama.2019.12618'!$A$1:$R$11</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'C_jama.2019.14231'!$A$1:$R$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'C_jama.2019.14630'!$A$1:$R$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'C_jama.2019.14901'!$A$1:$R$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'C_jama.2019.17380'!$A$1:$R$19</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'C_jama.2019.2210'!$A$1:$R$8</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'C_jama.2019.4755'!$A$1:$R$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'C_jama.2019.7505'!$A$1:$R$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'C_jama.2019.14630'!$A$1:$R$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'C_jama.2019.14901'!$A$1:$R$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'C_jama.2019.17380'!$A$1:$R$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'C_jama.2019.2210'!$A$1:$R$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'C_jama.2019.4755'!$A$1:$R$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'C_jama.2019.7505'!$A$1:$R$14</definedName>
   </definedNames>
   <calcPr calcId="124519" calcMode="auto" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
@@ -1279,1213 +1277,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R19"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="22" customWidth="1" style="14" min="1" max="1"/>
-    <col width="28" customWidth="1" style="14" min="2" max="2"/>
-    <col width="22" customWidth="1" style="14" min="3" max="3"/>
-    <col width="20" customWidth="1" style="14" min="4" max="4"/>
-    <col width="35" customWidth="1" style="14" min="5" max="5"/>
-    <col width="17" customWidth="1" style="14" min="6" max="6"/>
-    <col width="29" customWidth="1" style="14" min="7" max="7"/>
-    <col width="28" customWidth="1" style="14" min="8" max="8"/>
-    <col width="20" customWidth="1" style="14" min="9" max="9"/>
-    <col width="20" customWidth="1" style="14" min="10" max="10"/>
-    <col width="34" customWidth="1" style="14" min="11" max="11"/>
-    <col width="26" customWidth="1" style="14" min="12" max="12"/>
-    <col hidden="1" width="3" customWidth="1" style="14" min="13" max="13"/>
-    <col hidden="1" width="3" customWidth="1" style="14" min="14" max="14"/>
-    <col hidden="1" width="3" customWidth="1" style="14" min="15" max="15"/>
-    <col hidden="1" width="3" customWidth="1" style="14" min="16" max="16"/>
-    <col hidden="1" width="3" customWidth="1" style="14" min="17" max="17"/>
-    <col width="32" customWidth="1" style="14" min="18" max="18"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="70" customFormat="1" customHeight="1" s="14">
-      <c r="A1" s="19" t="inlineStr">
-        <is>
-          <t>Candidate key</t>
-        </is>
-      </c>
-      <c r="B1" s="19" t="inlineStr">
-        <is>
-          <t>Candidate title</t>
-        </is>
-      </c>
-      <c r="C1" s="19" t="inlineStr">
-        <is>
-          <t>Source location</t>
-        </is>
-      </c>
-      <c r="D1" s="19" t="inlineStr">
-        <is>
-          <t>Disposition</t>
-        </is>
-      </c>
-      <c r="E1" s="19" t="inlineStr">
-        <is>
-          <t>Review domain (AI suggestion; editable)</t>
-        </is>
-      </c>
-      <c r="F1" s="19" t="inlineStr">
-        <is>
-          <t>Complete</t>
-        </is>
-      </c>
-      <c r="G1" s="19" t="inlineStr">
-        <is>
-          <t>Validation hint</t>
-        </is>
-      </c>
-      <c r="H1" s="19" t="inlineStr">
-        <is>
-          <t>Statistical_or_numerical issue</t>
-        </is>
-      </c>
-      <c r="I1" s="19" t="inlineStr">
-        <is>
-          <t>Substantiveness</t>
-        </is>
-      </c>
-      <c r="J1" s="19" t="inlineStr">
-        <is>
-          <t>Downstream impact</t>
-        </is>
-      </c>
-      <c r="K1" s="19" t="inlineStr">
-        <is>
-          <t>Report-internal or planning-material inconsistency</t>
-        </is>
-      </c>
-      <c r="L1" s="19" t="inlineStr">
-        <is>
-          <t>Protocol interpretation</t>
-        </is>
-      </c>
-      <c r="M1" s="19" t="n"/>
-      <c r="N1" s="19" t="n"/>
-      <c r="O1" s="19" t="n"/>
-      <c r="P1" s="19" t="n"/>
-      <c r="Q1" s="19" t="n"/>
-      <c r="R1" s="19" t="inlineStr">
-        <is>
-          <t>Notes (optional)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="92" customFormat="1" customHeight="1" s="14">
-      <c r="A2" s="20" t="inlineStr">
-        <is>
-          <t>2019::jama.2019.17380::C001</t>
-        </is>
-      </c>
-      <c r="B2" s="20" t="inlineStr">
-        <is>
-          <t>Documented outcome-hierarchy and composite amendment</t>
-        </is>
-      </c>
-      <c r="C2" s="20" t="inlineStr">
-        <is>
-          <t>joi190122supp1_prod.pdf — p.11 aims; joi190122supp1_prod.pdf — p.17 VI.b–c; joi190122supp1_prod.pdf — p.19 Table 2; joi190122supp1_prod.pdf — p.31 dates; joi190122supp1_prod.pdf — p.32 §15b; jama_de_boer_2019_oi_190122.pdf — p.1 primary outcome; jama_de_boer_2019_oi_190122.pdf — p.2 Outcomes; jama_de_boer_2019_oi_190122.pdf — p.3 secondary definitions; jama_de_boer_2019_oi_190122.pdf — p.4 composite narrative; jama_de_boer_2019_oi_190122.pdf — p.9 Table 3.</t>
-        </is>
-      </c>
-      <c r="D2" s="21" t="n"/>
-      <c r="E2" s="21" t="inlineStr">
-        <is>
-          <t>protocol_report</t>
-        </is>
-      </c>
-      <c r="F2" s="21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="G2" s="20">
-        <f>IFERROR(IF(LEN(TRIM(CLEAN(SUBSTITUTE(Setup!$B$2,CHAR(160)," "))))=0,"CHECK REVIEWER ID",IF(OR(A2="",COUNTIF($A$2:$A$19,A2)&lt;&gt;1,LEFT(A2,LEN("2019::jama.2019.17380::"))&lt;&gt;"2019::jama.2019.17380::"),"CHECK KEY",IF(OR(AND(NOT(AND(D2="retain",E2="statistical_results")),H2&lt;&gt;"",NOT(EXACT(H2,"not_applicable"))),AND(NOT(AND(D2="retain",E2="statistical_results")),I2&lt;&gt;"",NOT(EXACT(I2,"not_applicable"))),AND(NOT(AND(D2="retain",E2="statistical_results")),J2&lt;&gt;"",NOT(EXACT(J2,"not_applicable"))),AND(NOT(AND(D2="retain",OR(E2="report_internal_inconsistency",E2="plan_material"))),K2&lt;&gt;"",NOT(EXACT(K2,"not_applicable"))),AND(NOT(AND(D2="retain",E2="protocol_report")),L2&lt;&gt;"",NOT(EXACT(L2,"not_applicable")))),"CLEAR INACTIVE VALUES",IF(OR(NOT(OR(EXACT(D2,"retain"),EXACT(D2,"exclude"),EXACT(D2,"discuss"))),NOT(OR(EXACT(E2,"statistical_results"),EXACT(E2,"report_internal_inconsistency"),EXACT(E2,"plan_material"),EXACT(E2,"protocol_report"))),AND(AND(D2="retain",E2="statistical_results"),NOT(OR(EXACT(H2,"confirmed_issue"),EXACT(H2,"probable_issue"),EXACT(H2,"not_issue"),EXACT(H2,"indeterminate")))),AND(AND(D2="retain",E2="statistical_results"),NOT(OR(EXACT(I2,"substantive"),EXACT(I2,"minor_presentation"),EXACT(I2,"indeterminate")))),AND(AND(D2="retain",E2="statistical_results"),J2&lt;&gt;"",NOT(OR(EXACT(J2,"direct"),EXACT(J2,"possible"),EXACT(J2,"unlikely"),EXACT(J2,"unknown")))),AND(AND(D2="retain",OR(E2="report_internal_inconsistency",E2="plan_material")),NOT(OR(EXACT(K2,"substantive_inconsistency"),EXACT(K2,"minor_presentation"),EXACT(K2,"non_inconsistency"),EXACT(K2,"indeterminate")))),AND(AND(D2="retain",E2="protocol_report"),L2&lt;&gt;"",NOT(OR(EXACT(L2,"substantive_difference"),EXACT(L2,"minor_presentation"),EXACT(L2,"version_timing"),EXACT(L2,"non_inconsistency"),EXACT(L2,"indeterminate"))))),"CHECK FIELDS",IF(AND(F2&lt;&gt;"",NOT(OR(EXACT(F2,"no"),EXACT(F2,"primary_done")))),"CHECK COMPLETE",IF(EXACT(F2,"primary_done"),"PRIMARY READY","PRIMARY DRAFT")))))),"CHECK INPUT / KEY")</f>
-        <v/>
-      </c>
-      <c r="H2" s="21">
-        <f>IF(AND(OR(D2="retain",D2=""),E2="statistical_results"),"","not_applicable")</f>
-        <v/>
-      </c>
-      <c r="I2" s="21">
-        <f>IF(AND(OR(D2="retain",D2=""),E2="statistical_results"),"","not_applicable")</f>
-        <v/>
-      </c>
-      <c r="J2" s="22">
-        <f>IF(AND(OR(D2="retain",D2=""),E2="statistical_results"),"","not_applicable")</f>
-        <v/>
-      </c>
-      <c r="K2" s="21">
-        <f>IF(AND(OR(D2="retain",D2=""),OR(E2="report_internal_inconsistency",E2="plan_material")),"","not_applicable")</f>
-        <v/>
-      </c>
-      <c r="L2" s="22">
-        <f>IF(AND(OR(D2="retain",D2=""),E2="protocol_report"),"","not_applicable")</f>
-        <v/>
-      </c>
-      <c r="M2" s="20" t="n"/>
-      <c r="N2" s="23" t="n"/>
-      <c r="O2" s="23" t="n"/>
-      <c r="P2" s="23" t="n"/>
-      <c r="Q2" s="23" t="n"/>
-      <c r="R2" s="22" t="n"/>
-    </row>
-    <row r="3" ht="92" customFormat="1" customHeight="1" s="14">
-      <c r="A3" s="24" t="inlineStr">
-        <is>
-          <t>2019::jama.2019.17380::C002</t>
-        </is>
-      </c>
-      <c r="B3" s="24" t="inlineStr">
-        <is>
-          <t>Age eligibility thresholds differ between plan and report</t>
-        </is>
-      </c>
-      <c r="C3" s="24" t="inlineStr">
-        <is>
-          <t>joi190122supp1_prod.pdf — p.4 abstract; joi190122supp1_prod.pdf — p.11 aims/population; joi190122supp1_prod.pdf — p.12 Table 1/population; jama_de_boer_2019_oi_190122.pdf — p.2 Study Population; joi190122supp1_prod.pdf — p.31; joi190122supp1_prod.pdf — p.32; joi190122supp1_prod.pdf — p.33.</t>
-        </is>
-      </c>
-      <c r="D3" s="21" t="n"/>
-      <c r="E3" s="21" t="inlineStr">
-        <is>
-          <t>protocol_report</t>
-        </is>
-      </c>
-      <c r="F3" s="21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="G3" s="24">
-        <f>IFERROR(IF(LEN(TRIM(CLEAN(SUBSTITUTE(Setup!$B$2,CHAR(160)," "))))=0,"CHECK REVIEWER ID",IF(OR(A3="",COUNTIF($A$2:$A$19,A3)&lt;&gt;1,LEFT(A3,LEN("2019::jama.2019.17380::"))&lt;&gt;"2019::jama.2019.17380::"),"CHECK KEY",IF(OR(AND(NOT(AND(D3="retain",E3="statistical_results")),H3&lt;&gt;"",NOT(EXACT(H3,"not_applicable"))),AND(NOT(AND(D3="retain",E3="statistical_results")),I3&lt;&gt;"",NOT(EXACT(I3,"not_applicable"))),AND(NOT(AND(D3="retain",E3="statistical_results")),J3&lt;&gt;"",NOT(EXACT(J3,"not_applicable"))),AND(NOT(AND(D3="retain",OR(E3="report_internal_inconsistency",E3="plan_material"))),K3&lt;&gt;"",NOT(EXACT(K3,"not_applicable"))),AND(NOT(AND(D3="retain",E3="protocol_report")),L3&lt;&gt;"",NOT(EXACT(L3,"not_applicable")))),"CLEAR INACTIVE VALUES",IF(OR(NOT(OR(EXACT(D3,"retain"),EXACT(D3,"exclude"),EXACT(D3,"discuss"))),NOT(OR(EXACT(E3,"statistical_results"),EXACT(E3,"report_internal_inconsistency"),EXACT(E3,"plan_material"),EXACT(E3,"protocol_report"))),AND(AND(D3="retain",E3="statistical_results"),NOT(OR(EXACT(H3,"confirmed_issue"),EXACT(H3,"probable_issue"),EXACT(H3,"not_issue"),EXACT(H3,"indeterminate")))),AND(AND(D3="retain",E3="statistical_results"),NOT(OR(EXACT(I3,"substantive"),EXACT(I3,"minor_presentation"),EXACT(I3,"indeterminate")))),AND(AND(D3="retain",E3="statistical_results"),J3&lt;&gt;"",NOT(OR(EXACT(J3,"direct"),EXACT(J3,"possible"),EXACT(J3,"unlikely"),EXACT(J3,"unknown")))),AND(AND(D3="retain",OR(E3="report_internal_inconsistency",E3="plan_material")),NOT(OR(EXACT(K3,"substantive_inconsistency"),EXACT(K3,"minor_presentation"),EXACT(K3,"non_inconsistency"),EXACT(K3,"indeterminate")))),AND(AND(D3="retain",E3="protocol_report"),L3&lt;&gt;"",NOT(OR(EXACT(L3,"substantive_difference"),EXACT(L3,"minor_presentation"),EXACT(L3,"version_timing"),EXACT(L3,"non_inconsistency"),EXACT(L3,"indeterminate"))))),"CHECK FIELDS",IF(AND(F3&lt;&gt;"",NOT(OR(EXACT(F3,"no"),EXACT(F3,"primary_done")))),"CHECK COMPLETE",IF(EXACT(F3,"primary_done"),"PRIMARY READY","PRIMARY DRAFT")))))),"CHECK INPUT / KEY")</f>
-        <v/>
-      </c>
-      <c r="H3" s="21">
-        <f>IF(AND(OR(D3="retain",D3=""),E3="statistical_results"),"","not_applicable")</f>
-        <v/>
-      </c>
-      <c r="I3" s="21">
-        <f>IF(AND(OR(D3="retain",D3=""),E3="statistical_results"),"","not_applicable")</f>
-        <v/>
-      </c>
-      <c r="J3" s="22">
-        <f>IF(AND(OR(D3="retain",D3=""),E3="statistical_results"),"","not_applicable")</f>
-        <v/>
-      </c>
-      <c r="K3" s="21">
-        <f>IF(AND(OR(D3="retain",D3=""),OR(E3="report_internal_inconsistency",E3="plan_material")),"","not_applicable")</f>
-        <v/>
-      </c>
-      <c r="L3" s="22">
-        <f>IF(AND(OR(D3="retain",D3=""),E3="protocol_report"),"","not_applicable")</f>
-        <v/>
-      </c>
-      <c r="M3" s="24" t="n"/>
-      <c r="N3" s="23" t="n"/>
-      <c r="O3" s="23" t="n"/>
-      <c r="P3" s="23" t="n"/>
-      <c r="Q3" s="23" t="n"/>
-      <c r="R3" s="22" t="n"/>
-    </row>
-    <row r="4" ht="92" customFormat="1" customHeight="1" s="14">
-      <c r="A4" s="20" t="inlineStr">
-        <is>
-          <t>2019::jama.2019.17380::C003</t>
-        </is>
-      </c>
-      <c r="B4" s="20" t="inlineStr">
-        <is>
-          <t>Diabetes exclusion criteria use different insulin rules</t>
-        </is>
-      </c>
-      <c r="C4" s="20" t="inlineStr">
-        <is>
-          <t>joi190122supp1_prod.pdf — p.12 Table 1 and population narrative; joi190122supp1_prod.pdf — p.14 IV.a enrollment algorithm; jama_de_boer_2019_oi_190122.pdf — p.2 Study Population.</t>
-        </is>
-      </c>
-      <c r="D4" s="21" t="n"/>
-      <c r="E4" s="21" t="inlineStr">
-        <is>
-          <t>protocol_report</t>
-        </is>
-      </c>
-      <c r="F4" s="21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="G4" s="20">
-        <f>IFERROR(IF(LEN(TRIM(CLEAN(SUBSTITUTE(Setup!$B$2,CHAR(160)," "))))=0,"CHECK REVIEWER ID",IF(OR(A4="",COUNTIF($A$2:$A$19,A4)&lt;&gt;1,LEFT(A4,LEN("2019::jama.2019.17380::"))&lt;&gt;"2019::jama.2019.17380::"),"CHECK KEY",IF(OR(AND(NOT(AND(D4="retain",E4="statistical_results")),H4&lt;&gt;"",NOT(EXACT(H4,"not_applicable"))),AND(NOT(AND(D4="retain",E4="statistical_results")),I4&lt;&gt;"",NOT(EXACT(I4,"not_applicable"))),AND(NOT(AND(D4="retain",E4="statistical_results")),J4&lt;&gt;"",NOT(EXACT(J4,"not_applicable"))),AND(NOT(AND(D4="retain",OR(E4="report_internal_inconsistency",E4="plan_material"))),K4&lt;&gt;"",NOT(EXACT(K4,"not_applicable"))),AND(NOT(AND(D4="retain",E4="protocol_report")),L4&lt;&gt;"",NOT(EXACT(L4,"not_applicable")))),"CLEAR INACTIVE VALUES",IF(OR(NOT(OR(EXACT(D4,"retain"),EXACT(D4,"exclude"),EXACT(D4,"discuss"))),NOT(OR(EXACT(E4,"statistical_results"),EXACT(E4,"report_internal_inconsistency"),EXACT(E4,"plan_material"),EXACT(E4,"protocol_report"))),AND(AND(D4="retain",E4="statistical_results"),NOT(OR(EXACT(H4,"confirmed_issue"),EXACT(H4,"probable_issue"),EXACT(H4,"not_issue"),EXACT(H4,"indeterminate")))),AND(AND(D4="retain",E4="statistical_results"),NOT(OR(EXACT(I4,"substantive"),EXACT(I4,"minor_presentation"),EXACT(I4,"indeterminate")))),AND(AND(D4="retain",E4="statistical_results"),J4&lt;&gt;"",NOT(OR(EXACT(J4,"direct"),EXACT(J4,"possible"),EXACT(J4,"unlikely"),EXACT(J4,"unknown")))),AND(AND(D4="retain",OR(E4="report_internal_inconsistency",E4="plan_material")),NOT(OR(EXACT(K4,"substantive_inconsistency"),EXACT(K4,"minor_presentation"),EXACT(K4,"non_inconsistency"),EXACT(K4,"indeterminate")))),AND(AND(D4="retain",E4="protocol_report"),L4&lt;&gt;"",NOT(OR(EXACT(L4,"substantive_difference"),EXACT(L4,"minor_presentation"),EXACT(L4,"version_timing"),EXACT(L4,"non_inconsistency"),EXACT(L4,"indeterminate"))))),"CHECK FIELDS",IF(AND(F4&lt;&gt;"",NOT(OR(EXACT(F4,"no"),EXACT(F4,"primary_done")))),"CHECK COMPLETE",IF(EXACT(F4,"primary_done"),"PRIMARY READY","PRIMARY DRAFT")))))),"CHECK INPUT / KEY")</f>
-        <v/>
-      </c>
-      <c r="H4" s="21">
-        <f>IF(AND(OR(D4="retain",D4=""),E4="statistical_results"),"","not_applicable")</f>
-        <v/>
-      </c>
-      <c r="I4" s="21">
-        <f>IF(AND(OR(D4="retain",D4=""),E4="statistical_results"),"","not_applicable")</f>
-        <v/>
-      </c>
-      <c r="J4" s="22">
-        <f>IF(AND(OR(D4="retain",D4=""),E4="statistical_results"),"","not_applicable")</f>
-        <v/>
-      </c>
-      <c r="K4" s="21">
-        <f>IF(AND(OR(D4="retain",D4=""),OR(E4="report_internal_inconsistency",E4="plan_material")),"","not_applicable")</f>
-        <v/>
-      </c>
-      <c r="L4" s="22">
-        <f>IF(AND(OR(D4="retain",D4=""),E4="protocol_report"),"","not_applicable")</f>
-        <v/>
-      </c>
-      <c r="M4" s="20" t="n"/>
-      <c r="N4" s="23" t="n"/>
-      <c r="O4" s="23" t="n"/>
-      <c r="P4" s="23" t="n"/>
-      <c r="Q4" s="23" t="n"/>
-      <c r="R4" s="22" t="n"/>
-    </row>
-    <row r="5" ht="92" customFormat="1" customHeight="1" s="14">
-      <c r="A5" s="24" t="inlineStr">
-        <is>
-          <t>2019::jama.2019.17380::C004</t>
-        </is>
-      </c>
-      <c r="B5" s="24" t="inlineStr">
-        <is>
-          <t>Randomization stratifiers differ between plan and report</t>
-        </is>
-      </c>
-      <c r="C5" s="24" t="inlineStr">
-        <is>
-          <t>joi190122supp1_prod.pdf — p.14 IV.c Treatment Assignment; jama_de_boer_2019_oi_190122.pdf — p.2 Interventions; joi190122supp1_prod.pdf — pp.31–33 analytic addendum; joi190122supp1_prod.pdf — p.32; joi190122supp1_prod.pdf — p.33.</t>
-        </is>
-      </c>
-      <c r="D5" s="21" t="n"/>
-      <c r="E5" s="21" t="inlineStr">
-        <is>
-          <t>protocol_report</t>
-        </is>
-      </c>
-      <c r="F5" s="21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="G5" s="24">
-        <f>IFERROR(IF(LEN(TRIM(CLEAN(SUBSTITUTE(Setup!$B$2,CHAR(160)," "))))=0,"CHECK REVIEWER ID",IF(OR(A5="",COUNTIF($A$2:$A$19,A5)&lt;&gt;1,LEFT(A5,LEN("2019::jama.2019.17380::"))&lt;&gt;"2019::jama.2019.17380::"),"CHECK KEY",IF(OR(AND(NOT(AND(D5="retain",E5="statistical_results")),H5&lt;&gt;"",NOT(EXACT(H5,"not_applicable"))),AND(NOT(AND(D5="retain",E5="statistical_results")),I5&lt;&gt;"",NOT(EXACT(I5,"not_applicable"))),AND(NOT(AND(D5="retain",E5="statistical_results")),J5&lt;&gt;"",NOT(EXACT(J5,"not_applicable"))),AND(NOT(AND(D5="retain",OR(E5="report_internal_inconsistency",E5="plan_material"))),K5&lt;&gt;"",NOT(EXACT(K5,"not_applicable"))),AND(NOT(AND(D5="retain",E5="protocol_report")),L5&lt;&gt;"",NOT(EXACT(L5,"not_applicable")))),"CLEAR INACTIVE VALUES",IF(OR(NOT(OR(EXACT(D5,"retain"),EXACT(D5,"exclude"),EXACT(D5,"discuss"))),NOT(OR(EXACT(E5,"statistical_results"),EXACT(E5,"report_internal_inconsistency"),EXACT(E5,"plan_material"),EXACT(E5,"protocol_report"))),AND(AND(D5="retain",E5="statistical_results"),NOT(OR(EXACT(H5,"confirmed_issue"),EXACT(H5,"probable_issue"),EXACT(H5,"not_issue"),EXACT(H5,"indeterminate")))),AND(AND(D5="retain",E5="statistical_results"),NOT(OR(EXACT(I5,"substantive"),EXACT(I5,"minor_presentation"),EXACT(I5,"indeterminate")))),AND(AND(D5="retain",E5="statistical_results"),J5&lt;&gt;"",NOT(OR(EXACT(J5,"direct"),EXACT(J5,"possible"),EXACT(J5,"unlikely"),EXACT(J5,"unknown")))),AND(AND(D5="retain",OR(E5="report_internal_inconsistency",E5="plan_material")),NOT(OR(EXACT(K5,"substantive_inconsistency"),EXACT(K5,"minor_presentation"),EXACT(K5,"non_inconsistency"),EXACT(K5,"indeterminate")))),AND(AND(D5="retain",E5="protocol_report"),L5&lt;&gt;"",NOT(OR(EXACT(L5,"substantive_difference"),EXACT(L5,"minor_presentation"),EXACT(L5,"version_timing"),EXACT(L5,"non_inconsistency"),EXACT(L5,"indeterminate"))))),"CHECK FIELDS",IF(AND(F5&lt;&gt;"",NOT(OR(EXACT(F5,"no"),EXACT(F5,"primary_done")))),"CHECK COMPLETE",IF(EXACT(F5,"primary_done"),"PRIMARY READY","PRIMARY DRAFT")))))),"CHECK INPUT / KEY")</f>
-        <v/>
-      </c>
-      <c r="H5" s="21">
-        <f>IF(AND(OR(D5="retain",D5=""),E5="statistical_results"),"","not_applicable")</f>
-        <v/>
-      </c>
-      <c r="I5" s="21">
-        <f>IF(AND(OR(D5="retain",D5=""),E5="statistical_results"),"","not_applicable")</f>
-        <v/>
-      </c>
-      <c r="J5" s="22">
-        <f>IF(AND(OR(D5="retain",D5=""),E5="statistical_results"),"","not_applicable")</f>
-        <v/>
-      </c>
-      <c r="K5" s="21">
-        <f>IF(AND(OR(D5="retain",D5=""),OR(E5="report_internal_inconsistency",E5="plan_material")),"","not_applicable")</f>
-        <v/>
-      </c>
-      <c r="L5" s="22">
-        <f>IF(AND(OR(D5="retain",D5=""),E5="protocol_report"),"","not_applicable")</f>
-        <v/>
-      </c>
-      <c r="M5" s="24" t="n"/>
-      <c r="N5" s="23" t="n"/>
-      <c r="O5" s="23" t="n"/>
-      <c r="P5" s="23" t="n"/>
-      <c r="Q5" s="23" t="n"/>
-      <c r="R5" s="22" t="n"/>
-    </row>
-    <row r="6" ht="92" customFormat="1" customHeight="1" s="14">
-      <c r="A6" s="20" t="inlineStr">
-        <is>
-          <t>2019::jama.2019.17380::C005</t>
-        </is>
-      </c>
-      <c r="B6" s="20" t="inlineStr">
-        <is>
-          <t>Primary eGFR estimator identity differs from the supplied plan</t>
-        </is>
-      </c>
-      <c r="C6" s="20" t="inlineStr">
-        <is>
-          <t>joi190122supp1_prod.pdf — p.17 VI.c Equation 1; joi190122supp1_prod.pdf — p.30; joi190122supp1_prod.pdf — p.32 §15b; jama_de_boer_2019_oi_190122.pdf — p.3 Outcomes; jama_de_boer_2019_oi_190122.pdf — p.11; joi190122supp2_prod.pdf — p.2; joi190122supp2_prod.pdf — p.3; joi190122supp2_prod.pdf — p.4.</t>
-        </is>
-      </c>
-      <c r="D6" s="21" t="n"/>
-      <c r="E6" s="21" t="inlineStr">
-        <is>
-          <t>protocol_report</t>
-        </is>
-      </c>
-      <c r="F6" s="21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="G6" s="20">
-        <f>IFERROR(IF(LEN(TRIM(CLEAN(SUBSTITUTE(Setup!$B$2,CHAR(160)," "))))=0,"CHECK REVIEWER ID",IF(OR(A6="",COUNTIF($A$2:$A$19,A6)&lt;&gt;1,LEFT(A6,LEN("2019::jama.2019.17380::"))&lt;&gt;"2019::jama.2019.17380::"),"CHECK KEY",IF(OR(AND(NOT(AND(D6="retain",E6="statistical_results")),H6&lt;&gt;"",NOT(EXACT(H6,"not_applicable"))),AND(NOT(AND(D6="retain",E6="statistical_results")),I6&lt;&gt;"",NOT(EXACT(I6,"not_applicable"))),AND(NOT(AND(D6="retain",E6="statistical_results")),J6&lt;&gt;"",NOT(EXACT(J6,"not_applicable"))),AND(NOT(AND(D6="retain",OR(E6="report_internal_inconsistency",E6="plan_material"))),K6&lt;&gt;"",NOT(EXACT(K6,"not_applicable"))),AND(NOT(AND(D6="retain",E6="protocol_report")),L6&lt;&gt;"",NOT(EXACT(L6,"not_applicable")))),"CLEAR INACTIVE VALUES",IF(OR(NOT(OR(EXACT(D6,"retain"),EXACT(D6,"exclude"),EXACT(D6,"discuss"))),NOT(OR(EXACT(E6,"statistical_results"),EXACT(E6,"report_internal_inconsistency"),EXACT(E6,"plan_material"),EXACT(E6,"protocol_report"))),AND(AND(D6="retain",E6="statistical_results"),NOT(OR(EXACT(H6,"confirmed_issue"),EXACT(H6,"probable_issue"),EXACT(H6,"not_issue"),EXACT(H6,"indeterminate")))),AND(AND(D6="retain",E6="statistical_results"),NOT(OR(EXACT(I6,"substantive"),EXACT(I6,"minor_presentation"),EXACT(I6,"indeterminate")))),AND(AND(D6="retain",E6="statistical_results"),J6&lt;&gt;"",NOT(OR(EXACT(J6,"direct"),EXACT(J6,"possible"),EXACT(J6,"unlikely"),EXACT(J6,"unknown")))),AND(AND(D6="retain",OR(E6="report_internal_inconsistency",E6="plan_material")),NOT(OR(EXACT(K6,"substantive_inconsistency"),EXACT(K6,"minor_presentation"),EXACT(K6,"non_inconsistency"),EXACT(K6,"indeterminate")))),AND(AND(D6="retain",E6="protocol_report"),L6&lt;&gt;"",NOT(OR(EXACT(L6,"substantive_difference"),EXACT(L6,"minor_presentation"),EXACT(L6,"version_timing"),EXACT(L6,"non_inconsistency"),EXACT(L6,"indeterminate"))))),"CHECK FIELDS",IF(AND(F6&lt;&gt;"",NOT(OR(EXACT(F6,"no"),EXACT(F6,"primary_done")))),"CHECK COMPLETE",IF(EXACT(F6,"primary_done"),"PRIMARY READY","PRIMARY DRAFT")))))),"CHECK INPUT / KEY")</f>
-        <v/>
-      </c>
-      <c r="H6" s="21">
-        <f>IF(AND(OR(D6="retain",D6=""),E6="statistical_results"),"","not_applicable")</f>
-        <v/>
-      </c>
-      <c r="I6" s="21">
-        <f>IF(AND(OR(D6="retain",D6=""),E6="statistical_results"),"","not_applicable")</f>
-        <v/>
-      </c>
-      <c r="J6" s="22">
-        <f>IF(AND(OR(D6="retain",D6=""),E6="statistical_results"),"","not_applicable")</f>
-        <v/>
-      </c>
-      <c r="K6" s="21">
-        <f>IF(AND(OR(D6="retain",D6=""),OR(E6="report_internal_inconsistency",E6="plan_material")),"","not_applicable")</f>
-        <v/>
-      </c>
-      <c r="L6" s="22">
-        <f>IF(AND(OR(D6="retain",D6=""),E6="protocol_report"),"","not_applicable")</f>
-        <v/>
-      </c>
-      <c r="M6" s="20" t="n"/>
-      <c r="N6" s="23" t="n"/>
-      <c r="O6" s="23" t="n"/>
-      <c r="P6" s="23" t="n"/>
-      <c r="Q6" s="23" t="n"/>
-      <c r="R6" s="22" t="n"/>
-    </row>
-    <row r="7" ht="92" customFormat="1" customHeight="1" s="14">
-      <c r="A7" s="24" t="inlineStr">
-        <is>
-          <t>2019::jama.2019.17380::C006</t>
-        </is>
-      </c>
-      <c r="B7" s="24" t="inlineStr">
-        <is>
-          <t>Standalone categorical ACR analysis is called prespecified</t>
-        </is>
-      </c>
-      <c r="C7" s="24" t="inlineStr">
-        <is>
-          <t>joi190122supp1_prod.pdf — p.17 original composite; joi190122supp1_prod.pdf — p.32 §15b/e; joi190122supp1_prod.pdf — p.33 categorical-model continuation; jama_de_boer_2019_oi_190122.pdf — p.3 Outcomes; jama_de_boer_2019_oi_190122.pdf — p.4 secondary narrative; jama_de_boer_2019_oi_190122.pdf — p.9 Table 3 and footnote a.</t>
-        </is>
-      </c>
-      <c r="D7" s="21" t="n"/>
-      <c r="E7" s="21" t="inlineStr">
-        <is>
-          <t>protocol_report</t>
-        </is>
-      </c>
-      <c r="F7" s="21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="G7" s="24">
-        <f>IFERROR(IF(LEN(TRIM(CLEAN(SUBSTITUTE(Setup!$B$2,CHAR(160)," "))))=0,"CHECK REVIEWER ID",IF(OR(A7="",COUNTIF($A$2:$A$19,A7)&lt;&gt;1,LEFT(A7,LEN("2019::jama.2019.17380::"))&lt;&gt;"2019::jama.2019.17380::"),"CHECK KEY",IF(OR(AND(NOT(AND(D7="retain",E7="statistical_results")),H7&lt;&gt;"",NOT(EXACT(H7,"not_applicable"))),AND(NOT(AND(D7="retain",E7="statistical_results")),I7&lt;&gt;"",NOT(EXACT(I7,"not_applicable"))),AND(NOT(AND(D7="retain",E7="statistical_results")),J7&lt;&gt;"",NOT(EXACT(J7,"not_applicable"))),AND(NOT(AND(D7="retain",OR(E7="report_internal_inconsistency",E7="plan_material"))),K7&lt;&gt;"",NOT(EXACT(K7,"not_applicable"))),AND(NOT(AND(D7="retain",E7="protocol_report")),L7&lt;&gt;"",NOT(EXACT(L7,"not_applicable")))),"CLEAR INACTIVE VALUES",IF(OR(NOT(OR(EXACT(D7,"retain"),EXACT(D7,"exclude"),EXACT(D7,"discuss"))),NOT(OR(EXACT(E7,"statistical_results"),EXACT(E7,"report_internal_inconsistency"),EXACT(E7,"plan_material"),EXACT(E7,"protocol_report"))),AND(AND(D7="retain",E7="statistical_results"),NOT(OR(EXACT(H7,"confirmed_issue"),EXACT(H7,"probable_issue"),EXACT(H7,"not_issue"),EXACT(H7,"indeterminate")))),AND(AND(D7="retain",E7="statistical_results"),NOT(OR(EXACT(I7,"substantive"),EXACT(I7,"minor_presentation"),EXACT(I7,"indeterminate")))),AND(AND(D7="retain",E7="statistical_results"),J7&lt;&gt;"",NOT(OR(EXACT(J7,"direct"),EXACT(J7,"possible"),EXACT(J7,"unlikely"),EXACT(J7,"unknown")))),AND(AND(D7="retain",OR(E7="report_internal_inconsistency",E7="plan_material")),NOT(OR(EXACT(K7,"substantive_inconsistency"),EXACT(K7,"minor_presentation"),EXACT(K7,"non_inconsistency"),EXACT(K7,"indeterminate")))),AND(AND(D7="retain",E7="protocol_report"),L7&lt;&gt;"",NOT(OR(EXACT(L7,"substantive_difference"),EXACT(L7,"minor_presentation"),EXACT(L7,"version_timing"),EXACT(L7,"non_inconsistency"),EXACT(L7,"indeterminate"))))),"CHECK FIELDS",IF(AND(F7&lt;&gt;"",NOT(OR(EXACT(F7,"no"),EXACT(F7,"primary_done")))),"CHECK COMPLETE",IF(EXACT(F7,"primary_done"),"PRIMARY READY","PRIMARY DRAFT")))))),"CHECK INPUT / KEY")</f>
-        <v/>
-      </c>
-      <c r="H7" s="21">
-        <f>IF(AND(OR(D7="retain",D7=""),E7="statistical_results"),"","not_applicable")</f>
-        <v/>
-      </c>
-      <c r="I7" s="21">
-        <f>IF(AND(OR(D7="retain",D7=""),E7="statistical_results"),"","not_applicable")</f>
-        <v/>
-      </c>
-      <c r="J7" s="22">
-        <f>IF(AND(OR(D7="retain",D7=""),E7="statistical_results"),"","not_applicable")</f>
-        <v/>
-      </c>
-      <c r="K7" s="21">
-        <f>IF(AND(OR(D7="retain",D7=""),OR(E7="report_internal_inconsistency",E7="plan_material")),"","not_applicable")</f>
-        <v/>
-      </c>
-      <c r="L7" s="22">
-        <f>IF(AND(OR(D7="retain",D7=""),E7="protocol_report"),"","not_applicable")</f>
-        <v/>
-      </c>
-      <c r="M7" s="24" t="n"/>
-      <c r="N7" s="23" t="n"/>
-      <c r="O7" s="23" t="n"/>
-      <c r="P7" s="23" t="n"/>
-      <c r="Q7" s="23" t="n"/>
-      <c r="R7" s="22" t="n"/>
-    </row>
-    <row r="8" ht="92" customFormat="1" customHeight="1" s="14">
-      <c r="A8" s="20" t="inlineStr">
-        <is>
-          <t>2019::jama.2019.17380::C007</t>
-        </is>
-      </c>
-      <c r="B8" s="20" t="inlineStr">
-        <is>
-          <t>Adherence sensitivity populations use different criteria</t>
-        </is>
-      </c>
-      <c r="C8" s="20" t="inlineStr">
-        <is>
-          <t>joi190122supp1_prod.pdf — p.19 VI.g; joi190122supp1_prod.pdf — p.33 §15g; jama_de_boer_2019_oi_190122.pdf — p.3 Covariates/Data Analysis; jama_de_boer_2019_oi_190122.pdf — p.4 sensitivity narrative; joi190122supp2_prod.pdf — p.6 eTable 1 footnote; joi190122supp2_prod.pdf — p.10 eTable 5 definition; joi190122supp2_prod.pdf — p.13 eTable 8 definition.</t>
-        </is>
-      </c>
-      <c r="D8" s="21" t="n"/>
-      <c r="E8" s="21" t="inlineStr">
-        <is>
-          <t>protocol_report</t>
-        </is>
-      </c>
-      <c r="F8" s="21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="G8" s="20">
-        <f>IFERROR(IF(LEN(TRIM(CLEAN(SUBSTITUTE(Setup!$B$2,CHAR(160)," "))))=0,"CHECK REVIEWER ID",IF(OR(A8="",COUNTIF($A$2:$A$19,A8)&lt;&gt;1,LEFT(A8,LEN("2019::jama.2019.17380::"))&lt;&gt;"2019::jama.2019.17380::"),"CHECK KEY",IF(OR(AND(NOT(AND(D8="retain",E8="statistical_results")),H8&lt;&gt;"",NOT(EXACT(H8,"not_applicable"))),AND(NOT(AND(D8="retain",E8="statistical_results")),I8&lt;&gt;"",NOT(EXACT(I8,"not_applicable"))),AND(NOT(AND(D8="retain",E8="statistical_results")),J8&lt;&gt;"",NOT(EXACT(J8,"not_applicable"))),AND(NOT(AND(D8="retain",OR(E8="report_internal_inconsistency",E8="plan_material"))),K8&lt;&gt;"",NOT(EXACT(K8,"not_applicable"))),AND(NOT(AND(D8="retain",E8="protocol_report")),L8&lt;&gt;"",NOT(EXACT(L8,"not_applicable")))),"CLEAR INACTIVE VALUES",IF(OR(NOT(OR(EXACT(D8,"retain"),EXACT(D8,"exclude"),EXACT(D8,"discuss"))),NOT(OR(EXACT(E8,"statistical_results"),EXACT(E8,"report_internal_inconsistency"),EXACT(E8,"plan_material"),EXACT(E8,"protocol_report"))),AND(AND(D8="retain",E8="statistical_results"),NOT(OR(EXACT(H8,"confirmed_issue"),EXACT(H8,"probable_issue"),EXACT(H8,"not_issue"),EXACT(H8,"indeterminate")))),AND(AND(D8="retain",E8="statistical_results"),NOT(OR(EXACT(I8,"substantive"),EXACT(I8,"minor_presentation"),EXACT(I8,"indeterminate")))),AND(AND(D8="retain",E8="statistical_results"),J8&lt;&gt;"",NOT(OR(EXACT(J8,"direct"),EXACT(J8,"possible"),EXACT(J8,"unlikely"),EXACT(J8,"unknown")))),AND(AND(D8="retain",OR(E8="report_internal_inconsistency",E8="plan_material")),NOT(OR(EXACT(K8,"substantive_inconsistency"),EXACT(K8,"minor_presentation"),EXACT(K8,"non_inconsistency"),EXACT(K8,"indeterminate")))),AND(AND(D8="retain",E8="protocol_report"),L8&lt;&gt;"",NOT(OR(EXACT(L8,"substantive_difference"),EXACT(L8,"minor_presentation"),EXACT(L8,"version_timing"),EXACT(L8,"non_inconsistency"),EXACT(L8,"indeterminate"))))),"CHECK FIELDS",IF(AND(F8&lt;&gt;"",NOT(OR(EXACT(F8,"no"),EXACT(F8,"primary_done")))),"CHECK COMPLETE",IF(EXACT(F8,"primary_done"),"PRIMARY READY","PRIMARY DRAFT")))))),"CHECK INPUT / KEY")</f>
-        <v/>
-      </c>
-      <c r="H8" s="21">
-        <f>IF(AND(OR(D8="retain",D8=""),E8="statistical_results"),"","not_applicable")</f>
-        <v/>
-      </c>
-      <c r="I8" s="21">
-        <f>IF(AND(OR(D8="retain",D8=""),E8="statistical_results"),"","not_applicable")</f>
-        <v/>
-      </c>
-      <c r="J8" s="22">
-        <f>IF(AND(OR(D8="retain",D8=""),E8="statistical_results"),"","not_applicable")</f>
-        <v/>
-      </c>
-      <c r="K8" s="21">
-        <f>IF(AND(OR(D8="retain",D8=""),OR(E8="report_internal_inconsistency",E8="plan_material")),"","not_applicable")</f>
-        <v/>
-      </c>
-      <c r="L8" s="22">
-        <f>IF(AND(OR(D8="retain",D8=""),E8="protocol_report"),"","not_applicable")</f>
-        <v/>
-      </c>
-      <c r="M8" s="20" t="n"/>
-      <c r="N8" s="23" t="n"/>
-      <c r="O8" s="23" t="n"/>
-      <c r="P8" s="23" t="n"/>
-      <c r="Q8" s="23" t="n"/>
-      <c r="R8" s="22" t="n"/>
-    </row>
-    <row r="9" ht="92" customFormat="1" customHeight="1" s="14">
-      <c r="A9" s="24" t="inlineStr">
-        <is>
-          <t>2019::jama.2019.17380::C008</t>
-        </is>
-      </c>
-      <c r="B9" s="24" t="inlineStr">
-        <is>
-          <t>Primary analysis population drops the planned follow-up condition</t>
-        </is>
-      </c>
-      <c r="C9" s="24" t="inlineStr">
-        <is>
-          <t>joi190122supp1_prod.pdf — p.32 §15c; jama_de_boer_2019_oi_190122.pdf — p.3 Data Analysis; jama_de_boer_2019_oi_190122.pdf — p.4 Retention; jama_de_boer_2019_oi_190122.pdf — p.6 Figure 1; jama_de_boer_2019_oi_190122.pdf — p.8 Table 2 footnotes.</t>
-        </is>
-      </c>
-      <c r="D9" s="21" t="n"/>
-      <c r="E9" s="21" t="inlineStr">
-        <is>
-          <t>protocol_report</t>
-        </is>
-      </c>
-      <c r="F9" s="21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="G9" s="24">
-        <f>IFERROR(IF(LEN(TRIM(CLEAN(SUBSTITUTE(Setup!$B$2,CHAR(160)," "))))=0,"CHECK REVIEWER ID",IF(OR(A9="",COUNTIF($A$2:$A$19,A9)&lt;&gt;1,LEFT(A9,LEN("2019::jama.2019.17380::"))&lt;&gt;"2019::jama.2019.17380::"),"CHECK KEY",IF(OR(AND(NOT(AND(D9="retain",E9="statistical_results")),H9&lt;&gt;"",NOT(EXACT(H9,"not_applicable"))),AND(NOT(AND(D9="retain",E9="statistical_results")),I9&lt;&gt;"",NOT(EXACT(I9,"not_applicable"))),AND(NOT(AND(D9="retain",E9="statistical_results")),J9&lt;&gt;"",NOT(EXACT(J9,"not_applicable"))),AND(NOT(AND(D9="retain",OR(E9="report_internal_inconsistency",E9="plan_material"))),K9&lt;&gt;"",NOT(EXACT(K9,"not_applicable"))),AND(NOT(AND(D9="retain",E9="protocol_report")),L9&lt;&gt;"",NOT(EXACT(L9,"not_applicable")))),"CLEAR INACTIVE VALUES",IF(OR(NOT(OR(EXACT(D9,"retain"),EXACT(D9,"exclude"),EXACT(D9,"discuss"))),NOT(OR(EXACT(E9,"statistical_results"),EXACT(E9,"report_internal_inconsistency"),EXACT(E9,"plan_material"),EXACT(E9,"protocol_report"))),AND(AND(D9="retain",E9="statistical_results"),NOT(OR(EXACT(H9,"confirmed_issue"),EXACT(H9,"probable_issue"),EXACT(H9,"not_issue"),EXACT(H9,"indeterminate")))),AND(AND(D9="retain",E9="statistical_results"),NOT(OR(EXACT(I9,"substantive"),EXACT(I9,"minor_presentation"),EXACT(I9,"indeterminate")))),AND(AND(D9="retain",E9="statistical_results"),J9&lt;&gt;"",NOT(OR(EXACT(J9,"direct"),EXACT(J9,"possible"),EXACT(J9,"unlikely"),EXACT(J9,"unknown")))),AND(AND(D9="retain",OR(E9="report_internal_inconsistency",E9="plan_material")),NOT(OR(EXACT(K9,"substantive_inconsistency"),EXACT(K9,"minor_presentation"),EXACT(K9,"non_inconsistency"),EXACT(K9,"indeterminate")))),AND(AND(D9="retain",E9="protocol_report"),L9&lt;&gt;"",NOT(OR(EXACT(L9,"substantive_difference"),EXACT(L9,"minor_presentation"),EXACT(L9,"version_timing"),EXACT(L9,"non_inconsistency"),EXACT(L9,"indeterminate"))))),"CHECK FIELDS",IF(AND(F9&lt;&gt;"",NOT(OR(EXACT(F9,"no"),EXACT(F9,"primary_done")))),"CHECK COMPLETE",IF(EXACT(F9,"primary_done"),"PRIMARY READY","PRIMARY DRAFT")))))),"CHECK INPUT / KEY")</f>
-        <v/>
-      </c>
-      <c r="H9" s="21">
-        <f>IF(AND(OR(D9="retain",D9=""),E9="statistical_results"),"","not_applicable")</f>
-        <v/>
-      </c>
-      <c r="I9" s="21">
-        <f>IF(AND(OR(D9="retain",D9=""),E9="statistical_results"),"","not_applicable")</f>
-        <v/>
-      </c>
-      <c r="J9" s="22">
-        <f>IF(AND(OR(D9="retain",D9=""),E9="statistical_results"),"","not_applicable")</f>
-        <v/>
-      </c>
-      <c r="K9" s="21">
-        <f>IF(AND(OR(D9="retain",D9=""),OR(E9="report_internal_inconsistency",E9="plan_material")),"","not_applicable")</f>
-        <v/>
-      </c>
-      <c r="L9" s="22">
-        <f>IF(AND(OR(D9="retain",D9=""),E9="protocol_report"),"","not_applicable")</f>
-        <v/>
-      </c>
-      <c r="M9" s="24" t="n"/>
-      <c r="N9" s="23" t="n"/>
-      <c r="O9" s="23" t="n"/>
-      <c r="P9" s="23" t="n"/>
-      <c r="Q9" s="23" t="n"/>
-      <c r="R9" s="22" t="n"/>
-    </row>
-    <row r="10" ht="92" customFormat="1" customHeight="1" s="14">
-      <c r="A10" s="20" t="inlineStr">
-        <is>
-          <t>2019::jama.2019.17380::C009</t>
-        </is>
-      </c>
-      <c r="B10" s="20" t="inlineStr">
-        <is>
-          <t>Primary imputation count differs between plan and report</t>
-        </is>
-      </c>
-      <c r="C10" s="20" t="inlineStr">
-        <is>
-          <t>joi190122supp1_prod.pdf — p.32 §15c; jama_de_boer_2019_oi_190122.pdf — p.3 Data Analysis; jama_de_boer_2019_oi_190122.pdf — p.8 Table 2 footnotes.</t>
-        </is>
-      </c>
-      <c r="D10" s="21" t="n"/>
-      <c r="E10" s="21" t="inlineStr">
-        <is>
-          <t>protocol_report</t>
-        </is>
-      </c>
-      <c r="F10" s="21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="G10" s="20">
-        <f>IFERROR(IF(LEN(TRIM(CLEAN(SUBSTITUTE(Setup!$B$2,CHAR(160)," "))))=0,"CHECK REVIEWER ID",IF(OR(A10="",COUNTIF($A$2:$A$19,A10)&lt;&gt;1,LEFT(A10,LEN("2019::jama.2019.17380::"))&lt;&gt;"2019::jama.2019.17380::"),"CHECK KEY",IF(OR(AND(NOT(AND(D10="retain",E10="statistical_results")),H10&lt;&gt;"",NOT(EXACT(H10,"not_applicable"))),AND(NOT(AND(D10="retain",E10="statistical_results")),I10&lt;&gt;"",NOT(EXACT(I10,"not_applicable"))),AND(NOT(AND(D10="retain",E10="statistical_results")),J10&lt;&gt;"",NOT(EXACT(J10,"not_applicable"))),AND(NOT(AND(D10="retain",OR(E10="report_internal_inconsistency",E10="plan_material"))),K10&lt;&gt;"",NOT(EXACT(K10,"not_applicable"))),AND(NOT(AND(D10="retain",E10="protocol_report")),L10&lt;&gt;"",NOT(EXACT(L10,"not_applicable")))),"CLEAR INACTIVE VALUES",IF(OR(NOT(OR(EXACT(D10,"retain"),EXACT(D10,"exclude"),EXACT(D10,"discuss"))),NOT(OR(EXACT(E10,"statistical_results"),EXACT(E10,"report_internal_inconsistency"),EXACT(E10,"plan_material"),EXACT(E10,"protocol_report"))),AND(AND(D10="retain",E10="statistical_results"),NOT(OR(EXACT(H10,"confirmed_issue"),EXACT(H10,"probable_issue"),EXACT(H10,"not_issue"),EXACT(H10,"indeterminate")))),AND(AND(D10="retain",E10="statistical_results"),NOT(OR(EXACT(I10,"substantive"),EXACT(I10,"minor_presentation"),EXACT(I10,"indeterminate")))),AND(AND(D10="retain",E10="statistical_results"),J10&lt;&gt;"",NOT(OR(EXACT(J10,"direct"),EXACT(J10,"possible"),EXACT(J10,"unlikely"),EXACT(J10,"unknown")))),AND(AND(D10="retain",OR(E10="report_internal_inconsistency",E10="plan_material")),NOT(OR(EXACT(K10,"substantive_inconsistency"),EXACT(K10,"minor_presentation"),EXACT(K10,"non_inconsistency"),EXACT(K10,"indeterminate")))),AND(AND(D10="retain",E10="protocol_report"),L10&lt;&gt;"",NOT(OR(EXACT(L10,"substantive_difference"),EXACT(L10,"minor_presentation"),EXACT(L10,"version_timing"),EXACT(L10,"non_inconsistency"),EXACT(L10,"indeterminate"))))),"CHECK FIELDS",IF(AND(F10&lt;&gt;"",NOT(OR(EXACT(F10,"no"),EXACT(F10,"primary_done")))),"CHECK COMPLETE",IF(EXACT(F10,"primary_done"),"PRIMARY READY","PRIMARY DRAFT")))))),"CHECK INPUT / KEY")</f>
-        <v/>
-      </c>
-      <c r="H10" s="21">
-        <f>IF(AND(OR(D10="retain",D10=""),E10="statistical_results"),"","not_applicable")</f>
-        <v/>
-      </c>
-      <c r="I10" s="21">
-        <f>IF(AND(OR(D10="retain",D10=""),E10="statistical_results"),"","not_applicable")</f>
-        <v/>
-      </c>
-      <c r="J10" s="22">
-        <f>IF(AND(OR(D10="retain",D10=""),E10="statistical_results"),"","not_applicable")</f>
-        <v/>
-      </c>
-      <c r="K10" s="21">
-        <f>IF(AND(OR(D10="retain",D10=""),OR(E10="report_internal_inconsistency",E10="plan_material")),"","not_applicable")</f>
-        <v/>
-      </c>
-      <c r="L10" s="22">
-        <f>IF(AND(OR(D10="retain",D10=""),E10="protocol_report"),"","not_applicable")</f>
-        <v/>
-      </c>
-      <c r="M10" s="20" t="n"/>
-      <c r="N10" s="23" t="n"/>
-      <c r="O10" s="23" t="n"/>
-      <c r="P10" s="23" t="n"/>
-      <c r="Q10" s="23" t="n"/>
-      <c r="R10" s="22" t="n"/>
-    </row>
-    <row r="11" ht="92" customFormat="1" customHeight="1" s="14">
-      <c r="A11" s="24" t="inlineStr">
-        <is>
-          <t>2019::jama.2019.17380::C010</t>
-        </is>
-      </c>
-      <c r="B11" s="24" t="inlineStr">
-        <is>
-          <t>Reported primary covariates differ from the planned primary model</t>
-        </is>
-      </c>
-      <c r="C11" s="24" t="inlineStr">
-        <is>
-          <t>joi190122supp1_prod.pdf — p.32 §15e Equation 2 and conditional sensitivity clause; joi190122supp1_prod.pdf — p.33; jama_de_boer_2019_oi_190122.pdf — p.3 Data Analysis; jama_de_boer_2019_oi_190122.pdf — p.8 Table 2 footnote a; joi190122supp2_prod.pdf — p.9 eTable 4; joi190122supp2_prod.pdf — p.10 eTable 5.</t>
-        </is>
-      </c>
-      <c r="D11" s="21" t="n"/>
-      <c r="E11" s="21" t="inlineStr">
-        <is>
-          <t>protocol_report</t>
-        </is>
-      </c>
-      <c r="F11" s="21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="G11" s="24">
-        <f>IFERROR(IF(LEN(TRIM(CLEAN(SUBSTITUTE(Setup!$B$2,CHAR(160)," "))))=0,"CHECK REVIEWER ID",IF(OR(A11="",COUNTIF($A$2:$A$19,A11)&lt;&gt;1,LEFT(A11,LEN("2019::jama.2019.17380::"))&lt;&gt;"2019::jama.2019.17380::"),"CHECK KEY",IF(OR(AND(NOT(AND(D11="retain",E11="statistical_results")),H11&lt;&gt;"",NOT(EXACT(H11,"not_applicable"))),AND(NOT(AND(D11="retain",E11="statistical_results")),I11&lt;&gt;"",NOT(EXACT(I11,"not_applicable"))),AND(NOT(AND(D11="retain",E11="statistical_results")),J11&lt;&gt;"",NOT(EXACT(J11,"not_applicable"))),AND(NOT(AND(D11="retain",OR(E11="report_internal_inconsistency",E11="plan_material"))),K11&lt;&gt;"",NOT(EXACT(K11,"not_applicable"))),AND(NOT(AND(D11="retain",E11="protocol_report")),L11&lt;&gt;"",NOT(EXACT(L11,"not_applicable")))),"CLEAR INACTIVE VALUES",IF(OR(NOT(OR(EXACT(D11,"retain"),EXACT(D11,"exclude"),EXACT(D11,"discuss"))),NOT(OR(EXACT(E11,"statistical_results"),EXACT(E11,"report_internal_inconsistency"),EXACT(E11,"plan_material"),EXACT(E11,"protocol_report"))),AND(AND(D11="retain",E11="statistical_results"),NOT(OR(EXACT(H11,"confirmed_issue"),EXACT(H11,"probable_issue"),EXACT(H11,"not_issue"),EXACT(H11,"indeterminate")))),AND(AND(D11="retain",E11="statistical_results"),NOT(OR(EXACT(I11,"substantive"),EXACT(I11,"minor_presentation"),EXACT(I11,"indeterminate")))),AND(AND(D11="retain",E11="statistical_results"),J11&lt;&gt;"",NOT(OR(EXACT(J11,"direct"),EXACT(J11,"possible"),EXACT(J11,"unlikely"),EXACT(J11,"unknown")))),AND(AND(D11="retain",OR(E11="report_internal_inconsistency",E11="plan_material")),NOT(OR(EXACT(K11,"substantive_inconsistency"),EXACT(K11,"minor_presentation"),EXACT(K11,"non_inconsistency"),EXACT(K11,"indeterminate")))),AND(AND(D11="retain",E11="protocol_report"),L11&lt;&gt;"",NOT(OR(EXACT(L11,"substantive_difference"),EXACT(L11,"minor_presentation"),EXACT(L11,"version_timing"),EXACT(L11,"non_inconsistency"),EXACT(L11,"indeterminate"))))),"CHECK FIELDS",IF(AND(F11&lt;&gt;"",NOT(OR(EXACT(F11,"no"),EXACT(F11,"primary_done")))),"CHECK COMPLETE",IF(EXACT(F11,"primary_done"),"PRIMARY READY","PRIMARY DRAFT")))))),"CHECK INPUT / KEY")</f>
-        <v/>
-      </c>
-      <c r="H11" s="21">
-        <f>IF(AND(OR(D11="retain",D11=""),E11="statistical_results"),"","not_applicable")</f>
-        <v/>
-      </c>
-      <c r="I11" s="21">
-        <f>IF(AND(OR(D11="retain",D11=""),E11="statistical_results"),"","not_applicable")</f>
-        <v/>
-      </c>
-      <c r="J11" s="22">
-        <f>IF(AND(OR(D11="retain",D11=""),E11="statistical_results"),"","not_applicable")</f>
-        <v/>
-      </c>
-      <c r="K11" s="21">
-        <f>IF(AND(OR(D11="retain",D11=""),OR(E11="report_internal_inconsistency",E11="plan_material")),"","not_applicable")</f>
-        <v/>
-      </c>
-      <c r="L11" s="22">
-        <f>IF(AND(OR(D11="retain",D11=""),E11="protocol_report"),"","not_applicable")</f>
-        <v/>
-      </c>
-      <c r="M11" s="24" t="n"/>
-      <c r="N11" s="23" t="n"/>
-      <c r="O11" s="23" t="n"/>
-      <c r="P11" s="23" t="n"/>
-      <c r="Q11" s="23" t="n"/>
-      <c r="R11" s="22" t="n"/>
-    </row>
-    <row r="12" ht="92" customFormat="1" customHeight="1" s="14">
-      <c r="A12" s="20" t="inlineStr">
-        <is>
-          <t>2019::jama.2019.17380::C011</t>
-        </is>
-      </c>
-      <c r="B12" s="20" t="inlineStr">
-        <is>
-          <t>Planned bioavailable vitamin-D subgroup result is absent</t>
-        </is>
-      </c>
-      <c r="C12" s="20" t="inlineStr">
-        <is>
-          <t>joi190122supp1_prod.pdf — p.33 §15f; jama_de_boer_2019_oi_190122.pdf — p.3 subgroup methods; jama_de_boer_2019_oi_190122.pdf — p.8 Figure 3; jama_de_boer_2019_oi_190122.pdf — p.9 interpretation; jama_de_boer_2019_oi_190122.pdf — p.10 interpretation/disclosure; joi190122supp2_prod.pdf — p.18 eFigure 2; joi190122supp2_prod.pdf — p.17 eFigure 1; joi190122supp3_prod.pdf — data-sharing statement p.1.</t>
-        </is>
-      </c>
-      <c r="D12" s="21" t="n"/>
-      <c r="E12" s="21" t="inlineStr">
-        <is>
-          <t>protocol_report</t>
-        </is>
-      </c>
-      <c r="F12" s="21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="G12" s="20">
-        <f>IFERROR(IF(LEN(TRIM(CLEAN(SUBSTITUTE(Setup!$B$2,CHAR(160)," "))))=0,"CHECK REVIEWER ID",IF(OR(A12="",COUNTIF($A$2:$A$19,A12)&lt;&gt;1,LEFT(A12,LEN("2019::jama.2019.17380::"))&lt;&gt;"2019::jama.2019.17380::"),"CHECK KEY",IF(OR(AND(NOT(AND(D12="retain",E12="statistical_results")),H12&lt;&gt;"",NOT(EXACT(H12,"not_applicable"))),AND(NOT(AND(D12="retain",E12="statistical_results")),I12&lt;&gt;"",NOT(EXACT(I12,"not_applicable"))),AND(NOT(AND(D12="retain",E12="statistical_results")),J12&lt;&gt;"",NOT(EXACT(J12,"not_applicable"))),AND(NOT(AND(D12="retain",OR(E12="report_internal_inconsistency",E12="plan_material"))),K12&lt;&gt;"",NOT(EXACT(K12,"not_applicable"))),AND(NOT(AND(D12="retain",E12="protocol_report")),L12&lt;&gt;"",NOT(EXACT(L12,"not_applicable")))),"CLEAR INACTIVE VALUES",IF(OR(NOT(OR(EXACT(D12,"retain"),EXACT(D12,"exclude"),EXACT(D12,"discuss"))),NOT(OR(EXACT(E12,"statistical_results"),EXACT(E12,"report_internal_inconsistency"),EXACT(E12,"plan_material"),EXACT(E12,"protocol_report"))),AND(AND(D12="retain",E12="statistical_results"),NOT(OR(EXACT(H12,"confirmed_issue"),EXACT(H12,"probable_issue"),EXACT(H12,"not_issue"),EXACT(H12,"indeterminate")))),AND(AND(D12="retain",E12="statistical_results"),NOT(OR(EXACT(I12,"substantive"),EXACT(I12,"minor_presentation"),EXACT(I12,"indeterminate")))),AND(AND(D12="retain",E12="statistical_results"),J12&lt;&gt;"",NOT(OR(EXACT(J12,"direct"),EXACT(J12,"possible"),EXACT(J12,"unlikely"),EXACT(J12,"unknown")))),AND(AND(D12="retain",OR(E12="report_internal_inconsistency",E12="plan_material")),NOT(OR(EXACT(K12,"substantive_inconsistency"),EXACT(K12,"minor_presentation"),EXACT(K12,"non_inconsistency"),EXACT(K12,"indeterminate")))),AND(AND(D12="retain",E12="protocol_report"),L12&lt;&gt;"",NOT(OR(EXACT(L12,"substantive_difference"),EXACT(L12,"minor_presentation"),EXACT(L12,"version_timing"),EXACT(L12,"non_inconsistency"),EXACT(L12,"indeterminate"))))),"CHECK FIELDS",IF(AND(F12&lt;&gt;"",NOT(OR(EXACT(F12,"no"),EXACT(F12,"primary_done")))),"CHECK COMPLETE",IF(EXACT(F12,"primary_done"),"PRIMARY READY","PRIMARY DRAFT")))))),"CHECK INPUT / KEY")</f>
-        <v/>
-      </c>
-      <c r="H12" s="21">
-        <f>IF(AND(OR(D12="retain",D12=""),E12="statistical_results"),"","not_applicable")</f>
-        <v/>
-      </c>
-      <c r="I12" s="21">
-        <f>IF(AND(OR(D12="retain",D12=""),E12="statistical_results"),"","not_applicable")</f>
-        <v/>
-      </c>
-      <c r="J12" s="22">
-        <f>IF(AND(OR(D12="retain",D12=""),E12="statistical_results"),"","not_applicable")</f>
-        <v/>
-      </c>
-      <c r="K12" s="21">
-        <f>IF(AND(OR(D12="retain",D12=""),OR(E12="report_internal_inconsistency",E12="plan_material")),"","not_applicable")</f>
-        <v/>
-      </c>
-      <c r="L12" s="22">
-        <f>IF(AND(OR(D12="retain",D12=""),E12="protocol_report"),"","not_applicable")</f>
-        <v/>
-      </c>
-      <c r="M12" s="20" t="n"/>
-      <c r="N12" s="23" t="n"/>
-      <c r="O12" s="23" t="n"/>
-      <c r="P12" s="23" t="n"/>
-      <c r="Q12" s="23" t="n"/>
-      <c r="R12" s="22" t="n"/>
-    </row>
-    <row r="13" ht="92" customFormat="1" customHeight="1" s="14">
-      <c r="A13" s="24" t="inlineStr">
-        <is>
-          <t>2019::jama.2019.17380::C012</t>
-        </is>
-      </c>
-      <c r="B13" s="24" t="inlineStr">
-        <is>
-          <t>Forest figures associate counts with opposite treatment columns</t>
-        </is>
-      </c>
-      <c r="C13" s="24" t="inlineStr">
-        <is>
-          <t>jama_de_boer_2019_oi_190122.pdf — main p.8 Figure 3 and Table 2; jama_de_boer_2019_oi_190122.pdf — main p.9 Figure 4; joi190122supp2_prod.pdf — supplement p.18 eFigure 2; joi190122supp2_prod.pdf — supplement p.19 eFigure 3; jama_de_boer_2019_oi_190122.pdf — main p.1 allocation; jama_de_boer_2019_oi_190122.pdf — p.5 Table 1; jama_de_boer_2019_oi_190122.pdf — p.6 Figure 1; joi190122supp2_prod.pdf — supplement p.11 eTable 6; joi190122supp2_prod.pdf — p.16 eTable 11 marginal allocations.</t>
-        </is>
-      </c>
-      <c r="D13" s="21" t="n"/>
-      <c r="E13" s="21" t="inlineStr">
-        <is>
-          <t>statistical_results</t>
-        </is>
-      </c>
-      <c r="F13" s="21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="G13" s="24">
-        <f>IFERROR(IF(LEN(TRIM(CLEAN(SUBSTITUTE(Setup!$B$2,CHAR(160)," "))))=0,"CHECK REVIEWER ID",IF(OR(A13="",COUNTIF($A$2:$A$19,A13)&lt;&gt;1,LEFT(A13,LEN("2019::jama.2019.17380::"))&lt;&gt;"2019::jama.2019.17380::"),"CHECK KEY",IF(OR(AND(NOT(AND(D13="retain",E13="statistical_results")),H13&lt;&gt;"",NOT(EXACT(H13,"not_applicable"))),AND(NOT(AND(D13="retain",E13="statistical_results")),I13&lt;&gt;"",NOT(EXACT(I13,"not_applicable"))),AND(NOT(AND(D13="retain",E13="statistical_results")),J13&lt;&gt;"",NOT(EXACT(J13,"not_applicable"))),AND(NOT(AND(D13="retain",OR(E13="report_internal_inconsistency",E13="plan_material"))),K13&lt;&gt;"",NOT(EXACT(K13,"not_applicable"))),AND(NOT(AND(D13="retain",E13="protocol_report")),L13&lt;&gt;"",NOT(EXACT(L13,"not_applicable")))),"CLEAR INACTIVE VALUES",IF(OR(NOT(OR(EXACT(D13,"retain"),EXACT(D13,"exclude"),EXACT(D13,"discuss"))),NOT(OR(EXACT(E13,"statistical_results"),EXACT(E13,"report_internal_inconsistency"),EXACT(E13,"plan_material"),EXACT(E13,"protocol_report"))),AND(AND(D13="retain",E13="statistical_results"),NOT(OR(EXACT(H13,"confirmed_issue"),EXACT(H13,"probable_issue"),EXACT(H13,"not_issue"),EXACT(H13,"indeterminate")))),AND(AND(D13="retain",E13="statistical_results"),NOT(OR(EXACT(I13,"substantive"),EXACT(I13,"minor_presentation"),EXACT(I13,"indeterminate")))),AND(AND(D13="retain",E13="statistical_results"),J13&lt;&gt;"",NOT(OR(EXACT(J13,"direct"),EXACT(J13,"possible"),EXACT(J13,"unlikely"),EXACT(J13,"unknown")))),AND(AND(D13="retain",OR(E13="report_internal_inconsistency",E13="plan_material")),NOT(OR(EXACT(K13,"substantive_inconsistency"),EXACT(K13,"minor_presentation"),EXACT(K13,"non_inconsistency"),EXACT(K13,"indeterminate")))),AND(AND(D13="retain",E13="protocol_report"),L13&lt;&gt;"",NOT(OR(EXACT(L13,"substantive_difference"),EXACT(L13,"minor_presentation"),EXACT(L13,"version_timing"),EXACT(L13,"non_inconsistency"),EXACT(L13,"indeterminate"))))),"CHECK FIELDS",IF(AND(F13&lt;&gt;"",NOT(OR(EXACT(F13,"no"),EXACT(F13,"primary_done")))),"CHECK COMPLETE",IF(EXACT(F13,"primary_done"),"PRIMARY READY","PRIMARY DRAFT")))))),"CHECK INPUT / KEY")</f>
-        <v/>
-      </c>
-      <c r="H13" s="21">
-        <f>IF(AND(OR(D13="retain",D13=""),E13="statistical_results"),"","not_applicable")</f>
-        <v/>
-      </c>
-      <c r="I13" s="21">
-        <f>IF(AND(OR(D13="retain",D13=""),E13="statistical_results"),"","not_applicable")</f>
-        <v/>
-      </c>
-      <c r="J13" s="22">
-        <f>IF(AND(OR(D13="retain",D13=""),E13="statistical_results"),"","not_applicable")</f>
-        <v/>
-      </c>
-      <c r="K13" s="21">
-        <f>IF(AND(OR(D13="retain",D13=""),OR(E13="report_internal_inconsistency",E13="plan_material")),"","not_applicable")</f>
-        <v/>
-      </c>
-      <c r="L13" s="22">
-        <f>IF(AND(OR(D13="retain",D13=""),E13="protocol_report"),"","not_applicable")</f>
-        <v/>
-      </c>
-      <c r="M13" s="24" t="n"/>
-      <c r="N13" s="23" t="n"/>
-      <c r="O13" s="23" t="n"/>
-      <c r="P13" s="23" t="n"/>
-      <c r="Q13" s="23" t="n"/>
-      <c r="R13" s="22" t="n"/>
-    </row>
-    <row r="14" ht="92" customFormat="1" customHeight="1" s="14">
-      <c r="A14" s="20" t="inlineStr">
-        <is>
-          <t>2019::jama.2019.17380::C013</t>
-        </is>
-      </c>
-      <c r="B14" s="20" t="inlineStr">
-        <is>
-          <t>Omega-3 contributor rows repeat vitamin-D counts</t>
-        </is>
-      </c>
-      <c r="C14" s="20" t="inlineStr">
-        <is>
-          <t>jama_de_boer_2019_oi_190122.pdf — main p.7 Figure 2 A–D and caption; jama_de_boer_2019_oi_190122.pdf — main p.8 Table 2; joi190122supp2_prod.pdf — supplement p.11 eTable 6; jama_de_boer_2019_oi_190122.pdf — main p.1 allocation.</t>
-        </is>
-      </c>
-      <c r="D14" s="21" t="n"/>
-      <c r="E14" s="21" t="inlineStr">
-        <is>
-          <t>statistical_results</t>
-        </is>
-      </c>
-      <c r="F14" s="21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="G14" s="20">
-        <f>IFERROR(IF(LEN(TRIM(CLEAN(SUBSTITUTE(Setup!$B$2,CHAR(160)," "))))=0,"CHECK REVIEWER ID",IF(OR(A14="",COUNTIF($A$2:$A$19,A14)&lt;&gt;1,LEFT(A14,LEN("2019::jama.2019.17380::"))&lt;&gt;"2019::jama.2019.17380::"),"CHECK KEY",IF(OR(AND(NOT(AND(D14="retain",E14="statistical_results")),H14&lt;&gt;"",NOT(EXACT(H14,"not_applicable"))),AND(NOT(AND(D14="retain",E14="statistical_results")),I14&lt;&gt;"",NOT(EXACT(I14,"not_applicable"))),AND(NOT(AND(D14="retain",E14="statistical_results")),J14&lt;&gt;"",NOT(EXACT(J14,"not_applicable"))),AND(NOT(AND(D14="retain",OR(E14="report_internal_inconsistency",E14="plan_material"))),K14&lt;&gt;"",NOT(EXACT(K14,"not_applicable"))),AND(NOT(AND(D14="retain",E14="protocol_report")),L14&lt;&gt;"",NOT(EXACT(L14,"not_applicable")))),"CLEAR INACTIVE VALUES",IF(OR(NOT(OR(EXACT(D14,"retain"),EXACT(D14,"exclude"),EXACT(D14,"discuss"))),NOT(OR(EXACT(E14,"statistical_results"),EXACT(E14,"report_internal_inconsistency"),EXACT(E14,"plan_material"),EXACT(E14,"protocol_report"))),AND(AND(D14="retain",E14="statistical_results"),NOT(OR(EXACT(H14,"confirmed_issue"),EXACT(H14,"probable_issue"),EXACT(H14,"not_issue"),EXACT(H14,"indeterminate")))),AND(AND(D14="retain",E14="statistical_results"),NOT(OR(EXACT(I14,"substantive"),EXACT(I14,"minor_presentation"),EXACT(I14,"indeterminate")))),AND(AND(D14="retain",E14="statistical_results"),J14&lt;&gt;"",NOT(OR(EXACT(J14,"direct"),EXACT(J14,"possible"),EXACT(J14,"unlikely"),EXACT(J14,"unknown")))),AND(AND(D14="retain",OR(E14="report_internal_inconsistency",E14="plan_material")),NOT(OR(EXACT(K14,"substantive_inconsistency"),EXACT(K14,"minor_presentation"),EXACT(K14,"non_inconsistency"),EXACT(K14,"indeterminate")))),AND(AND(D14="retain",E14="protocol_report"),L14&lt;&gt;"",NOT(OR(EXACT(L14,"substantive_difference"),EXACT(L14,"minor_presentation"),EXACT(L14,"version_timing"),EXACT(L14,"non_inconsistency"),EXACT(L14,"indeterminate"))))),"CHECK FIELDS",IF(AND(F14&lt;&gt;"",NOT(OR(EXACT(F14,"no"),EXACT(F14,"primary_done")))),"CHECK COMPLETE",IF(EXACT(F14,"primary_done"),"PRIMARY READY","PRIMARY DRAFT")))))),"CHECK INPUT / KEY")</f>
-        <v/>
-      </c>
-      <c r="H14" s="21">
-        <f>IF(AND(OR(D14="retain",D14=""),E14="statistical_results"),"","not_applicable")</f>
-        <v/>
-      </c>
-      <c r="I14" s="21">
-        <f>IF(AND(OR(D14="retain",D14=""),E14="statistical_results"),"","not_applicable")</f>
-        <v/>
-      </c>
-      <c r="J14" s="22">
-        <f>IF(AND(OR(D14="retain",D14=""),E14="statistical_results"),"","not_applicable")</f>
-        <v/>
-      </c>
-      <c r="K14" s="21">
-        <f>IF(AND(OR(D14="retain",D14=""),OR(E14="report_internal_inconsistency",E14="plan_material")),"","not_applicable")</f>
-        <v/>
-      </c>
-      <c r="L14" s="22">
-        <f>IF(AND(OR(D14="retain",D14=""),E14="protocol_report"),"","not_applicable")</f>
-        <v/>
-      </c>
-      <c r="M14" s="20" t="n"/>
-      <c r="N14" s="23" t="n"/>
-      <c r="O14" s="23" t="n"/>
-      <c r="P14" s="23" t="n"/>
-      <c r="Q14" s="23" t="n"/>
-      <c r="R14" s="22" t="n"/>
-    </row>
-    <row r="15" ht="92" customFormat="1" customHeight="1" s="14">
-      <c r="A15" s="24" t="inlineStr">
-        <is>
-          <t>2019::jama.2019.17380::C014</t>
-        </is>
-      </c>
-      <c r="B15" s="24" t="inlineStr">
-        <is>
-          <t>Plan gives two microgram equivalents for the same vitamin-D dose</t>
-        </is>
-      </c>
-      <c r="C15" s="24" t="inlineStr">
-        <is>
-          <t>joi190122supp1_prod.pdf — p.15 V.e.1; joi190122supp1_prod.pdf — p.21 VII.a; jama_de_boer_2019_oi_190122.pdf — main p.2 intervention.</t>
-        </is>
-      </c>
-      <c r="D15" s="21" t="n"/>
-      <c r="E15" s="21" t="inlineStr">
-        <is>
-          <t>plan_material</t>
-        </is>
-      </c>
-      <c r="F15" s="21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="G15" s="24">
-        <f>IFERROR(IF(LEN(TRIM(CLEAN(SUBSTITUTE(Setup!$B$2,CHAR(160)," "))))=0,"CHECK REVIEWER ID",IF(OR(A15="",COUNTIF($A$2:$A$19,A15)&lt;&gt;1,LEFT(A15,LEN("2019::jama.2019.17380::"))&lt;&gt;"2019::jama.2019.17380::"),"CHECK KEY",IF(OR(AND(NOT(AND(D15="retain",E15="statistical_results")),H15&lt;&gt;"",NOT(EXACT(H15,"not_applicable"))),AND(NOT(AND(D15="retain",E15="statistical_results")),I15&lt;&gt;"",NOT(EXACT(I15,"not_applicable"))),AND(NOT(AND(D15="retain",E15="statistical_results")),J15&lt;&gt;"",NOT(EXACT(J15,"not_applicable"))),AND(NOT(AND(D15="retain",OR(E15="report_internal_inconsistency",E15="plan_material"))),K15&lt;&gt;"",NOT(EXACT(K15,"not_applicable"))),AND(NOT(AND(D15="retain",E15="protocol_report")),L15&lt;&gt;"",NOT(EXACT(L15,"not_applicable")))),"CLEAR INACTIVE VALUES",IF(OR(NOT(OR(EXACT(D15,"retain"),EXACT(D15,"exclude"),EXACT(D15,"discuss"))),NOT(OR(EXACT(E15,"statistical_results"),EXACT(E15,"report_internal_inconsistency"),EXACT(E15,"plan_material"),EXACT(E15,"protocol_report"))),AND(AND(D15="retain",E15="statistical_results"),NOT(OR(EXACT(H15,"confirmed_issue"),EXACT(H15,"probable_issue"),EXACT(H15,"not_issue"),EXACT(H15,"indeterminate")))),AND(AND(D15="retain",E15="statistical_results"),NOT(OR(EXACT(I15,"substantive"),EXACT(I15,"minor_presentation"),EXACT(I15,"indeterminate")))),AND(AND(D15="retain",E15="statistical_results"),J15&lt;&gt;"",NOT(OR(EXACT(J15,"direct"),EXACT(J15,"possible"),EXACT(J15,"unlikely"),EXACT(J15,"unknown")))),AND(AND(D15="retain",OR(E15="report_internal_inconsistency",E15="plan_material")),NOT(OR(EXACT(K15,"substantive_inconsistency"),EXACT(K15,"minor_presentation"),EXACT(K15,"non_inconsistency"),EXACT(K15,"indeterminate")))),AND(AND(D15="retain",E15="protocol_report"),L15&lt;&gt;"",NOT(OR(EXACT(L15,"substantive_difference"),EXACT(L15,"minor_presentation"),EXACT(L15,"version_timing"),EXACT(L15,"non_inconsistency"),EXACT(L15,"indeterminate"))))),"CHECK FIELDS",IF(AND(F15&lt;&gt;"",NOT(OR(EXACT(F15,"no"),EXACT(F15,"primary_done")))),"CHECK COMPLETE",IF(EXACT(F15,"primary_done"),"PRIMARY READY","PRIMARY DRAFT")))))),"CHECK INPUT / KEY")</f>
-        <v/>
-      </c>
-      <c r="H15" s="21">
-        <f>IF(AND(OR(D15="retain",D15=""),E15="statistical_results"),"","not_applicable")</f>
-        <v/>
-      </c>
-      <c r="I15" s="21">
-        <f>IF(AND(OR(D15="retain",D15=""),E15="statistical_results"),"","not_applicable")</f>
-        <v/>
-      </c>
-      <c r="J15" s="22">
-        <f>IF(AND(OR(D15="retain",D15=""),E15="statistical_results"),"","not_applicable")</f>
-        <v/>
-      </c>
-      <c r="K15" s="21">
-        <f>IF(AND(OR(D15="retain",D15=""),OR(E15="report_internal_inconsistency",E15="plan_material")),"","not_applicable")</f>
-        <v/>
-      </c>
-      <c r="L15" s="22">
-        <f>IF(AND(OR(D15="retain",D15=""),E15="protocol_report"),"","not_applicable")</f>
-        <v/>
-      </c>
-      <c r="M15" s="24" t="n"/>
-      <c r="N15" s="23" t="n"/>
-      <c r="O15" s="23" t="n"/>
-      <c r="P15" s="23" t="n"/>
-      <c r="Q15" s="23" t="n"/>
-      <c r="R15" s="22" t="n"/>
-    </row>
-    <row r="16" ht="92" customFormat="1" customHeight="1" s="14">
-      <c r="A16" s="20" t="inlineStr">
-        <is>
-          <t>2019::jama.2019.17380::C015</t>
-        </is>
-      </c>
-      <c r="B16" s="20" t="inlineStr">
-        <is>
-          <t>Plan interaction and primary models specify different time terms</t>
-        </is>
-      </c>
-      <c r="C16" s="20" t="inlineStr">
-        <is>
-          <t>joi190122supp1_prod.pdf — p.32 §15d Equation 1 and §15e Equation 2; jama_de_boer_2019_oi_190122.pdf — main p.3; jama_de_boer_2019_oi_190122.pdf — p.4.</t>
-        </is>
-      </c>
-      <c r="D16" s="21" t="n"/>
-      <c r="E16" s="21" t="inlineStr">
-        <is>
-          <t>plan_material</t>
-        </is>
-      </c>
-      <c r="F16" s="21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="G16" s="20">
-        <f>IFERROR(IF(LEN(TRIM(CLEAN(SUBSTITUTE(Setup!$B$2,CHAR(160)," "))))=0,"CHECK REVIEWER ID",IF(OR(A16="",COUNTIF($A$2:$A$19,A16)&lt;&gt;1,LEFT(A16,LEN("2019::jama.2019.17380::"))&lt;&gt;"2019::jama.2019.17380::"),"CHECK KEY",IF(OR(AND(NOT(AND(D16="retain",E16="statistical_results")),H16&lt;&gt;"",NOT(EXACT(H16,"not_applicable"))),AND(NOT(AND(D16="retain",E16="statistical_results")),I16&lt;&gt;"",NOT(EXACT(I16,"not_applicable"))),AND(NOT(AND(D16="retain",E16="statistical_results")),J16&lt;&gt;"",NOT(EXACT(J16,"not_applicable"))),AND(NOT(AND(D16="retain",OR(E16="report_internal_inconsistency",E16="plan_material"))),K16&lt;&gt;"",NOT(EXACT(K16,"not_applicable"))),AND(NOT(AND(D16="retain",E16="protocol_report")),L16&lt;&gt;"",NOT(EXACT(L16,"not_applicable")))),"CLEAR INACTIVE VALUES",IF(OR(NOT(OR(EXACT(D16,"retain"),EXACT(D16,"exclude"),EXACT(D16,"discuss"))),NOT(OR(EXACT(E16,"statistical_results"),EXACT(E16,"report_internal_inconsistency"),EXACT(E16,"plan_material"),EXACT(E16,"protocol_report"))),AND(AND(D16="retain",E16="statistical_results"),NOT(OR(EXACT(H16,"confirmed_issue"),EXACT(H16,"probable_issue"),EXACT(H16,"not_issue"),EXACT(H16,"indeterminate")))),AND(AND(D16="retain",E16="statistical_results"),NOT(OR(EXACT(I16,"substantive"),EXACT(I16,"minor_presentation"),EXACT(I16,"indeterminate")))),AND(AND(D16="retain",E16="statistical_results"),J16&lt;&gt;"",NOT(OR(EXACT(J16,"direct"),EXACT(J16,"possible"),EXACT(J16,"unlikely"),EXACT(J16,"unknown")))),AND(AND(D16="retain",OR(E16="report_internal_inconsistency",E16="plan_material")),NOT(OR(EXACT(K16,"substantive_inconsistency"),EXACT(K16,"minor_presentation"),EXACT(K16,"non_inconsistency"),EXACT(K16,"indeterminate")))),AND(AND(D16="retain",E16="protocol_report"),L16&lt;&gt;"",NOT(OR(EXACT(L16,"substantive_difference"),EXACT(L16,"minor_presentation"),EXACT(L16,"version_timing"),EXACT(L16,"non_inconsistency"),EXACT(L16,"indeterminate"))))),"CHECK FIELDS",IF(AND(F16&lt;&gt;"",NOT(OR(EXACT(F16,"no"),EXACT(F16,"primary_done")))),"CHECK COMPLETE",IF(EXACT(F16,"primary_done"),"PRIMARY READY","PRIMARY DRAFT")))))),"CHECK INPUT / KEY")</f>
-        <v/>
-      </c>
-      <c r="H16" s="21">
-        <f>IF(AND(OR(D16="retain",D16=""),E16="statistical_results"),"","not_applicable")</f>
-        <v/>
-      </c>
-      <c r="I16" s="21">
-        <f>IF(AND(OR(D16="retain",D16=""),E16="statistical_results"),"","not_applicable")</f>
-        <v/>
-      </c>
-      <c r="J16" s="22">
-        <f>IF(AND(OR(D16="retain",D16=""),E16="statistical_results"),"","not_applicable")</f>
-        <v/>
-      </c>
-      <c r="K16" s="21">
-        <f>IF(AND(OR(D16="retain",D16=""),OR(E16="report_internal_inconsistency",E16="plan_material")),"","not_applicable")</f>
-        <v/>
-      </c>
-      <c r="L16" s="22">
-        <f>IF(AND(OR(D16="retain",D16=""),E16="protocol_report"),"","not_applicable")</f>
-        <v/>
-      </c>
-      <c r="M16" s="20" t="n"/>
-      <c r="N16" s="23" t="n"/>
-      <c r="O16" s="23" t="n"/>
-      <c r="P16" s="23" t="n"/>
-      <c r="Q16" s="23" t="n"/>
-      <c r="R16" s="22" t="n"/>
-    </row>
-    <row r="17" ht="92" customFormat="1" customHeight="1" s="14">
-      <c r="A17" s="24" t="inlineStr">
-        <is>
-          <t>2019::jama.2019.17380::C016</t>
-        </is>
-      </c>
-      <c r="B17" s="24" t="inlineStr">
-        <is>
-          <t>Year-5 SGLT2 count and percentage do not reconcile</t>
-        </is>
-      </c>
-      <c r="C17" s="24" t="inlineStr">
-        <is>
-          <t>joi190122supp2_prod.pdf — supplement p.7 eTable 2.</t>
-        </is>
-      </c>
-      <c r="D17" s="21" t="n"/>
-      <c r="E17" s="21" t="inlineStr">
-        <is>
-          <t>statistical_results</t>
-        </is>
-      </c>
-      <c r="F17" s="21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="G17" s="24">
-        <f>IFERROR(IF(LEN(TRIM(CLEAN(SUBSTITUTE(Setup!$B$2,CHAR(160)," "))))=0,"CHECK REVIEWER ID",IF(OR(A17="",COUNTIF($A$2:$A$19,A17)&lt;&gt;1,LEFT(A17,LEN("2019::jama.2019.17380::"))&lt;&gt;"2019::jama.2019.17380::"),"CHECK KEY",IF(OR(AND(NOT(AND(D17="retain",E17="statistical_results")),H17&lt;&gt;"",NOT(EXACT(H17,"not_applicable"))),AND(NOT(AND(D17="retain",E17="statistical_results")),I17&lt;&gt;"",NOT(EXACT(I17,"not_applicable"))),AND(NOT(AND(D17="retain",E17="statistical_results")),J17&lt;&gt;"",NOT(EXACT(J17,"not_applicable"))),AND(NOT(AND(D17="retain",OR(E17="report_internal_inconsistency",E17="plan_material"))),K17&lt;&gt;"",NOT(EXACT(K17,"not_applicable"))),AND(NOT(AND(D17="retain",E17="protocol_report")),L17&lt;&gt;"",NOT(EXACT(L17,"not_applicable")))),"CLEAR INACTIVE VALUES",IF(OR(NOT(OR(EXACT(D17,"retain"),EXACT(D17,"exclude"),EXACT(D17,"discuss"))),NOT(OR(EXACT(E17,"statistical_results"),EXACT(E17,"report_internal_inconsistency"),EXACT(E17,"plan_material"),EXACT(E17,"protocol_report"))),AND(AND(D17="retain",E17="statistical_results"),NOT(OR(EXACT(H17,"confirmed_issue"),EXACT(H17,"probable_issue"),EXACT(H17,"not_issue"),EXACT(H17,"indeterminate")))),AND(AND(D17="retain",E17="statistical_results"),NOT(OR(EXACT(I17,"substantive"),EXACT(I17,"minor_presentation"),EXACT(I17,"indeterminate")))),AND(AND(D17="retain",E17="statistical_results"),J17&lt;&gt;"",NOT(OR(EXACT(J17,"direct"),EXACT(J17,"possible"),EXACT(J17,"unlikely"),EXACT(J17,"unknown")))),AND(AND(D17="retain",OR(E17="report_internal_inconsistency",E17="plan_material")),NOT(OR(EXACT(K17,"substantive_inconsistency"),EXACT(K17,"minor_presentation"),EXACT(K17,"non_inconsistency"),EXACT(K17,"indeterminate")))),AND(AND(D17="retain",E17="protocol_report"),L17&lt;&gt;"",NOT(OR(EXACT(L17,"substantive_difference"),EXACT(L17,"minor_presentation"),EXACT(L17,"version_timing"),EXACT(L17,"non_inconsistency"),EXACT(L17,"indeterminate"))))),"CHECK FIELDS",IF(AND(F17&lt;&gt;"",NOT(OR(EXACT(F17,"no"),EXACT(F17,"primary_done")))),"CHECK COMPLETE",IF(EXACT(F17,"primary_done"),"PRIMARY READY","PRIMARY DRAFT")))))),"CHECK INPUT / KEY")</f>
-        <v/>
-      </c>
-      <c r="H17" s="21">
-        <f>IF(AND(OR(D17="retain",D17=""),E17="statistical_results"),"","not_applicable")</f>
-        <v/>
-      </c>
-      <c r="I17" s="21">
-        <f>IF(AND(OR(D17="retain",D17=""),E17="statistical_results"),"","not_applicable")</f>
-        <v/>
-      </c>
-      <c r="J17" s="22">
-        <f>IF(AND(OR(D17="retain",D17=""),E17="statistical_results"),"","not_applicable")</f>
-        <v/>
-      </c>
-      <c r="K17" s="21">
-        <f>IF(AND(OR(D17="retain",D17=""),OR(E17="report_internal_inconsistency",E17="plan_material")),"","not_applicable")</f>
-        <v/>
-      </c>
-      <c r="L17" s="22">
-        <f>IF(AND(OR(D17="retain",D17=""),E17="protocol_report"),"","not_applicable")</f>
-        <v/>
-      </c>
-      <c r="M17" s="24" t="n"/>
-      <c r="N17" s="23" t="n"/>
-      <c r="O17" s="23" t="n"/>
-      <c r="P17" s="23" t="n"/>
-      <c r="Q17" s="23" t="n"/>
-      <c r="R17" s="22" t="n"/>
-    </row>
-    <row r="18" ht="92" customFormat="1" customHeight="1" s="14">
-      <c r="A18" s="20" t="inlineStr">
-        <is>
-          <t>2019::jama.2019.17380::C017</t>
-        </is>
-      </c>
-      <c r="B18" s="20" t="inlineStr">
-        <is>
-          <t>Paired-urine exclusion accounting does not reconcile</t>
-        </is>
-      </c>
-      <c r="C18" s="20" t="inlineStr">
-        <is>
-          <t>joi190122supp2_prod.pdf — supplement p.12 eTable 7.</t>
-        </is>
-      </c>
-      <c r="D18" s="21" t="n"/>
-      <c r="E18" s="21" t="inlineStr">
-        <is>
-          <t>statistical_results</t>
-        </is>
-      </c>
-      <c r="F18" s="21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="G18" s="20">
-        <f>IFERROR(IF(LEN(TRIM(CLEAN(SUBSTITUTE(Setup!$B$2,CHAR(160)," "))))=0,"CHECK REVIEWER ID",IF(OR(A18="",COUNTIF($A$2:$A$19,A18)&lt;&gt;1,LEFT(A18,LEN("2019::jama.2019.17380::"))&lt;&gt;"2019::jama.2019.17380::"),"CHECK KEY",IF(OR(AND(NOT(AND(D18="retain",E18="statistical_results")),H18&lt;&gt;"",NOT(EXACT(H18,"not_applicable"))),AND(NOT(AND(D18="retain",E18="statistical_results")),I18&lt;&gt;"",NOT(EXACT(I18,"not_applicable"))),AND(NOT(AND(D18="retain",E18="statistical_results")),J18&lt;&gt;"",NOT(EXACT(J18,"not_applicable"))),AND(NOT(AND(D18="retain",OR(E18="report_internal_inconsistency",E18="plan_material"))),K18&lt;&gt;"",NOT(EXACT(K18,"not_applicable"))),AND(NOT(AND(D18="retain",E18="protocol_report")),L18&lt;&gt;"",NOT(EXACT(L18,"not_applicable")))),"CLEAR INACTIVE VALUES",IF(OR(NOT(OR(EXACT(D18,"retain"),EXACT(D18,"exclude"),EXACT(D18,"discuss"))),NOT(OR(EXACT(E18,"statistical_results"),EXACT(E18,"report_internal_inconsistency"),EXACT(E18,"plan_material"),EXACT(E18,"protocol_report"))),AND(AND(D18="retain",E18="statistical_results"),NOT(OR(EXACT(H18,"confirmed_issue"),EXACT(H18,"probable_issue"),EXACT(H18,"not_issue"),EXACT(H18,"indeterminate")))),AND(AND(D18="retain",E18="statistical_results"),NOT(OR(EXACT(I18,"substantive"),EXACT(I18,"minor_presentation"),EXACT(I18,"indeterminate")))),AND(AND(D18="retain",E18="statistical_results"),J18&lt;&gt;"",NOT(OR(EXACT(J18,"direct"),EXACT(J18,"possible"),EXACT(J18,"unlikely"),EXACT(J18,"unknown")))),AND(AND(D18="retain",OR(E18="report_internal_inconsistency",E18="plan_material")),NOT(OR(EXACT(K18,"substantive_inconsistency"),EXACT(K18,"minor_presentation"),EXACT(K18,"non_inconsistency"),EXACT(K18,"indeterminate")))),AND(AND(D18="retain",E18="protocol_report"),L18&lt;&gt;"",NOT(OR(EXACT(L18,"substantive_difference"),EXACT(L18,"minor_presentation"),EXACT(L18,"version_timing"),EXACT(L18,"non_inconsistency"),EXACT(L18,"indeterminate"))))),"CHECK FIELDS",IF(AND(F18&lt;&gt;"",NOT(OR(EXACT(F18,"no"),EXACT(F18,"primary_done")))),"CHECK COMPLETE",IF(EXACT(F18,"primary_done"),"PRIMARY READY","PRIMARY DRAFT")))))),"CHECK INPUT / KEY")</f>
-        <v/>
-      </c>
-      <c r="H18" s="21">
-        <f>IF(AND(OR(D18="retain",D18=""),E18="statistical_results"),"","not_applicable")</f>
-        <v/>
-      </c>
-      <c r="I18" s="21">
-        <f>IF(AND(OR(D18="retain",D18=""),E18="statistical_results"),"","not_applicable")</f>
-        <v/>
-      </c>
-      <c r="J18" s="22">
-        <f>IF(AND(OR(D18="retain",D18=""),E18="statistical_results"),"","not_applicable")</f>
-        <v/>
-      </c>
-      <c r="K18" s="21">
-        <f>IF(AND(OR(D18="retain",D18=""),OR(E18="report_internal_inconsistency",E18="plan_material")),"","not_applicable")</f>
-        <v/>
-      </c>
-      <c r="L18" s="22">
-        <f>IF(AND(OR(D18="retain",D18=""),E18="protocol_report"),"","not_applicable")</f>
-        <v/>
-      </c>
-      <c r="M18" s="20" t="n"/>
-      <c r="N18" s="23" t="n"/>
-      <c r="O18" s="23" t="n"/>
-      <c r="P18" s="23" t="n"/>
-      <c r="Q18" s="23" t="n"/>
-      <c r="R18" s="22" t="n"/>
-    </row>
-    <row r="19" ht="92" customFormat="1" customHeight="1" s="14">
-      <c r="A19" s="24" t="inlineStr">
-        <is>
-          <t>2019::jama.2019.17380::C018</t>
-        </is>
-      </c>
-      <c r="B19" s="24" t="inlineStr">
-        <is>
-          <t>Albuminuria forest favor labels reverse the ratio direction</t>
-        </is>
-      </c>
-      <c r="C19" s="24" t="inlineStr">
-        <is>
-          <t>joi190122supp2_prod.pdf — supplement p.18 eFigure 2; joi190122supp2_prod.pdf — p.19 eFigure 3; joi190122supp2_prod.pdf — supplement p.11 eTable 6; jama_de_boer_2019_oi_190122.pdf — main p.3 ACR progression definition; jama_de_boer_2019_oi_190122.pdf — p.4 threefold increase narrative; joi190122supp1_prod.pdf — p.11 slower-progression hypotheses; joi190122supp1_prod.pdf — p.17 ACR definition.</t>
-        </is>
-      </c>
-      <c r="D19" s="21" t="n"/>
-      <c r="E19" s="21" t="inlineStr">
-        <is>
-          <t>statistical_results</t>
-        </is>
-      </c>
-      <c r="F19" s="21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="G19" s="24">
-        <f>IFERROR(IF(LEN(TRIM(CLEAN(SUBSTITUTE(Setup!$B$2,CHAR(160)," "))))=0,"CHECK REVIEWER ID",IF(OR(A19="",COUNTIF($A$2:$A$19,A19)&lt;&gt;1,LEFT(A19,LEN("2019::jama.2019.17380::"))&lt;&gt;"2019::jama.2019.17380::"),"CHECK KEY",IF(OR(AND(NOT(AND(D19="retain",E19="statistical_results")),H19&lt;&gt;"",NOT(EXACT(H19,"not_applicable"))),AND(NOT(AND(D19="retain",E19="statistical_results")),I19&lt;&gt;"",NOT(EXACT(I19,"not_applicable"))),AND(NOT(AND(D19="retain",E19="statistical_results")),J19&lt;&gt;"",NOT(EXACT(J19,"not_applicable"))),AND(NOT(AND(D19="retain",OR(E19="report_internal_inconsistency",E19="plan_material"))),K19&lt;&gt;"",NOT(EXACT(K19,"not_applicable"))),AND(NOT(AND(D19="retain",E19="protocol_report")),L19&lt;&gt;"",NOT(EXACT(L19,"not_applicable")))),"CLEAR INACTIVE VALUES",IF(OR(NOT(OR(EXACT(D19,"retain"),EXACT(D19,"exclude"),EXACT(D19,"discuss"))),NOT(OR(EXACT(E19,"statistical_results"),EXACT(E19,"report_internal_inconsistency"),EXACT(E19,"plan_material"),EXACT(E19,"protocol_report"))),AND(AND(D19="retain",E19="statistical_results"),NOT(OR(EXACT(H19,"confirmed_issue"),EXACT(H19,"probable_issue"),EXACT(H19,"not_issue"),EXACT(H19,"indeterminate")))),AND(AND(D19="retain",E19="statistical_results"),NOT(OR(EXACT(I19,"substantive"),EXACT(I19,"minor_presentation"),EXACT(I19,"indeterminate")))),AND(AND(D19="retain",E19="statistical_results"),J19&lt;&gt;"",NOT(OR(EXACT(J19,"direct"),EXACT(J19,"possible"),EXACT(J19,"unlikely"),EXACT(J19,"unknown")))),AND(AND(D19="retain",OR(E19="report_internal_inconsistency",E19="plan_material")),NOT(OR(EXACT(K19,"substantive_inconsistency"),EXACT(K19,"minor_presentation"),EXACT(K19,"non_inconsistency"),EXACT(K19,"indeterminate")))),AND(AND(D19="retain",E19="protocol_report"),L19&lt;&gt;"",NOT(OR(EXACT(L19,"substantive_difference"),EXACT(L19,"minor_presentation"),EXACT(L19,"version_timing"),EXACT(L19,"non_inconsistency"),EXACT(L19,"indeterminate"))))),"CHECK FIELDS",IF(AND(F19&lt;&gt;"",NOT(OR(EXACT(F19,"no"),EXACT(F19,"primary_done")))),"CHECK COMPLETE",IF(EXACT(F19,"primary_done"),"PRIMARY READY","PRIMARY DRAFT")))))),"CHECK INPUT / KEY")</f>
-        <v/>
-      </c>
-      <c r="H19" s="21">
-        <f>IF(AND(OR(D19="retain",D19=""),E19="statistical_results"),"","not_applicable")</f>
-        <v/>
-      </c>
-      <c r="I19" s="21">
-        <f>IF(AND(OR(D19="retain",D19=""),E19="statistical_results"),"","not_applicable")</f>
-        <v/>
-      </c>
-      <c r="J19" s="22">
-        <f>IF(AND(OR(D19="retain",D19=""),E19="statistical_results"),"","not_applicable")</f>
-        <v/>
-      </c>
-      <c r="K19" s="21">
-        <f>IF(AND(OR(D19="retain",D19=""),OR(E19="report_internal_inconsistency",E19="plan_material")),"","not_applicable")</f>
-        <v/>
-      </c>
-      <c r="L19" s="22">
-        <f>IF(AND(OR(D19="retain",D19=""),E19="protocol_report"),"","not_applicable")</f>
-        <v/>
-      </c>
-      <c r="M19" s="24" t="n"/>
-      <c r="N19" s="23" t="n"/>
-      <c r="O19" s="23" t="n"/>
-      <c r="P19" s="23" t="n"/>
-      <c r="Q19" s="23" t="n"/>
-      <c r="R19" s="22" t="n"/>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:R19"/>
-  <conditionalFormatting sqref="H2:H19">
-    <cfRule type="expression" priority="8" dxfId="70">
-      <formula>NOT(AND(OR($D2="retain",$D2=""),$E2="statistical_results"))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I19">
-    <cfRule type="expression" priority="9" dxfId="70">
-      <formula>NOT(AND(OR($D2="retain",$D2=""),$E2="statistical_results"))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J19">
-    <cfRule type="expression" priority="10" dxfId="70">
-      <formula>NOT(AND(OR($D2="retain",$D2=""),$E2="statistical_results"))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K19">
-    <cfRule type="expression" priority="11" dxfId="70">
-      <formula>NOT(AND(OR($D2="retain",$D2=""),OR($E2="report_internal_inconsistency",$E2="plan_material")))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L19">
-    <cfRule type="expression" priority="12" dxfId="70">
-      <formula>NOT(AND(OR($D2="retain",$D2=""),$E2="protocol_report"))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G19">
-    <cfRule type="expression" priority="13" dxfId="71">
-      <formula>G2&lt;&gt;"PRIMARY READY"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <dataValidations count="8">
-    <dataValidation sqref="D2:D19" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Use a listed option" error="Choose an option; G also checks pasted entries." type="list" errorStyle="stop">
-      <formula1>"retain,exclude,discuss"</formula1>
-    </dataValidation>
-    <dataValidation sqref="E2:E19" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Use a listed option" error="Choose an option; G also checks pasted entries." type="list" errorStyle="stop">
-      <formula1>"statistical_results,report_internal_inconsistency,plan_material,protocol_report"</formula1>
-    </dataValidation>
-    <dataValidation sqref="F2:F19" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Use a listed option" error="Choose an option; G also checks pasted entries." type="list" errorStyle="stop">
-      <formula1>"no,primary_done"</formula1>
-    </dataValidation>
-    <dataValidation sqref="H2:H19" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Use a listed option" error="Choose an option; G also checks pasted entries." type="list" errorStyle="stop">
-      <formula1>"confirmed_issue,probable_issue,not_issue,indeterminate,not_applicable"</formula1>
-    </dataValidation>
-    <dataValidation sqref="I2:I19" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Use a listed option" error="Choose an option; G also checks pasted entries." type="list" errorStyle="stop">
-      <formula1>"substantive,minor_presentation,indeterminate,not_applicable"</formula1>
-    </dataValidation>
-    <dataValidation sqref="J2:J19" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Use a listed option" error="Choose an option; G also checks pasted entries." type="list" errorStyle="stop">
-      <formula1>"direct,possible,unlikely,unknown,not_applicable"</formula1>
-    </dataValidation>
-    <dataValidation sqref="K2:K19" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Use a listed option" error="Choose an option; G also checks pasted entries." type="list" errorStyle="stop">
-      <formula1>"substantive_inconsistency,minor_presentation,non_inconsistency,indeterminate,not_applicable"</formula1>
-    </dataValidation>
-    <dataValidation sqref="L2:L19" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Use a listed option" error="Choose an option; G also checks pasted entries." type="list" errorStyle="stop">
-      <formula1>"substantive_difference,minor_presentation,version_timing,non_inconsistency,indeterminate,not_applicable"</formula1>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:R8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -3049,7 +1840,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3270,7 +2061,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4187,7 +2978,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5395,7 +4186,7 @@
         </is>
       </c>
       <c r="B3" s="17" t="n">
-        <v>87</v>
+        <v>79</v>
       </c>
     </row>
     <row r="4" ht="55" customFormat="1" customHeight="1" s="14">
@@ -5405,7 +4196,7 @@
         </is>
       </c>
       <c r="B4" s="16">
-        <f>COUNTIF('C_jama.2019.0556'!$G$2:$G$12,"PRIMARY READY")+COUNTIF('C_jama.2019.10517'!$G$2:$G$6,"PRIMARY READY")+COUNTIF('C_jama.2019.12618'!$G$2:$G$11,"PRIMARY READY")+COUNTIF('C_jama.2019.14231'!$G$2:$G$9,"PRIMARY READY")+COUNTIF('C_jama.2019.14630'!$G$2:$G$10,"PRIMARY READY")+COUNTIF('C_jama.2019.14901'!$G$2:$G$6,"PRIMARY READY")+COUNTIF('C_jama.2019.17380'!$G$2:$G$19,"PRIMARY READY")+COUNTIF('C_jama.2019.2210'!$G$2:$G$8,"PRIMARY READY")+COUNTIF('C_jama.2019.4755'!$G$2:$G$2,"PRIMARY READY")+COUNTIF('C_jama.2019.7505'!$G$2:$G$14,"PRIMARY READY")</f>
+        <f>COUNTIF('C_jama.2019.0556'!$G$2:$G$12,"PRIMARY READY")+COUNTIF('C_jama.2019.10517'!$G$2:$G$6,"PRIMARY READY")+COUNTIF('C_jama.2019.12618'!$G$2:$G$11,"PRIMARY READY")+COUNTIF('C_jama.2019.14630'!$G$2:$G$10,"PRIMARY READY")+COUNTIF('C_jama.2019.14901'!$G$2:$G$6,"PRIMARY READY")+COUNTIF('C_jama.2019.17380'!$G$2:$G$19,"PRIMARY READY")+COUNTIF('C_jama.2019.2210'!$G$2:$G$8,"PRIMARY READY")+COUNTIF('C_jama.2019.4755'!$G$2:$G$2,"PRIMARY READY")+COUNTIF('C_jama.2019.7505'!$G$2:$G$14,"PRIMARY READY")</f>
         <v/>
       </c>
     </row>
@@ -5416,7 +4207,7 @@
         </is>
       </c>
       <c r="B5" s="17">
-        <f>COUNTIF('C_jama.2019.0556'!$D$2:$D$12,"discuss")+COUNTIF('C_jama.2019.10517'!$D$2:$D$6,"discuss")+COUNTIF('C_jama.2019.12618'!$D$2:$D$11,"discuss")+COUNTIF('C_jama.2019.14231'!$D$2:$D$9,"discuss")+COUNTIF('C_jama.2019.14630'!$D$2:$D$10,"discuss")+COUNTIF('C_jama.2019.14901'!$D$2:$D$6,"discuss")+COUNTIF('C_jama.2019.17380'!$D$2:$D$19,"discuss")+COUNTIF('C_jama.2019.2210'!$D$2:$D$8,"discuss")+COUNTIF('C_jama.2019.4755'!$D$2:$D$2,"discuss")+COUNTIF('C_jama.2019.7505'!$D$2:$D$14,"discuss")</f>
+        <f>COUNTIF('C_jama.2019.0556'!$D$2:$D$12,"discuss")+COUNTIF('C_jama.2019.10517'!$D$2:$D$6,"discuss")+COUNTIF('C_jama.2019.12618'!$D$2:$D$11,"discuss")+COUNTIF('C_jama.2019.14630'!$D$2:$D$10,"discuss")+COUNTIF('C_jama.2019.14901'!$D$2:$D$6,"discuss")+COUNTIF('C_jama.2019.17380'!$D$2:$D$19,"discuss")+COUNTIF('C_jama.2019.2210'!$D$2:$D$8,"discuss")+COUNTIF('C_jama.2019.4755'!$D$2:$D$2,"discuss")+COUNTIF('C_jama.2019.7505'!$D$2:$D$14,"discuss")</f>
         <v/>
       </c>
     </row>
@@ -5477,7 +4268,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" style="14" min="1" max="1"/>
@@ -5550,108 +4341,94 @@
     <row r="5" ht="36" customFormat="1" customHeight="1" s="14">
       <c r="A5" s="17" t="inlineStr">
         <is>
-          <t>jama.2019.14231</t>
+          <t>jama.2019.14630</t>
         </is>
       </c>
       <c r="B5" s="17" t="inlineStr">
         <is>
-          <t>C_jama.2019.14231</t>
+          <t>C_jama.2019.14630</t>
         </is>
       </c>
       <c r="C5" s="17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" ht="36" customFormat="1" customHeight="1" s="14">
       <c r="A6" s="16" t="inlineStr">
         <is>
-          <t>jama.2019.14630</t>
+          <t>jama.2019.14901</t>
         </is>
       </c>
       <c r="B6" s="16" t="inlineStr">
         <is>
-          <t>C_jama.2019.14630</t>
+          <t>C_jama.2019.14901</t>
         </is>
       </c>
       <c r="C6" s="16" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" ht="36" customFormat="1" customHeight="1" s="14">
       <c r="A7" s="17" t="inlineStr">
         <is>
-          <t>jama.2019.14901</t>
+          <t>jama.2019.17380</t>
         </is>
       </c>
       <c r="B7" s="17" t="inlineStr">
         <is>
-          <t>C_jama.2019.14901</t>
+          <t>C_jama.2019.17380</t>
         </is>
       </c>
       <c r="C7" s="17" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
     </row>
     <row r="8" ht="36" customFormat="1" customHeight="1" s="14">
       <c r="A8" s="16" t="inlineStr">
         <is>
-          <t>jama.2019.17380</t>
+          <t>jama.2019.2210</t>
         </is>
       </c>
       <c r="B8" s="16" t="inlineStr">
         <is>
-          <t>C_jama.2019.17380</t>
+          <t>C_jama.2019.2210</t>
         </is>
       </c>
       <c r="C8" s="16" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9" ht="36" customFormat="1" customHeight="1" s="14">
       <c r="A9" s="17" t="inlineStr">
         <is>
-          <t>jama.2019.2210</t>
+          <t>jama.2019.4755</t>
         </is>
       </c>
       <c r="B9" s="17" t="inlineStr">
         <is>
-          <t>C_jama.2019.2210</t>
+          <t>C_jama.2019.4755</t>
         </is>
       </c>
       <c r="C9" s="17" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" ht="36" customFormat="1" customHeight="1" s="14">
       <c r="A10" s="16" t="inlineStr">
         <is>
-          <t>jama.2019.4755</t>
+          <t>jama.2019.7505</t>
         </is>
       </c>
       <c r="B10" s="16" t="inlineStr">
         <is>
-          <t>C_jama.2019.4755</t>
+          <t>C_jama.2019.7505</t>
         </is>
       </c>
       <c r="C10" s="16" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" ht="36" customFormat="1" customHeight="1" s="14">
-      <c r="A11" s="17" t="inlineStr">
-        <is>
-          <t>jama.2019.7505</t>
-        </is>
-      </c>
-      <c r="B11" s="17" t="inlineStr">
-        <is>
-          <t>C_jama.2019.7505</t>
-        </is>
-      </c>
-      <c r="C11" s="17" t="n">
         <v>13</v>
       </c>
     </row>
+    <row r="11" ht="36" customFormat="1" customHeight="1" s="14"/>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="B2" location="'C_jama.2017.21906'!A1"/>
@@ -5663,7 +4440,6 @@
     <hyperlink ref="B8" location="'C_jama.2018.18020'!A1"/>
     <hyperlink ref="B9" location="'C_jama.2018.6496'!A1"/>
     <hyperlink ref="B10" location="'C_jama.2018.8802'!A1"/>
-    <hyperlink ref="B11" location="'C_jama.2018.9128'!A1"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7672,633 +6448,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R9"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="22" customWidth="1" style="14" min="1" max="1"/>
-    <col width="28" customWidth="1" style="14" min="2" max="2"/>
-    <col width="22" customWidth="1" style="14" min="3" max="3"/>
-    <col width="20" customWidth="1" style="14" min="4" max="4"/>
-    <col width="35" customWidth="1" style="14" min="5" max="5"/>
-    <col width="17" customWidth="1" style="14" min="6" max="6"/>
-    <col width="29" customWidth="1" style="14" min="7" max="7"/>
-    <col width="28" customWidth="1" style="14" min="8" max="8"/>
-    <col width="20" customWidth="1" style="14" min="9" max="9"/>
-    <col width="20" customWidth="1" style="14" min="10" max="10"/>
-    <col width="34" customWidth="1" style="14" min="11" max="11"/>
-    <col width="26" customWidth="1" style="14" min="12" max="12"/>
-    <col hidden="1" width="3" customWidth="1" style="14" min="13" max="13"/>
-    <col hidden="1" width="3" customWidth="1" style="14" min="14" max="14"/>
-    <col hidden="1" width="3" customWidth="1" style="14" min="15" max="15"/>
-    <col hidden="1" width="3" customWidth="1" style="14" min="16" max="16"/>
-    <col hidden="1" width="3" customWidth="1" style="14" min="17" max="17"/>
-    <col width="32" customWidth="1" style="14" min="18" max="18"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="70" customFormat="1" customHeight="1" s="14">
-      <c r="A1" s="19" t="inlineStr">
-        <is>
-          <t>Candidate key</t>
-        </is>
-      </c>
-      <c r="B1" s="19" t="inlineStr">
-        <is>
-          <t>Candidate title</t>
-        </is>
-      </c>
-      <c r="C1" s="19" t="inlineStr">
-        <is>
-          <t>Source location</t>
-        </is>
-      </c>
-      <c r="D1" s="19" t="inlineStr">
-        <is>
-          <t>Disposition</t>
-        </is>
-      </c>
-      <c r="E1" s="19" t="inlineStr">
-        <is>
-          <t>Review domain (AI suggestion; editable)</t>
-        </is>
-      </c>
-      <c r="F1" s="19" t="inlineStr">
-        <is>
-          <t>Complete</t>
-        </is>
-      </c>
-      <c r="G1" s="19" t="inlineStr">
-        <is>
-          <t>Validation hint</t>
-        </is>
-      </c>
-      <c r="H1" s="19" t="inlineStr">
-        <is>
-          <t>Statistical_or_numerical issue</t>
-        </is>
-      </c>
-      <c r="I1" s="19" t="inlineStr">
-        <is>
-          <t>Substantiveness</t>
-        </is>
-      </c>
-      <c r="J1" s="19" t="inlineStr">
-        <is>
-          <t>Downstream impact</t>
-        </is>
-      </c>
-      <c r="K1" s="19" t="inlineStr">
-        <is>
-          <t>Report-internal or planning-material inconsistency</t>
-        </is>
-      </c>
-      <c r="L1" s="19" t="inlineStr">
-        <is>
-          <t>Protocol interpretation</t>
-        </is>
-      </c>
-      <c r="M1" s="19" t="n"/>
-      <c r="N1" s="19" t="n"/>
-      <c r="O1" s="19" t="n"/>
-      <c r="P1" s="19" t="n"/>
-      <c r="Q1" s="19" t="n"/>
-      <c r="R1" s="19" t="inlineStr">
-        <is>
-          <t>Notes (optional)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="92" customFormat="1" customHeight="1" s="14">
-      <c r="A2" s="20" t="inlineStr">
-        <is>
-          <t>2019::jama.2019.14231::C001</t>
-        </is>
-      </c>
-      <c r="B2" s="20" t="inlineStr">
-        <is>
-          <t>Primary matching allocation differs between plan and report</t>
-        </is>
-      </c>
-      <c r="C2" s="20" t="inlineStr">
-        <is>
-          <t>PLAN joi190103supp2_prod.pdf — p3, Matching Process, joi190103supp2_prod.pdf — p6, sensitivity ratios and joi190103supp2_prod.pdf — p7, amendment; REPORT jama_aminian_2019_oi_190103.pdf — p1, abstract, jama_aminian_2019_oi_190103.pdf — p3, Figure 1 and matching caption and jama_aminian_2019_oi_190103.pdf — p4, statistical analysis.</t>
-        </is>
-      </c>
-      <c r="D2" s="21" t="n"/>
-      <c r="E2" s="21" t="inlineStr">
-        <is>
-          <t>protocol_report</t>
-        </is>
-      </c>
-      <c r="F2" s="21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="G2" s="20">
-        <f>IFERROR(IF(LEN(TRIM(CLEAN(SUBSTITUTE(Setup!$B$2,CHAR(160)," "))))=0,"CHECK REVIEWER ID",IF(OR(A2="",COUNTIF($A$2:$A$9,A2)&lt;&gt;1,LEFT(A2,LEN("2019::jama.2019.14231::"))&lt;&gt;"2019::jama.2019.14231::"),"CHECK KEY",IF(OR(AND(NOT(AND(D2="retain",E2="statistical_results")),H2&lt;&gt;"",NOT(EXACT(H2,"not_applicable"))),AND(NOT(AND(D2="retain",E2="statistical_results")),I2&lt;&gt;"",NOT(EXACT(I2,"not_applicable"))),AND(NOT(AND(D2="retain",E2="statistical_results")),J2&lt;&gt;"",NOT(EXACT(J2,"not_applicable"))),AND(NOT(AND(D2="retain",OR(E2="report_internal_inconsistency",E2="plan_material"))),K2&lt;&gt;"",NOT(EXACT(K2,"not_applicable"))),AND(NOT(AND(D2="retain",E2="protocol_report")),L2&lt;&gt;"",NOT(EXACT(L2,"not_applicable")))),"CLEAR INACTIVE VALUES",IF(OR(NOT(OR(EXACT(D2,"retain"),EXACT(D2,"exclude"),EXACT(D2,"discuss"))),NOT(OR(EXACT(E2,"statistical_results"),EXACT(E2,"report_internal_inconsistency"),EXACT(E2,"plan_material"),EXACT(E2,"protocol_report"))),AND(AND(D2="retain",E2="statistical_results"),NOT(OR(EXACT(H2,"confirmed_issue"),EXACT(H2,"probable_issue"),EXACT(H2,"not_issue"),EXACT(H2,"indeterminate")))),AND(AND(D2="retain",E2="statistical_results"),NOT(OR(EXACT(I2,"substantive"),EXACT(I2,"minor_presentation"),EXACT(I2,"indeterminate")))),AND(AND(D2="retain",E2="statistical_results"),J2&lt;&gt;"",NOT(OR(EXACT(J2,"direct"),EXACT(J2,"possible"),EXACT(J2,"unlikely"),EXACT(J2,"unknown")))),AND(AND(D2="retain",OR(E2="report_internal_inconsistency",E2="plan_material")),NOT(OR(EXACT(K2,"substantive_inconsistency"),EXACT(K2,"minor_presentation"),EXACT(K2,"non_inconsistency"),EXACT(K2,"indeterminate")))),AND(AND(D2="retain",E2="protocol_report"),L2&lt;&gt;"",NOT(OR(EXACT(L2,"substantive_difference"),EXACT(L2,"minor_presentation"),EXACT(L2,"version_timing"),EXACT(L2,"non_inconsistency"),EXACT(L2,"indeterminate"))))),"CHECK FIELDS",IF(AND(F2&lt;&gt;"",NOT(OR(EXACT(F2,"no"),EXACT(F2,"primary_done")))),"CHECK COMPLETE",IF(EXACT(F2,"primary_done"),"PRIMARY READY","PRIMARY DRAFT")))))),"CHECK INPUT / KEY")</f>
-        <v/>
-      </c>
-      <c r="H2" s="21">
-        <f>IF(AND(OR(D2="retain",D2=""),E2="statistical_results"),"","not_applicable")</f>
-        <v/>
-      </c>
-      <c r="I2" s="21">
-        <f>IF(AND(OR(D2="retain",D2=""),E2="statistical_results"),"","not_applicable")</f>
-        <v/>
-      </c>
-      <c r="J2" s="22">
-        <f>IF(AND(OR(D2="retain",D2=""),E2="statistical_results"),"","not_applicable")</f>
-        <v/>
-      </c>
-      <c r="K2" s="21">
-        <f>IF(AND(OR(D2="retain",D2=""),OR(E2="report_internal_inconsistency",E2="plan_material")),"","not_applicable")</f>
-        <v/>
-      </c>
-      <c r="L2" s="22">
-        <f>IF(AND(OR(D2="retain",D2=""),E2="protocol_report"),"","not_applicable")</f>
-        <v/>
-      </c>
-      <c r="M2" s="20" t="n"/>
-      <c r="N2" s="23" t="n"/>
-      <c r="O2" s="23" t="n"/>
-      <c r="P2" s="23" t="n"/>
-      <c r="Q2" s="23" t="n"/>
-      <c r="R2" s="22" t="n"/>
-    </row>
-    <row r="3" ht="92" customFormat="1" customHeight="1" s="14">
-      <c r="A3" s="24" t="inlineStr">
-        <is>
-          <t>2019::jama.2019.14231::C002</t>
-        </is>
-      </c>
-      <c r="B3" s="24" t="inlineStr">
-        <is>
-          <t>Five absolute risk differences do not reproduce displayed risk subtraction</t>
-        </is>
-      </c>
-      <c r="C3" s="24" t="inlineStr">
-        <is>
-          <t>Each affected row is in jama_aminian_2019_oi_190103.pdf — p7, Table 2: jama_aminian_2019_oi_190103.pdf — heart failure, jama_aminian_2019_oi_190103.pdf — coronary artery disease, jama_aminian_2019_oi_190103.pdf — cerebrovascular disease, jama_aminian_2019_oi_190103.pdf — nephropathy and jama_aminian_2019_oi_190103.pdf — atrial fibrillation, comparing group-risk columns, difference column and footnote a. jama_aminian_2019_oi_190103.pdf — Main p4 describes methods; joi190103supp1_prod.pdf — p7, eTable 5 corroborates every group risk.</t>
-        </is>
-      </c>
-      <c r="D3" s="21" t="n"/>
-      <c r="E3" s="21" t="inlineStr">
-        <is>
-          <t>statistical_results</t>
-        </is>
-      </c>
-      <c r="F3" s="21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="G3" s="24">
-        <f>IFERROR(IF(LEN(TRIM(CLEAN(SUBSTITUTE(Setup!$B$2,CHAR(160)," "))))=0,"CHECK REVIEWER ID",IF(OR(A3="",COUNTIF($A$2:$A$9,A3)&lt;&gt;1,LEFT(A3,LEN("2019::jama.2019.14231::"))&lt;&gt;"2019::jama.2019.14231::"),"CHECK KEY",IF(OR(AND(NOT(AND(D3="retain",E3="statistical_results")),H3&lt;&gt;"",NOT(EXACT(H3,"not_applicable"))),AND(NOT(AND(D3="retain",E3="statistical_results")),I3&lt;&gt;"",NOT(EXACT(I3,"not_applicable"))),AND(NOT(AND(D3="retain",E3="statistical_results")),J3&lt;&gt;"",NOT(EXACT(J3,"not_applicable"))),AND(NOT(AND(D3="retain",OR(E3="report_internal_inconsistency",E3="plan_material"))),K3&lt;&gt;"",NOT(EXACT(K3,"not_applicable"))),AND(NOT(AND(D3="retain",E3="protocol_report")),L3&lt;&gt;"",NOT(EXACT(L3,"not_applicable")))),"CLEAR INACTIVE VALUES",IF(OR(NOT(OR(EXACT(D3,"retain"),EXACT(D3,"exclude"),EXACT(D3,"discuss"))),NOT(OR(EXACT(E3,"statistical_results"),EXACT(E3,"report_internal_inconsistency"),EXACT(E3,"plan_material"),EXACT(E3,"protocol_report"))),AND(AND(D3="retain",E3="statistical_results"),NOT(OR(EXACT(H3,"confirmed_issue"),EXACT(H3,"probable_issue"),EXACT(H3,"not_issue"),EXACT(H3,"indeterminate")))),AND(AND(D3="retain",E3="statistical_results"),NOT(OR(EXACT(I3,"substantive"),EXACT(I3,"minor_presentation"),EXACT(I3,"indeterminate")))),AND(AND(D3="retain",E3="statistical_results"),J3&lt;&gt;"",NOT(OR(EXACT(J3,"direct"),EXACT(J3,"possible"),EXACT(J3,"unlikely"),EXACT(J3,"unknown")))),AND(AND(D3="retain",OR(E3="report_internal_inconsistency",E3="plan_material")),NOT(OR(EXACT(K3,"substantive_inconsistency"),EXACT(K3,"minor_presentation"),EXACT(K3,"non_inconsistency"),EXACT(K3,"indeterminate")))),AND(AND(D3="retain",E3="protocol_report"),L3&lt;&gt;"",NOT(OR(EXACT(L3,"substantive_difference"),EXACT(L3,"minor_presentation"),EXACT(L3,"version_timing"),EXACT(L3,"non_inconsistency"),EXACT(L3,"indeterminate"))))),"CHECK FIELDS",IF(AND(F3&lt;&gt;"",NOT(OR(EXACT(F3,"no"),EXACT(F3,"primary_done")))),"CHECK COMPLETE",IF(EXACT(F3,"primary_done"),"PRIMARY READY","PRIMARY DRAFT")))))),"CHECK INPUT / KEY")</f>
-        <v/>
-      </c>
-      <c r="H3" s="21">
-        <f>IF(AND(OR(D3="retain",D3=""),E3="statistical_results"),"","not_applicable")</f>
-        <v/>
-      </c>
-      <c r="I3" s="21">
-        <f>IF(AND(OR(D3="retain",D3=""),E3="statistical_results"),"","not_applicable")</f>
-        <v/>
-      </c>
-      <c r="J3" s="22">
-        <f>IF(AND(OR(D3="retain",D3=""),E3="statistical_results"),"","not_applicable")</f>
-        <v/>
-      </c>
-      <c r="K3" s="21">
-        <f>IF(AND(OR(D3="retain",D3=""),OR(E3="report_internal_inconsistency",E3="plan_material")),"","not_applicable")</f>
-        <v/>
-      </c>
-      <c r="L3" s="22">
-        <f>IF(AND(OR(D3="retain",D3=""),E3="protocol_report"),"","not_applicable")</f>
-        <v/>
-      </c>
-      <c r="M3" s="24" t="n"/>
-      <c r="N3" s="23" t="n"/>
-      <c r="O3" s="23" t="n"/>
-      <c r="P3" s="23" t="n"/>
-      <c r="Q3" s="23" t="n"/>
-      <c r="R3" s="22" t="n"/>
-    </row>
-    <row r="4" ht="92" customFormat="1" customHeight="1" s="14">
-      <c r="A4" s="20" t="inlineStr">
-        <is>
-          <t>2019::jama.2019.14231::C003</t>
-        </is>
-      </c>
-      <c r="B4" s="20" t="inlineStr">
-        <is>
-          <t>Cerebrovascular interval and treatment test give different null readings</t>
-        </is>
-      </c>
-      <c r="C4" s="20" t="inlineStr">
-        <is>
-          <t>jama_aminian_2019_oi_190103.pdf — p7, Table 2 cerebrovascular row and footnotes a/b, jama_aminian_2019_oi_190103.pdf — p4, inference methods and narrative beginning and jama_aminian_2019_oi_190103.pdf — p6, lower-incidence narrative continuation; corroborating adjusted estimates in jama_aminian_2019_oi_190103.pdf — p8, Figure 3D and joi190103supp1_prod.pdf — p9, eTable 6.</t>
-        </is>
-      </c>
-      <c r="D4" s="21" t="n"/>
-      <c r="E4" s="21" t="inlineStr">
-        <is>
-          <t>statistical_results</t>
-        </is>
-      </c>
-      <c r="F4" s="21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="G4" s="20">
-        <f>IFERROR(IF(LEN(TRIM(CLEAN(SUBSTITUTE(Setup!$B$2,CHAR(160)," "))))=0,"CHECK REVIEWER ID",IF(OR(A4="",COUNTIF($A$2:$A$9,A4)&lt;&gt;1,LEFT(A4,LEN("2019::jama.2019.14231::"))&lt;&gt;"2019::jama.2019.14231::"),"CHECK KEY",IF(OR(AND(NOT(AND(D4="retain",E4="statistical_results")),H4&lt;&gt;"",NOT(EXACT(H4,"not_applicable"))),AND(NOT(AND(D4="retain",E4="statistical_results")),I4&lt;&gt;"",NOT(EXACT(I4,"not_applicable"))),AND(NOT(AND(D4="retain",E4="statistical_results")),J4&lt;&gt;"",NOT(EXACT(J4,"not_applicable"))),AND(NOT(AND(D4="retain",OR(E4="report_internal_inconsistency",E4="plan_material"))),K4&lt;&gt;"",NOT(EXACT(K4,"not_applicable"))),AND(NOT(AND(D4="retain",E4="protocol_report")),L4&lt;&gt;"",NOT(EXACT(L4,"not_applicable")))),"CLEAR INACTIVE VALUES",IF(OR(NOT(OR(EXACT(D4,"retain"),EXACT(D4,"exclude"),EXACT(D4,"discuss"))),NOT(OR(EXACT(E4,"statistical_results"),EXACT(E4,"report_internal_inconsistency"),EXACT(E4,"plan_material"),EXACT(E4,"protocol_report"))),AND(AND(D4="retain",E4="statistical_results"),NOT(OR(EXACT(H4,"confirmed_issue"),EXACT(H4,"probable_issue"),EXACT(H4,"not_issue"),EXACT(H4,"indeterminate")))),AND(AND(D4="retain",E4="statistical_results"),NOT(OR(EXACT(I4,"substantive"),EXACT(I4,"minor_presentation"),EXACT(I4,"indeterminate")))),AND(AND(D4="retain",E4="statistical_results"),J4&lt;&gt;"",NOT(OR(EXACT(J4,"direct"),EXACT(J4,"possible"),EXACT(J4,"unlikely"),EXACT(J4,"unknown")))),AND(AND(D4="retain",OR(E4="report_internal_inconsistency",E4="plan_material")),NOT(OR(EXACT(K4,"substantive_inconsistency"),EXACT(K4,"minor_presentation"),EXACT(K4,"non_inconsistency"),EXACT(K4,"indeterminate")))),AND(AND(D4="retain",E4="protocol_report"),L4&lt;&gt;"",NOT(OR(EXACT(L4,"substantive_difference"),EXACT(L4,"minor_presentation"),EXACT(L4,"version_timing"),EXACT(L4,"non_inconsistency"),EXACT(L4,"indeterminate"))))),"CHECK FIELDS",IF(AND(F4&lt;&gt;"",NOT(OR(EXACT(F4,"no"),EXACT(F4,"primary_done")))),"CHECK COMPLETE",IF(EXACT(F4,"primary_done"),"PRIMARY READY","PRIMARY DRAFT")))))),"CHECK INPUT / KEY")</f>
-        <v/>
-      </c>
-      <c r="H4" s="21">
-        <f>IF(AND(OR(D4="retain",D4=""),E4="statistical_results"),"","not_applicable")</f>
-        <v/>
-      </c>
-      <c r="I4" s="21">
-        <f>IF(AND(OR(D4="retain",D4=""),E4="statistical_results"),"","not_applicable")</f>
-        <v/>
-      </c>
-      <c r="J4" s="22">
-        <f>IF(AND(OR(D4="retain",D4=""),E4="statistical_results"),"","not_applicable")</f>
-        <v/>
-      </c>
-      <c r="K4" s="21">
-        <f>IF(AND(OR(D4="retain",D4=""),OR(E4="report_internal_inconsistency",E4="plan_material")),"","not_applicable")</f>
-        <v/>
-      </c>
-      <c r="L4" s="22">
-        <f>IF(AND(OR(D4="retain",D4=""),E4="protocol_report"),"","not_applicable")</f>
-        <v/>
-      </c>
-      <c r="M4" s="20" t="n"/>
-      <c r="N4" s="23" t="n"/>
-      <c r="O4" s="23" t="n"/>
-      <c r="P4" s="23" t="n"/>
-      <c r="Q4" s="23" t="n"/>
-      <c r="R4" s="22" t="n"/>
-    </row>
-    <row r="5" ht="92" customFormat="1" customHeight="1" s="14">
-      <c r="A5" s="24" t="inlineStr">
-        <is>
-          <t>2019::jama.2019.14231::C004</t>
-        </is>
-      </c>
-      <c r="B5" s="24" t="inlineStr">
-        <is>
-          <t>Coronary diagnosis-position criteria differ between printed plan and report</t>
-        </is>
-      </c>
-      <c r="C5" s="24" t="inlineStr">
-        <is>
-          <t>joi190103supp2_prod.pdf — p4, opening eTable 1 reference, coronary Other criteria and primary endpoint and joi190103supp2_prod.pdf — p7, amendment; joi190103supp1_prod.pdf — p2, eTable 1 coronary row and bold-text footnote; jama_aminian_2019_oi_190103.pdf — p2, endpoint definition and jama_aminian_2019_oi_190103.pdf — p7, Table 2.</t>
-        </is>
-      </c>
-      <c r="D5" s="21" t="n"/>
-      <c r="E5" s="21" t="inlineStr">
-        <is>
-          <t>protocol_report</t>
-        </is>
-      </c>
-      <c r="F5" s="21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="G5" s="24">
-        <f>IFERROR(IF(LEN(TRIM(CLEAN(SUBSTITUTE(Setup!$B$2,CHAR(160)," "))))=0,"CHECK REVIEWER ID",IF(OR(A5="",COUNTIF($A$2:$A$9,A5)&lt;&gt;1,LEFT(A5,LEN("2019::jama.2019.14231::"))&lt;&gt;"2019::jama.2019.14231::"),"CHECK KEY",IF(OR(AND(NOT(AND(D5="retain",E5="statistical_results")),H5&lt;&gt;"",NOT(EXACT(H5,"not_applicable"))),AND(NOT(AND(D5="retain",E5="statistical_results")),I5&lt;&gt;"",NOT(EXACT(I5,"not_applicable"))),AND(NOT(AND(D5="retain",E5="statistical_results")),J5&lt;&gt;"",NOT(EXACT(J5,"not_applicable"))),AND(NOT(AND(D5="retain",OR(E5="report_internal_inconsistency",E5="plan_material"))),K5&lt;&gt;"",NOT(EXACT(K5,"not_applicable"))),AND(NOT(AND(D5="retain",E5="protocol_report")),L5&lt;&gt;"",NOT(EXACT(L5,"not_applicable")))),"CLEAR INACTIVE VALUES",IF(OR(NOT(OR(EXACT(D5,"retain"),EXACT(D5,"exclude"),EXACT(D5,"discuss"))),NOT(OR(EXACT(E5,"statistical_results"),EXACT(E5,"report_internal_inconsistency"),EXACT(E5,"plan_material"),EXACT(E5,"protocol_report"))),AND(AND(D5="retain",E5="statistical_results"),NOT(OR(EXACT(H5,"confirmed_issue"),EXACT(H5,"probable_issue"),EXACT(H5,"not_issue"),EXACT(H5,"indeterminate")))),AND(AND(D5="retain",E5="statistical_results"),NOT(OR(EXACT(I5,"substantive"),EXACT(I5,"minor_presentation"),EXACT(I5,"indeterminate")))),AND(AND(D5="retain",E5="statistical_results"),J5&lt;&gt;"",NOT(OR(EXACT(J5,"direct"),EXACT(J5,"possible"),EXACT(J5,"unlikely"),EXACT(J5,"unknown")))),AND(AND(D5="retain",OR(E5="report_internal_inconsistency",E5="plan_material")),NOT(OR(EXACT(K5,"substantive_inconsistency"),EXACT(K5,"minor_presentation"),EXACT(K5,"non_inconsistency"),EXACT(K5,"indeterminate")))),AND(AND(D5="retain",E5="protocol_report"),L5&lt;&gt;"",NOT(OR(EXACT(L5,"substantive_difference"),EXACT(L5,"minor_presentation"),EXACT(L5,"version_timing"),EXACT(L5,"non_inconsistency"),EXACT(L5,"indeterminate"))))),"CHECK FIELDS",IF(AND(F5&lt;&gt;"",NOT(OR(EXACT(F5,"no"),EXACT(F5,"primary_done")))),"CHECK COMPLETE",IF(EXACT(F5,"primary_done"),"PRIMARY READY","PRIMARY DRAFT")))))),"CHECK INPUT / KEY")</f>
-        <v/>
-      </c>
-      <c r="H5" s="21">
-        <f>IF(AND(OR(D5="retain",D5=""),E5="statistical_results"),"","not_applicable")</f>
-        <v/>
-      </c>
-      <c r="I5" s="21">
-        <f>IF(AND(OR(D5="retain",D5=""),E5="statistical_results"),"","not_applicable")</f>
-        <v/>
-      </c>
-      <c r="J5" s="22">
-        <f>IF(AND(OR(D5="retain",D5=""),E5="statistical_results"),"","not_applicable")</f>
-        <v/>
-      </c>
-      <c r="K5" s="21">
-        <f>IF(AND(OR(D5="retain",D5=""),OR(E5="report_internal_inconsistency",E5="plan_material")),"","not_applicable")</f>
-        <v/>
-      </c>
-      <c r="L5" s="22">
-        <f>IF(AND(OR(D5="retain",D5=""),E5="protocol_report"),"","not_applicable")</f>
-        <v/>
-      </c>
-      <c r="M5" s="24" t="n"/>
-      <c r="N5" s="23" t="n"/>
-      <c r="O5" s="23" t="n"/>
-      <c r="P5" s="23" t="n"/>
-      <c r="Q5" s="23" t="n"/>
-      <c r="R5" s="22" t="n"/>
-    </row>
-    <row r="6" ht="92" customFormat="1" customHeight="1" s="14">
-      <c r="A6" s="20" t="inlineStr">
-        <is>
-          <t>2019::jama.2019.14231::C005</t>
-        </is>
-      </c>
-      <c r="B6" s="20" t="inlineStr">
-        <is>
-          <t>Atrial-fibrillation code criterion differs between printed plan and report</t>
-        </is>
-      </c>
-      <c r="C6" s="20" t="inlineStr">
-        <is>
-          <t>joi190103supp2_prod.pdf — p4, opening eTable 1 reference, AF list and primary endpoint and joi190103supp2_prod.pdf — p7, amendment; joi190103supp1_prod.pdf — p2, eTable 1 AF row; jama_aminian_2019_oi_190103.pdf — p2, endpoint definition and jama_aminian_2019_oi_190103.pdf — p7, Table 2 AF/primary rows.</t>
-        </is>
-      </c>
-      <c r="D6" s="21" t="n"/>
-      <c r="E6" s="21" t="inlineStr">
-        <is>
-          <t>protocol_report</t>
-        </is>
-      </c>
-      <c r="F6" s="21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="G6" s="20">
-        <f>IFERROR(IF(LEN(TRIM(CLEAN(SUBSTITUTE(Setup!$B$2,CHAR(160)," "))))=0,"CHECK REVIEWER ID",IF(OR(A6="",COUNTIF($A$2:$A$9,A6)&lt;&gt;1,LEFT(A6,LEN("2019::jama.2019.14231::"))&lt;&gt;"2019::jama.2019.14231::"),"CHECK KEY",IF(OR(AND(NOT(AND(D6="retain",E6="statistical_results")),H6&lt;&gt;"",NOT(EXACT(H6,"not_applicable"))),AND(NOT(AND(D6="retain",E6="statistical_results")),I6&lt;&gt;"",NOT(EXACT(I6,"not_applicable"))),AND(NOT(AND(D6="retain",E6="statistical_results")),J6&lt;&gt;"",NOT(EXACT(J6,"not_applicable"))),AND(NOT(AND(D6="retain",OR(E6="report_internal_inconsistency",E6="plan_material"))),K6&lt;&gt;"",NOT(EXACT(K6,"not_applicable"))),AND(NOT(AND(D6="retain",E6="protocol_report")),L6&lt;&gt;"",NOT(EXACT(L6,"not_applicable")))),"CLEAR INACTIVE VALUES",IF(OR(NOT(OR(EXACT(D6,"retain"),EXACT(D6,"exclude"),EXACT(D6,"discuss"))),NOT(OR(EXACT(E6,"statistical_results"),EXACT(E6,"report_internal_inconsistency"),EXACT(E6,"plan_material"),EXACT(E6,"protocol_report"))),AND(AND(D6="retain",E6="statistical_results"),NOT(OR(EXACT(H6,"confirmed_issue"),EXACT(H6,"probable_issue"),EXACT(H6,"not_issue"),EXACT(H6,"indeterminate")))),AND(AND(D6="retain",E6="statistical_results"),NOT(OR(EXACT(I6,"substantive"),EXACT(I6,"minor_presentation"),EXACT(I6,"indeterminate")))),AND(AND(D6="retain",E6="statistical_results"),J6&lt;&gt;"",NOT(OR(EXACT(J6,"direct"),EXACT(J6,"possible"),EXACT(J6,"unlikely"),EXACT(J6,"unknown")))),AND(AND(D6="retain",OR(E6="report_internal_inconsistency",E6="plan_material")),NOT(OR(EXACT(K6,"substantive_inconsistency"),EXACT(K6,"minor_presentation"),EXACT(K6,"non_inconsistency"),EXACT(K6,"indeterminate")))),AND(AND(D6="retain",E6="protocol_report"),L6&lt;&gt;"",NOT(OR(EXACT(L6,"substantive_difference"),EXACT(L6,"minor_presentation"),EXACT(L6,"version_timing"),EXACT(L6,"non_inconsistency"),EXACT(L6,"indeterminate"))))),"CHECK FIELDS",IF(AND(F6&lt;&gt;"",NOT(OR(EXACT(F6,"no"),EXACT(F6,"primary_done")))),"CHECK COMPLETE",IF(EXACT(F6,"primary_done"),"PRIMARY READY","PRIMARY DRAFT")))))),"CHECK INPUT / KEY")</f>
-        <v/>
-      </c>
-      <c r="H6" s="21">
-        <f>IF(AND(OR(D6="retain",D6=""),E6="statistical_results"),"","not_applicable")</f>
-        <v/>
-      </c>
-      <c r="I6" s="21">
-        <f>IF(AND(OR(D6="retain",D6=""),E6="statistical_results"),"","not_applicable")</f>
-        <v/>
-      </c>
-      <c r="J6" s="22">
-        <f>IF(AND(OR(D6="retain",D6=""),E6="statistical_results"),"","not_applicable")</f>
-        <v/>
-      </c>
-      <c r="K6" s="21">
-        <f>IF(AND(OR(D6="retain",D6=""),OR(E6="report_internal_inconsistency",E6="plan_material")),"","not_applicable")</f>
-        <v/>
-      </c>
-      <c r="L6" s="22">
-        <f>IF(AND(OR(D6="retain",D6=""),E6="protocol_report"),"","not_applicable")</f>
-        <v/>
-      </c>
-      <c r="M6" s="20" t="n"/>
-      <c r="N6" s="23" t="n"/>
-      <c r="O6" s="23" t="n"/>
-      <c r="P6" s="23" t="n"/>
-      <c r="Q6" s="23" t="n"/>
-      <c r="R6" s="22" t="n"/>
-    </row>
-    <row r="7" ht="92" customFormat="1" customHeight="1" s="14">
-      <c r="A7" s="24" t="inlineStr">
-        <is>
-          <t>2019::jama.2019.14231::C006</t>
-        </is>
-      </c>
-      <c r="B7" s="24" t="inlineStr">
-        <is>
-          <t>Planned multiplicity rule and reported longitudinal intervals differ</t>
-        </is>
-      </c>
-      <c r="C7" s="24" t="inlineStr">
-        <is>
-          <t>joi190103supp2_prod.pdf — p6, weight/HbA1c paragraph and subsequent inference rule and joi190103supp2_prod.pdf — p7, nutritional amendment; joi190103supp1_prod.pdf — p12, eTable 8, all 52 entries, confidence heading and both method/confidence footnotes; jama_aminian_2019_oi_190103.pdf — p4, general inference context.</t>
-        </is>
-      </c>
-      <c r="D7" s="21" t="n"/>
-      <c r="E7" s="21" t="inlineStr">
-        <is>
-          <t>protocol_report</t>
-        </is>
-      </c>
-      <c r="F7" s="21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="G7" s="24">
-        <f>IFERROR(IF(LEN(TRIM(CLEAN(SUBSTITUTE(Setup!$B$2,CHAR(160)," "))))=0,"CHECK REVIEWER ID",IF(OR(A7="",COUNTIF($A$2:$A$9,A7)&lt;&gt;1,LEFT(A7,LEN("2019::jama.2019.14231::"))&lt;&gt;"2019::jama.2019.14231::"),"CHECK KEY",IF(OR(AND(NOT(AND(D7="retain",E7="statistical_results")),H7&lt;&gt;"",NOT(EXACT(H7,"not_applicable"))),AND(NOT(AND(D7="retain",E7="statistical_results")),I7&lt;&gt;"",NOT(EXACT(I7,"not_applicable"))),AND(NOT(AND(D7="retain",E7="statistical_results")),J7&lt;&gt;"",NOT(EXACT(J7,"not_applicable"))),AND(NOT(AND(D7="retain",OR(E7="report_internal_inconsistency",E7="plan_material"))),K7&lt;&gt;"",NOT(EXACT(K7,"not_applicable"))),AND(NOT(AND(D7="retain",E7="protocol_report")),L7&lt;&gt;"",NOT(EXACT(L7,"not_applicable")))),"CLEAR INACTIVE VALUES",IF(OR(NOT(OR(EXACT(D7,"retain"),EXACT(D7,"exclude"),EXACT(D7,"discuss"))),NOT(OR(EXACT(E7,"statistical_results"),EXACT(E7,"report_internal_inconsistency"),EXACT(E7,"plan_material"),EXACT(E7,"protocol_report"))),AND(AND(D7="retain",E7="statistical_results"),NOT(OR(EXACT(H7,"confirmed_issue"),EXACT(H7,"probable_issue"),EXACT(H7,"not_issue"),EXACT(H7,"indeterminate")))),AND(AND(D7="retain",E7="statistical_results"),NOT(OR(EXACT(I7,"substantive"),EXACT(I7,"minor_presentation"),EXACT(I7,"indeterminate")))),AND(AND(D7="retain",E7="statistical_results"),J7&lt;&gt;"",NOT(OR(EXACT(J7,"direct"),EXACT(J7,"possible"),EXACT(J7,"unlikely"),EXACT(J7,"unknown")))),AND(AND(D7="retain",OR(E7="report_internal_inconsistency",E7="plan_material")),NOT(OR(EXACT(K7,"substantive_inconsistency"),EXACT(K7,"minor_presentation"),EXACT(K7,"non_inconsistency"),EXACT(K7,"indeterminate")))),AND(AND(D7="retain",E7="protocol_report"),L7&lt;&gt;"",NOT(OR(EXACT(L7,"substantive_difference"),EXACT(L7,"minor_presentation"),EXACT(L7,"version_timing"),EXACT(L7,"non_inconsistency"),EXACT(L7,"indeterminate"))))),"CHECK FIELDS",IF(AND(F7&lt;&gt;"",NOT(OR(EXACT(F7,"no"),EXACT(F7,"primary_done")))),"CHECK COMPLETE",IF(EXACT(F7,"primary_done"),"PRIMARY READY","PRIMARY DRAFT")))))),"CHECK INPUT / KEY")</f>
-        <v/>
-      </c>
-      <c r="H7" s="21">
-        <f>IF(AND(OR(D7="retain",D7=""),E7="statistical_results"),"","not_applicable")</f>
-        <v/>
-      </c>
-      <c r="I7" s="21">
-        <f>IF(AND(OR(D7="retain",D7=""),E7="statistical_results"),"","not_applicable")</f>
-        <v/>
-      </c>
-      <c r="J7" s="22">
-        <f>IF(AND(OR(D7="retain",D7=""),E7="statistical_results"),"","not_applicable")</f>
-        <v/>
-      </c>
-      <c r="K7" s="21">
-        <f>IF(AND(OR(D7="retain",D7=""),OR(E7="report_internal_inconsistency",E7="plan_material")),"","not_applicable")</f>
-        <v/>
-      </c>
-      <c r="L7" s="22">
-        <f>IF(AND(OR(D7="retain",D7=""),E7="protocol_report"),"","not_applicable")</f>
-        <v/>
-      </c>
-      <c r="M7" s="24" t="n"/>
-      <c r="N7" s="23" t="n"/>
-      <c r="O7" s="23" t="n"/>
-      <c r="P7" s="23" t="n"/>
-      <c r="Q7" s="23" t="n"/>
-      <c r="R7" s="22" t="n"/>
-    </row>
-    <row r="8" ht="92" customFormat="1" customHeight="1" s="14">
-      <c r="A8" s="20" t="inlineStr">
-        <is>
-          <t>2019::jama.2019.14231::C007</t>
-        </is>
-      </c>
-      <c r="B8" s="20" t="inlineStr">
-        <is>
-          <t>Year-5 hemoglobin interval and P value give different null readings</t>
-        </is>
-      </c>
-      <c r="C8" s="20" t="inlineStr">
-        <is>
-          <t>joi190103supp1_prod.pdf — p12, eTable 8 hemoglobin year-5 estimate/interval/P, confidence heading and both footnotes; jama_aminian_2019_oi_190103.pdf — p4, two-sided and spline methods.</t>
-        </is>
-      </c>
-      <c r="D8" s="21" t="n"/>
-      <c r="E8" s="21" t="inlineStr">
-        <is>
-          <t>statistical_results</t>
-        </is>
-      </c>
-      <c r="F8" s="21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="G8" s="20">
-        <f>IFERROR(IF(LEN(TRIM(CLEAN(SUBSTITUTE(Setup!$B$2,CHAR(160)," "))))=0,"CHECK REVIEWER ID",IF(OR(A8="",COUNTIF($A$2:$A$9,A8)&lt;&gt;1,LEFT(A8,LEN("2019::jama.2019.14231::"))&lt;&gt;"2019::jama.2019.14231::"),"CHECK KEY",IF(OR(AND(NOT(AND(D8="retain",E8="statistical_results")),H8&lt;&gt;"",NOT(EXACT(H8,"not_applicable"))),AND(NOT(AND(D8="retain",E8="statistical_results")),I8&lt;&gt;"",NOT(EXACT(I8,"not_applicable"))),AND(NOT(AND(D8="retain",E8="statistical_results")),J8&lt;&gt;"",NOT(EXACT(J8,"not_applicable"))),AND(NOT(AND(D8="retain",OR(E8="report_internal_inconsistency",E8="plan_material"))),K8&lt;&gt;"",NOT(EXACT(K8,"not_applicable"))),AND(NOT(AND(D8="retain",E8="protocol_report")),L8&lt;&gt;"",NOT(EXACT(L8,"not_applicable")))),"CLEAR INACTIVE VALUES",IF(OR(NOT(OR(EXACT(D8,"retain"),EXACT(D8,"exclude"),EXACT(D8,"discuss"))),NOT(OR(EXACT(E8,"statistical_results"),EXACT(E8,"report_internal_inconsistency"),EXACT(E8,"plan_material"),EXACT(E8,"protocol_report"))),AND(AND(D8="retain",E8="statistical_results"),NOT(OR(EXACT(H8,"confirmed_issue"),EXACT(H8,"probable_issue"),EXACT(H8,"not_issue"),EXACT(H8,"indeterminate")))),AND(AND(D8="retain",E8="statistical_results"),NOT(OR(EXACT(I8,"substantive"),EXACT(I8,"minor_presentation"),EXACT(I8,"indeterminate")))),AND(AND(D8="retain",E8="statistical_results"),J8&lt;&gt;"",NOT(OR(EXACT(J8,"direct"),EXACT(J8,"possible"),EXACT(J8,"unlikely"),EXACT(J8,"unknown")))),AND(AND(D8="retain",OR(E8="report_internal_inconsistency",E8="plan_material")),NOT(OR(EXACT(K8,"substantive_inconsistency"),EXACT(K8,"minor_presentation"),EXACT(K8,"non_inconsistency"),EXACT(K8,"indeterminate")))),AND(AND(D8="retain",E8="protocol_report"),L8&lt;&gt;"",NOT(OR(EXACT(L8,"substantive_difference"),EXACT(L8,"minor_presentation"),EXACT(L8,"version_timing"),EXACT(L8,"non_inconsistency"),EXACT(L8,"indeterminate"))))),"CHECK FIELDS",IF(AND(F8&lt;&gt;"",NOT(OR(EXACT(F8,"no"),EXACT(F8,"primary_done")))),"CHECK COMPLETE",IF(EXACT(F8,"primary_done"),"PRIMARY READY","PRIMARY DRAFT")))))),"CHECK INPUT / KEY")</f>
-        <v/>
-      </c>
-      <c r="H8" s="21">
-        <f>IF(AND(OR(D8="retain",D8=""),E8="statistical_results"),"","not_applicable")</f>
-        <v/>
-      </c>
-      <c r="I8" s="21">
-        <f>IF(AND(OR(D8="retain",D8=""),E8="statistical_results"),"","not_applicable")</f>
-        <v/>
-      </c>
-      <c r="J8" s="22">
-        <f>IF(AND(OR(D8="retain",D8=""),E8="statistical_results"),"","not_applicable")</f>
-        <v/>
-      </c>
-      <c r="K8" s="21">
-        <f>IF(AND(OR(D8="retain",D8=""),OR(E8="report_internal_inconsistency",E8="plan_material")),"","not_applicable")</f>
-        <v/>
-      </c>
-      <c r="L8" s="22">
-        <f>IF(AND(OR(D8="retain",D8=""),E8="protocol_report"),"","not_applicable")</f>
-        <v/>
-      </c>
-      <c r="M8" s="20" t="n"/>
-      <c r="N8" s="23" t="n"/>
-      <c r="O8" s="23" t="n"/>
-      <c r="P8" s="23" t="n"/>
-      <c r="Q8" s="23" t="n"/>
-      <c r="R8" s="22" t="n"/>
-    </row>
-    <row r="9" ht="92" customFormat="1" customHeight="1" s="14">
-      <c r="A9" s="24" t="inlineStr">
-        <is>
-          <t>2019::jama.2019.14231::C008</t>
-        </is>
-      </c>
-      <c r="B9" s="24" t="inlineStr">
-        <is>
-          <t>Primary E-values do not reproduce the comparator supported by other rows</t>
-        </is>
-      </c>
-      <c r="C9" s="24" t="inlineStr">
-        <is>
-          <t>joi190103supp1_prod.pdf — p20, eTable 12 primary pair and all seven comparator pairs, joi190103supp1_prod.pdf — p19, E-value definition and repeated primary 2.15/1.92 interpretation and joi190103supp1_prod.pdf — p9, eTable 6 corresponding treatment HR/upper limits; jama_aminian_2019_oi_190103.pdf — p7, Table 2 matching inputs and jama_aminian_2019_oi_190103.pdf — p9, generic robustness discussion. joi190103supp2_prod.pdf — PLAN amendment p7 only corroborates intended eight-outcome E-value scope.</t>
-        </is>
-      </c>
-      <c r="D9" s="21" t="n"/>
-      <c r="E9" s="21" t="inlineStr">
-        <is>
-          <t>statistical_results</t>
-        </is>
-      </c>
-      <c r="F9" s="21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="G9" s="24">
-        <f>IFERROR(IF(LEN(TRIM(CLEAN(SUBSTITUTE(Setup!$B$2,CHAR(160)," "))))=0,"CHECK REVIEWER ID",IF(OR(A9="",COUNTIF($A$2:$A$9,A9)&lt;&gt;1,LEFT(A9,LEN("2019::jama.2019.14231::"))&lt;&gt;"2019::jama.2019.14231::"),"CHECK KEY",IF(OR(AND(NOT(AND(D9="retain",E9="statistical_results")),H9&lt;&gt;"",NOT(EXACT(H9,"not_applicable"))),AND(NOT(AND(D9="retain",E9="statistical_results")),I9&lt;&gt;"",NOT(EXACT(I9,"not_applicable"))),AND(NOT(AND(D9="retain",E9="statistical_results")),J9&lt;&gt;"",NOT(EXACT(J9,"not_applicable"))),AND(NOT(AND(D9="retain",OR(E9="report_internal_inconsistency",E9="plan_material"))),K9&lt;&gt;"",NOT(EXACT(K9,"not_applicable"))),AND(NOT(AND(D9="retain",E9="protocol_report")),L9&lt;&gt;"",NOT(EXACT(L9,"not_applicable")))),"CLEAR INACTIVE VALUES",IF(OR(NOT(OR(EXACT(D9,"retain"),EXACT(D9,"exclude"),EXACT(D9,"discuss"))),NOT(OR(EXACT(E9,"statistical_results"),EXACT(E9,"report_internal_inconsistency"),EXACT(E9,"plan_material"),EXACT(E9,"protocol_report"))),AND(AND(D9="retain",E9="statistical_results"),NOT(OR(EXACT(H9,"confirmed_issue"),EXACT(H9,"probable_issue"),EXACT(H9,"not_issue"),EXACT(H9,"indeterminate")))),AND(AND(D9="retain",E9="statistical_results"),NOT(OR(EXACT(I9,"substantive"),EXACT(I9,"minor_presentation"),EXACT(I9,"indeterminate")))),AND(AND(D9="retain",E9="statistical_results"),J9&lt;&gt;"",NOT(OR(EXACT(J9,"direct"),EXACT(J9,"possible"),EXACT(J9,"unlikely"),EXACT(J9,"unknown")))),AND(AND(D9="retain",OR(E9="report_internal_inconsistency",E9="plan_material")),NOT(OR(EXACT(K9,"substantive_inconsistency"),EXACT(K9,"minor_presentation"),EXACT(K9,"non_inconsistency"),EXACT(K9,"indeterminate")))),AND(AND(D9="retain",E9="protocol_report"),L9&lt;&gt;"",NOT(OR(EXACT(L9,"substantive_difference"),EXACT(L9,"minor_presentation"),EXACT(L9,"version_timing"),EXACT(L9,"non_inconsistency"),EXACT(L9,"indeterminate"))))),"CHECK FIELDS",IF(AND(F9&lt;&gt;"",NOT(OR(EXACT(F9,"no"),EXACT(F9,"primary_done")))),"CHECK COMPLETE",IF(EXACT(F9,"primary_done"),"PRIMARY READY","PRIMARY DRAFT")))))),"CHECK INPUT / KEY")</f>
-        <v/>
-      </c>
-      <c r="H9" s="21">
-        <f>IF(AND(OR(D9="retain",D9=""),E9="statistical_results"),"","not_applicable")</f>
-        <v/>
-      </c>
-      <c r="I9" s="21">
-        <f>IF(AND(OR(D9="retain",D9=""),E9="statistical_results"),"","not_applicable")</f>
-        <v/>
-      </c>
-      <c r="J9" s="22">
-        <f>IF(AND(OR(D9="retain",D9=""),E9="statistical_results"),"","not_applicable")</f>
-        <v/>
-      </c>
-      <c r="K9" s="21">
-        <f>IF(AND(OR(D9="retain",D9=""),OR(E9="report_internal_inconsistency",E9="plan_material")),"","not_applicable")</f>
-        <v/>
-      </c>
-      <c r="L9" s="22">
-        <f>IF(AND(OR(D9="retain",D9=""),E9="protocol_report"),"","not_applicable")</f>
-        <v/>
-      </c>
-      <c r="M9" s="24" t="n"/>
-      <c r="N9" s="23" t="n"/>
-      <c r="O9" s="23" t="n"/>
-      <c r="P9" s="23" t="n"/>
-      <c r="Q9" s="23" t="n"/>
-      <c r="R9" s="22" t="n"/>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:R9"/>
-  <conditionalFormatting sqref="H2:H9">
-    <cfRule type="expression" priority="8" dxfId="70">
-      <formula>NOT(AND(OR($D2="retain",$D2=""),$E2="statistical_results"))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I9">
-    <cfRule type="expression" priority="9" dxfId="70">
-      <formula>NOT(AND(OR($D2="retain",$D2=""),$E2="statistical_results"))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J9">
-    <cfRule type="expression" priority="10" dxfId="70">
-      <formula>NOT(AND(OR($D2="retain",$D2=""),$E2="statistical_results"))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K9">
-    <cfRule type="expression" priority="11" dxfId="70">
-      <formula>NOT(AND(OR($D2="retain",$D2=""),OR($E2="report_internal_inconsistency",$E2="plan_material")))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L9">
-    <cfRule type="expression" priority="12" dxfId="70">
-      <formula>NOT(AND(OR($D2="retain",$D2=""),$E2="protocol_report"))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G9">
-    <cfRule type="expression" priority="13" dxfId="71">
-      <formula>G2&lt;&gt;"PRIMARY READY"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <dataValidations count="8">
-    <dataValidation sqref="D2:D9" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Use a listed option" error="Choose an option; G also checks pasted entries." type="list" errorStyle="stop">
-      <formula1>"retain,exclude,discuss"</formula1>
-    </dataValidation>
-    <dataValidation sqref="E2:E9" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Use a listed option" error="Choose an option; G also checks pasted entries." type="list" errorStyle="stop">
-      <formula1>"statistical_results,report_internal_inconsistency,plan_material,protocol_report"</formula1>
-    </dataValidation>
-    <dataValidation sqref="F2:F9" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Use a listed option" error="Choose an option; G also checks pasted entries." type="list" errorStyle="stop">
-      <formula1>"no,primary_done"</formula1>
-    </dataValidation>
-    <dataValidation sqref="H2:H9" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Use a listed option" error="Choose an option; G also checks pasted entries." type="list" errorStyle="stop">
-      <formula1>"confirmed_issue,probable_issue,not_issue,indeterminate,not_applicable"</formula1>
-    </dataValidation>
-    <dataValidation sqref="I2:I9" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Use a listed option" error="Choose an option; G also checks pasted entries." type="list" errorStyle="stop">
-      <formula1>"substantive,minor_presentation,indeterminate,not_applicable"</formula1>
-    </dataValidation>
-    <dataValidation sqref="J2:J9" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Use a listed option" error="Choose an option; G also checks pasted entries." type="list" errorStyle="stop">
-      <formula1>"direct,possible,unlikely,unknown,not_applicable"</formula1>
-    </dataValidation>
-    <dataValidation sqref="K2:K9" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Use a listed option" error="Choose an option; G also checks pasted entries." type="list" errorStyle="stop">
-      <formula1>"substantive_inconsistency,minor_presentation,non_inconsistency,indeterminate,not_applicable"</formula1>
-    </dataValidation>
-    <dataValidation sqref="L2:L9" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Use a listed option" error="Choose an option; G also checks pasted entries." type="list" errorStyle="stop">
-      <formula1>"substantive_difference,minor_presentation,version_timing,non_inconsistency,indeterminate,not_applicable"</formula1>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:R10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -8978,7 +7127,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -9429,4 +7578,1211 @@
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:R19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" style="14" min="1" max="1"/>
+    <col width="28" customWidth="1" style="14" min="2" max="2"/>
+    <col width="22" customWidth="1" style="14" min="3" max="3"/>
+    <col width="20" customWidth="1" style="14" min="4" max="4"/>
+    <col width="35" customWidth="1" style="14" min="5" max="5"/>
+    <col width="17" customWidth="1" style="14" min="6" max="6"/>
+    <col width="29" customWidth="1" style="14" min="7" max="7"/>
+    <col width="28" customWidth="1" style="14" min="8" max="8"/>
+    <col width="20" customWidth="1" style="14" min="9" max="9"/>
+    <col width="20" customWidth="1" style="14" min="10" max="10"/>
+    <col width="34" customWidth="1" style="14" min="11" max="11"/>
+    <col width="26" customWidth="1" style="14" min="12" max="12"/>
+    <col hidden="1" width="3" customWidth="1" style="14" min="13" max="13"/>
+    <col hidden="1" width="3" customWidth="1" style="14" min="14" max="14"/>
+    <col hidden="1" width="3" customWidth="1" style="14" min="15" max="15"/>
+    <col hidden="1" width="3" customWidth="1" style="14" min="16" max="16"/>
+    <col hidden="1" width="3" customWidth="1" style="14" min="17" max="17"/>
+    <col width="32" customWidth="1" style="14" min="18" max="18"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="70" customFormat="1" customHeight="1" s="14">
+      <c r="A1" s="19" t="inlineStr">
+        <is>
+          <t>Candidate key</t>
+        </is>
+      </c>
+      <c r="B1" s="19" t="inlineStr">
+        <is>
+          <t>Candidate title</t>
+        </is>
+      </c>
+      <c r="C1" s="19" t="inlineStr">
+        <is>
+          <t>Source location</t>
+        </is>
+      </c>
+      <c r="D1" s="19" t="inlineStr">
+        <is>
+          <t>Disposition</t>
+        </is>
+      </c>
+      <c r="E1" s="19" t="inlineStr">
+        <is>
+          <t>Review domain (AI suggestion; editable)</t>
+        </is>
+      </c>
+      <c r="F1" s="19" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+      <c r="G1" s="19" t="inlineStr">
+        <is>
+          <t>Validation hint</t>
+        </is>
+      </c>
+      <c r="H1" s="19" t="inlineStr">
+        <is>
+          <t>Statistical_or_numerical issue</t>
+        </is>
+      </c>
+      <c r="I1" s="19" t="inlineStr">
+        <is>
+          <t>Substantiveness</t>
+        </is>
+      </c>
+      <c r="J1" s="19" t="inlineStr">
+        <is>
+          <t>Downstream impact</t>
+        </is>
+      </c>
+      <c r="K1" s="19" t="inlineStr">
+        <is>
+          <t>Report-internal or planning-material inconsistency</t>
+        </is>
+      </c>
+      <c r="L1" s="19" t="inlineStr">
+        <is>
+          <t>Protocol interpretation</t>
+        </is>
+      </c>
+      <c r="M1" s="19" t="n"/>
+      <c r="N1" s="19" t="n"/>
+      <c r="O1" s="19" t="n"/>
+      <c r="P1" s="19" t="n"/>
+      <c r="Q1" s="19" t="n"/>
+      <c r="R1" s="19" t="inlineStr">
+        <is>
+          <t>Notes (optional)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="92" customFormat="1" customHeight="1" s="14">
+      <c r="A2" s="20" t="inlineStr">
+        <is>
+          <t>2019::jama.2019.17380::C001</t>
+        </is>
+      </c>
+      <c r="B2" s="20" t="inlineStr">
+        <is>
+          <t>Documented outcome-hierarchy and composite amendment</t>
+        </is>
+      </c>
+      <c r="C2" s="20" t="inlineStr">
+        <is>
+          <t>joi190122supp1_prod.pdf — p.11 aims; joi190122supp1_prod.pdf — p.17 VI.b–c; joi190122supp1_prod.pdf — p.19 Table 2; joi190122supp1_prod.pdf — p.31 dates; joi190122supp1_prod.pdf — p.32 §15b; jama_de_boer_2019_oi_190122.pdf — p.1 primary outcome; jama_de_boer_2019_oi_190122.pdf — p.2 Outcomes; jama_de_boer_2019_oi_190122.pdf — p.3 secondary definitions; jama_de_boer_2019_oi_190122.pdf — p.4 composite narrative; jama_de_boer_2019_oi_190122.pdf — p.9 Table 3.</t>
+        </is>
+      </c>
+      <c r="D2" s="21" t="n"/>
+      <c r="E2" s="21" t="inlineStr">
+        <is>
+          <t>protocol_report</t>
+        </is>
+      </c>
+      <c r="F2" s="21" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G2" s="20">
+        <f>IFERROR(IF(LEN(TRIM(CLEAN(SUBSTITUTE(Setup!$B$2,CHAR(160)," "))))=0,"CHECK REVIEWER ID",IF(OR(A2="",COUNTIF($A$2:$A$19,A2)&lt;&gt;1,LEFT(A2,LEN("2019::jama.2019.17380::"))&lt;&gt;"2019::jama.2019.17380::"),"CHECK KEY",IF(OR(AND(NOT(AND(D2="retain",E2="statistical_results")),H2&lt;&gt;"",NOT(EXACT(H2,"not_applicable"))),AND(NOT(AND(D2="retain",E2="statistical_results")),I2&lt;&gt;"",NOT(EXACT(I2,"not_applicable"))),AND(NOT(AND(D2="retain",E2="statistical_results")),J2&lt;&gt;"",NOT(EXACT(J2,"not_applicable"))),AND(NOT(AND(D2="retain",OR(E2="report_internal_inconsistency",E2="plan_material"))),K2&lt;&gt;"",NOT(EXACT(K2,"not_applicable"))),AND(NOT(AND(D2="retain",E2="protocol_report")),L2&lt;&gt;"",NOT(EXACT(L2,"not_applicable")))),"CLEAR INACTIVE VALUES",IF(OR(NOT(OR(EXACT(D2,"retain"),EXACT(D2,"exclude"),EXACT(D2,"discuss"))),NOT(OR(EXACT(E2,"statistical_results"),EXACT(E2,"report_internal_inconsistency"),EXACT(E2,"plan_material"),EXACT(E2,"protocol_report"))),AND(AND(D2="retain",E2="statistical_results"),NOT(OR(EXACT(H2,"confirmed_issue"),EXACT(H2,"probable_issue"),EXACT(H2,"not_issue"),EXACT(H2,"indeterminate")))),AND(AND(D2="retain",E2="statistical_results"),NOT(OR(EXACT(I2,"substantive"),EXACT(I2,"minor_presentation"),EXACT(I2,"indeterminate")))),AND(AND(D2="retain",E2="statistical_results"),J2&lt;&gt;"",NOT(OR(EXACT(J2,"direct"),EXACT(J2,"possible"),EXACT(J2,"unlikely"),EXACT(J2,"unknown")))),AND(AND(D2="retain",OR(E2="report_internal_inconsistency",E2="plan_material")),NOT(OR(EXACT(K2,"substantive_inconsistency"),EXACT(K2,"minor_presentation"),EXACT(K2,"non_inconsistency"),EXACT(K2,"indeterminate")))),AND(AND(D2="retain",E2="protocol_report"),L2&lt;&gt;"",NOT(OR(EXACT(L2,"substantive_difference"),EXACT(L2,"minor_presentation"),EXACT(L2,"version_timing"),EXACT(L2,"non_inconsistency"),EXACT(L2,"indeterminate"))))),"CHECK FIELDS",IF(AND(F2&lt;&gt;"",NOT(OR(EXACT(F2,"no"),EXACT(F2,"primary_done")))),"CHECK COMPLETE",IF(EXACT(F2,"primary_done"),"PRIMARY READY","PRIMARY DRAFT")))))),"CHECK INPUT / KEY")</f>
+        <v/>
+      </c>
+      <c r="H2" s="21">
+        <f>IF(AND(OR(D2="retain",D2=""),E2="statistical_results"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="I2" s="21">
+        <f>IF(AND(OR(D2="retain",D2=""),E2="statistical_results"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="J2" s="22">
+        <f>IF(AND(OR(D2="retain",D2=""),E2="statistical_results"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="K2" s="21">
+        <f>IF(AND(OR(D2="retain",D2=""),OR(E2="report_internal_inconsistency",E2="plan_material")),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="L2" s="22">
+        <f>IF(AND(OR(D2="retain",D2=""),E2="protocol_report"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="M2" s="20" t="n"/>
+      <c r="N2" s="23" t="n"/>
+      <c r="O2" s="23" t="n"/>
+      <c r="P2" s="23" t="n"/>
+      <c r="Q2" s="23" t="n"/>
+      <c r="R2" s="22" t="n"/>
+    </row>
+    <row r="3" ht="92" customFormat="1" customHeight="1" s="14">
+      <c r="A3" s="24" t="inlineStr">
+        <is>
+          <t>2019::jama.2019.17380::C002</t>
+        </is>
+      </c>
+      <c r="B3" s="24" t="inlineStr">
+        <is>
+          <t>Age eligibility thresholds differ between plan and report</t>
+        </is>
+      </c>
+      <c r="C3" s="24" t="inlineStr">
+        <is>
+          <t>joi190122supp1_prod.pdf — p.4 abstract; joi190122supp1_prod.pdf — p.11 aims/population; joi190122supp1_prod.pdf — p.12 Table 1/population; jama_de_boer_2019_oi_190122.pdf — p.2 Study Population; joi190122supp1_prod.pdf — p.31; joi190122supp1_prod.pdf — p.32; joi190122supp1_prod.pdf — p.33.</t>
+        </is>
+      </c>
+      <c r="D3" s="21" t="n"/>
+      <c r="E3" s="21" t="inlineStr">
+        <is>
+          <t>protocol_report</t>
+        </is>
+      </c>
+      <c r="F3" s="21" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G3" s="24">
+        <f>IFERROR(IF(LEN(TRIM(CLEAN(SUBSTITUTE(Setup!$B$2,CHAR(160)," "))))=0,"CHECK REVIEWER ID",IF(OR(A3="",COUNTIF($A$2:$A$19,A3)&lt;&gt;1,LEFT(A3,LEN("2019::jama.2019.17380::"))&lt;&gt;"2019::jama.2019.17380::"),"CHECK KEY",IF(OR(AND(NOT(AND(D3="retain",E3="statistical_results")),H3&lt;&gt;"",NOT(EXACT(H3,"not_applicable"))),AND(NOT(AND(D3="retain",E3="statistical_results")),I3&lt;&gt;"",NOT(EXACT(I3,"not_applicable"))),AND(NOT(AND(D3="retain",E3="statistical_results")),J3&lt;&gt;"",NOT(EXACT(J3,"not_applicable"))),AND(NOT(AND(D3="retain",OR(E3="report_internal_inconsistency",E3="plan_material"))),K3&lt;&gt;"",NOT(EXACT(K3,"not_applicable"))),AND(NOT(AND(D3="retain",E3="protocol_report")),L3&lt;&gt;"",NOT(EXACT(L3,"not_applicable")))),"CLEAR INACTIVE VALUES",IF(OR(NOT(OR(EXACT(D3,"retain"),EXACT(D3,"exclude"),EXACT(D3,"discuss"))),NOT(OR(EXACT(E3,"statistical_results"),EXACT(E3,"report_internal_inconsistency"),EXACT(E3,"plan_material"),EXACT(E3,"protocol_report"))),AND(AND(D3="retain",E3="statistical_results"),NOT(OR(EXACT(H3,"confirmed_issue"),EXACT(H3,"probable_issue"),EXACT(H3,"not_issue"),EXACT(H3,"indeterminate")))),AND(AND(D3="retain",E3="statistical_results"),NOT(OR(EXACT(I3,"substantive"),EXACT(I3,"minor_presentation"),EXACT(I3,"indeterminate")))),AND(AND(D3="retain",E3="statistical_results"),J3&lt;&gt;"",NOT(OR(EXACT(J3,"direct"),EXACT(J3,"possible"),EXACT(J3,"unlikely"),EXACT(J3,"unknown")))),AND(AND(D3="retain",OR(E3="report_internal_inconsistency",E3="plan_material")),NOT(OR(EXACT(K3,"substantive_inconsistency"),EXACT(K3,"minor_presentation"),EXACT(K3,"non_inconsistency"),EXACT(K3,"indeterminate")))),AND(AND(D3="retain",E3="protocol_report"),L3&lt;&gt;"",NOT(OR(EXACT(L3,"substantive_difference"),EXACT(L3,"minor_presentation"),EXACT(L3,"version_timing"),EXACT(L3,"non_inconsistency"),EXACT(L3,"indeterminate"))))),"CHECK FIELDS",IF(AND(F3&lt;&gt;"",NOT(OR(EXACT(F3,"no"),EXACT(F3,"primary_done")))),"CHECK COMPLETE",IF(EXACT(F3,"primary_done"),"PRIMARY READY","PRIMARY DRAFT")))))),"CHECK INPUT / KEY")</f>
+        <v/>
+      </c>
+      <c r="H3" s="21">
+        <f>IF(AND(OR(D3="retain",D3=""),E3="statistical_results"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="I3" s="21">
+        <f>IF(AND(OR(D3="retain",D3=""),E3="statistical_results"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="J3" s="22">
+        <f>IF(AND(OR(D3="retain",D3=""),E3="statistical_results"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="K3" s="21">
+        <f>IF(AND(OR(D3="retain",D3=""),OR(E3="report_internal_inconsistency",E3="plan_material")),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="L3" s="22">
+        <f>IF(AND(OR(D3="retain",D3=""),E3="protocol_report"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="M3" s="24" t="n"/>
+      <c r="N3" s="23" t="n"/>
+      <c r="O3" s="23" t="n"/>
+      <c r="P3" s="23" t="n"/>
+      <c r="Q3" s="23" t="n"/>
+      <c r="R3" s="22" t="n"/>
+    </row>
+    <row r="4" ht="92" customFormat="1" customHeight="1" s="14">
+      <c r="A4" s="20" t="inlineStr">
+        <is>
+          <t>2019::jama.2019.17380::C003</t>
+        </is>
+      </c>
+      <c r="B4" s="20" t="inlineStr">
+        <is>
+          <t>Diabetes exclusion criteria use different insulin rules</t>
+        </is>
+      </c>
+      <c r="C4" s="20" t="inlineStr">
+        <is>
+          <t>joi190122supp1_prod.pdf — p.12 Table 1 and population narrative; joi190122supp1_prod.pdf — p.14 IV.a enrollment algorithm; jama_de_boer_2019_oi_190122.pdf — p.2 Study Population.</t>
+        </is>
+      </c>
+      <c r="D4" s="21" t="n"/>
+      <c r="E4" s="21" t="inlineStr">
+        <is>
+          <t>protocol_report</t>
+        </is>
+      </c>
+      <c r="F4" s="21" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G4" s="20">
+        <f>IFERROR(IF(LEN(TRIM(CLEAN(SUBSTITUTE(Setup!$B$2,CHAR(160)," "))))=0,"CHECK REVIEWER ID",IF(OR(A4="",COUNTIF($A$2:$A$19,A4)&lt;&gt;1,LEFT(A4,LEN("2019::jama.2019.17380::"))&lt;&gt;"2019::jama.2019.17380::"),"CHECK KEY",IF(OR(AND(NOT(AND(D4="retain",E4="statistical_results")),H4&lt;&gt;"",NOT(EXACT(H4,"not_applicable"))),AND(NOT(AND(D4="retain",E4="statistical_results")),I4&lt;&gt;"",NOT(EXACT(I4,"not_applicable"))),AND(NOT(AND(D4="retain",E4="statistical_results")),J4&lt;&gt;"",NOT(EXACT(J4,"not_applicable"))),AND(NOT(AND(D4="retain",OR(E4="report_internal_inconsistency",E4="plan_material"))),K4&lt;&gt;"",NOT(EXACT(K4,"not_applicable"))),AND(NOT(AND(D4="retain",E4="protocol_report")),L4&lt;&gt;"",NOT(EXACT(L4,"not_applicable")))),"CLEAR INACTIVE VALUES",IF(OR(NOT(OR(EXACT(D4,"retain"),EXACT(D4,"exclude"),EXACT(D4,"discuss"))),NOT(OR(EXACT(E4,"statistical_results"),EXACT(E4,"report_internal_inconsistency"),EXACT(E4,"plan_material"),EXACT(E4,"protocol_report"))),AND(AND(D4="retain",E4="statistical_results"),NOT(OR(EXACT(H4,"confirmed_issue"),EXACT(H4,"probable_issue"),EXACT(H4,"not_issue"),EXACT(H4,"indeterminate")))),AND(AND(D4="retain",E4="statistical_results"),NOT(OR(EXACT(I4,"substantive"),EXACT(I4,"minor_presentation"),EXACT(I4,"indeterminate")))),AND(AND(D4="retain",E4="statistical_results"),J4&lt;&gt;"",NOT(OR(EXACT(J4,"direct"),EXACT(J4,"possible"),EXACT(J4,"unlikely"),EXACT(J4,"unknown")))),AND(AND(D4="retain",OR(E4="report_internal_inconsistency",E4="plan_material")),NOT(OR(EXACT(K4,"substantive_inconsistency"),EXACT(K4,"minor_presentation"),EXACT(K4,"non_inconsistency"),EXACT(K4,"indeterminate")))),AND(AND(D4="retain",E4="protocol_report"),L4&lt;&gt;"",NOT(OR(EXACT(L4,"substantive_difference"),EXACT(L4,"minor_presentation"),EXACT(L4,"version_timing"),EXACT(L4,"non_inconsistency"),EXACT(L4,"indeterminate"))))),"CHECK FIELDS",IF(AND(F4&lt;&gt;"",NOT(OR(EXACT(F4,"no"),EXACT(F4,"primary_done")))),"CHECK COMPLETE",IF(EXACT(F4,"primary_done"),"PRIMARY READY","PRIMARY DRAFT")))))),"CHECK INPUT / KEY")</f>
+        <v/>
+      </c>
+      <c r="H4" s="21">
+        <f>IF(AND(OR(D4="retain",D4=""),E4="statistical_results"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="I4" s="21">
+        <f>IF(AND(OR(D4="retain",D4=""),E4="statistical_results"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="J4" s="22">
+        <f>IF(AND(OR(D4="retain",D4=""),E4="statistical_results"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="K4" s="21">
+        <f>IF(AND(OR(D4="retain",D4=""),OR(E4="report_internal_inconsistency",E4="plan_material")),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="L4" s="22">
+        <f>IF(AND(OR(D4="retain",D4=""),E4="protocol_report"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="M4" s="20" t="n"/>
+      <c r="N4" s="23" t="n"/>
+      <c r="O4" s="23" t="n"/>
+      <c r="P4" s="23" t="n"/>
+      <c r="Q4" s="23" t="n"/>
+      <c r="R4" s="22" t="n"/>
+    </row>
+    <row r="5" ht="92" customFormat="1" customHeight="1" s="14">
+      <c r="A5" s="24" t="inlineStr">
+        <is>
+          <t>2019::jama.2019.17380::C004</t>
+        </is>
+      </c>
+      <c r="B5" s="24" t="inlineStr">
+        <is>
+          <t>Randomization stratifiers differ between plan and report</t>
+        </is>
+      </c>
+      <c r="C5" s="24" t="inlineStr">
+        <is>
+          <t>joi190122supp1_prod.pdf — p.14 IV.c Treatment Assignment; jama_de_boer_2019_oi_190122.pdf — p.2 Interventions; joi190122supp1_prod.pdf — pp.31–33 analytic addendum; joi190122supp1_prod.pdf — p.32; joi190122supp1_prod.pdf — p.33.</t>
+        </is>
+      </c>
+      <c r="D5" s="21" t="n"/>
+      <c r="E5" s="21" t="inlineStr">
+        <is>
+          <t>protocol_report</t>
+        </is>
+      </c>
+      <c r="F5" s="21" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G5" s="24">
+        <f>IFERROR(IF(LEN(TRIM(CLEAN(SUBSTITUTE(Setup!$B$2,CHAR(160)," "))))=0,"CHECK REVIEWER ID",IF(OR(A5="",COUNTIF($A$2:$A$19,A5)&lt;&gt;1,LEFT(A5,LEN("2019::jama.2019.17380::"))&lt;&gt;"2019::jama.2019.17380::"),"CHECK KEY",IF(OR(AND(NOT(AND(D5="retain",E5="statistical_results")),H5&lt;&gt;"",NOT(EXACT(H5,"not_applicable"))),AND(NOT(AND(D5="retain",E5="statistical_results")),I5&lt;&gt;"",NOT(EXACT(I5,"not_applicable"))),AND(NOT(AND(D5="retain",E5="statistical_results")),J5&lt;&gt;"",NOT(EXACT(J5,"not_applicable"))),AND(NOT(AND(D5="retain",OR(E5="report_internal_inconsistency",E5="plan_material"))),K5&lt;&gt;"",NOT(EXACT(K5,"not_applicable"))),AND(NOT(AND(D5="retain",E5="protocol_report")),L5&lt;&gt;"",NOT(EXACT(L5,"not_applicable")))),"CLEAR INACTIVE VALUES",IF(OR(NOT(OR(EXACT(D5,"retain"),EXACT(D5,"exclude"),EXACT(D5,"discuss"))),NOT(OR(EXACT(E5,"statistical_results"),EXACT(E5,"report_internal_inconsistency"),EXACT(E5,"plan_material"),EXACT(E5,"protocol_report"))),AND(AND(D5="retain",E5="statistical_results"),NOT(OR(EXACT(H5,"confirmed_issue"),EXACT(H5,"probable_issue"),EXACT(H5,"not_issue"),EXACT(H5,"indeterminate")))),AND(AND(D5="retain",E5="statistical_results"),NOT(OR(EXACT(I5,"substantive"),EXACT(I5,"minor_presentation"),EXACT(I5,"indeterminate")))),AND(AND(D5="retain",E5="statistical_results"),J5&lt;&gt;"",NOT(OR(EXACT(J5,"direct"),EXACT(J5,"possible"),EXACT(J5,"unlikely"),EXACT(J5,"unknown")))),AND(AND(D5="retain",OR(E5="report_internal_inconsistency",E5="plan_material")),NOT(OR(EXACT(K5,"substantive_inconsistency"),EXACT(K5,"minor_presentation"),EXACT(K5,"non_inconsistency"),EXACT(K5,"indeterminate")))),AND(AND(D5="retain",E5="protocol_report"),L5&lt;&gt;"",NOT(OR(EXACT(L5,"substantive_difference"),EXACT(L5,"minor_presentation"),EXACT(L5,"version_timing"),EXACT(L5,"non_inconsistency"),EXACT(L5,"indeterminate"))))),"CHECK FIELDS",IF(AND(F5&lt;&gt;"",NOT(OR(EXACT(F5,"no"),EXACT(F5,"primary_done")))),"CHECK COMPLETE",IF(EXACT(F5,"primary_done"),"PRIMARY READY","PRIMARY DRAFT")))))),"CHECK INPUT / KEY")</f>
+        <v/>
+      </c>
+      <c r="H5" s="21">
+        <f>IF(AND(OR(D5="retain",D5=""),E5="statistical_results"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="I5" s="21">
+        <f>IF(AND(OR(D5="retain",D5=""),E5="statistical_results"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="J5" s="22">
+        <f>IF(AND(OR(D5="retain",D5=""),E5="statistical_results"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="K5" s="21">
+        <f>IF(AND(OR(D5="retain",D5=""),OR(E5="report_internal_inconsistency",E5="plan_material")),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="L5" s="22">
+        <f>IF(AND(OR(D5="retain",D5=""),E5="protocol_report"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="M5" s="24" t="n"/>
+      <c r="N5" s="23" t="n"/>
+      <c r="O5" s="23" t="n"/>
+      <c r="P5" s="23" t="n"/>
+      <c r="Q5" s="23" t="n"/>
+      <c r="R5" s="22" t="n"/>
+    </row>
+    <row r="6" ht="92" customFormat="1" customHeight="1" s="14">
+      <c r="A6" s="20" t="inlineStr">
+        <is>
+          <t>2019::jama.2019.17380::C005</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
+        <is>
+          <t>Primary eGFR estimator identity differs from the supplied plan</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr">
+        <is>
+          <t>joi190122supp1_prod.pdf — p.17 VI.c Equation 1; joi190122supp1_prod.pdf — p.30; joi190122supp1_prod.pdf — p.32 §15b; jama_de_boer_2019_oi_190122.pdf — p.3 Outcomes; jama_de_boer_2019_oi_190122.pdf — p.11; joi190122supp2_prod.pdf — p.2; joi190122supp2_prod.pdf — p.3; joi190122supp2_prod.pdf — p.4.</t>
+        </is>
+      </c>
+      <c r="D6" s="21" t="n"/>
+      <c r="E6" s="21" t="inlineStr">
+        <is>
+          <t>protocol_report</t>
+        </is>
+      </c>
+      <c r="F6" s="21" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G6" s="20">
+        <f>IFERROR(IF(LEN(TRIM(CLEAN(SUBSTITUTE(Setup!$B$2,CHAR(160)," "))))=0,"CHECK REVIEWER ID",IF(OR(A6="",COUNTIF($A$2:$A$19,A6)&lt;&gt;1,LEFT(A6,LEN("2019::jama.2019.17380::"))&lt;&gt;"2019::jama.2019.17380::"),"CHECK KEY",IF(OR(AND(NOT(AND(D6="retain",E6="statistical_results")),H6&lt;&gt;"",NOT(EXACT(H6,"not_applicable"))),AND(NOT(AND(D6="retain",E6="statistical_results")),I6&lt;&gt;"",NOT(EXACT(I6,"not_applicable"))),AND(NOT(AND(D6="retain",E6="statistical_results")),J6&lt;&gt;"",NOT(EXACT(J6,"not_applicable"))),AND(NOT(AND(D6="retain",OR(E6="report_internal_inconsistency",E6="plan_material"))),K6&lt;&gt;"",NOT(EXACT(K6,"not_applicable"))),AND(NOT(AND(D6="retain",E6="protocol_report")),L6&lt;&gt;"",NOT(EXACT(L6,"not_applicable")))),"CLEAR INACTIVE VALUES",IF(OR(NOT(OR(EXACT(D6,"retain"),EXACT(D6,"exclude"),EXACT(D6,"discuss"))),NOT(OR(EXACT(E6,"statistical_results"),EXACT(E6,"report_internal_inconsistency"),EXACT(E6,"plan_material"),EXACT(E6,"protocol_report"))),AND(AND(D6="retain",E6="statistical_results"),NOT(OR(EXACT(H6,"confirmed_issue"),EXACT(H6,"probable_issue"),EXACT(H6,"not_issue"),EXACT(H6,"indeterminate")))),AND(AND(D6="retain",E6="statistical_results"),NOT(OR(EXACT(I6,"substantive"),EXACT(I6,"minor_presentation"),EXACT(I6,"indeterminate")))),AND(AND(D6="retain",E6="statistical_results"),J6&lt;&gt;"",NOT(OR(EXACT(J6,"direct"),EXACT(J6,"possible"),EXACT(J6,"unlikely"),EXACT(J6,"unknown")))),AND(AND(D6="retain",OR(E6="report_internal_inconsistency",E6="plan_material")),NOT(OR(EXACT(K6,"substantive_inconsistency"),EXACT(K6,"minor_presentation"),EXACT(K6,"non_inconsistency"),EXACT(K6,"indeterminate")))),AND(AND(D6="retain",E6="protocol_report"),L6&lt;&gt;"",NOT(OR(EXACT(L6,"substantive_difference"),EXACT(L6,"minor_presentation"),EXACT(L6,"version_timing"),EXACT(L6,"non_inconsistency"),EXACT(L6,"indeterminate"))))),"CHECK FIELDS",IF(AND(F6&lt;&gt;"",NOT(OR(EXACT(F6,"no"),EXACT(F6,"primary_done")))),"CHECK COMPLETE",IF(EXACT(F6,"primary_done"),"PRIMARY READY","PRIMARY DRAFT")))))),"CHECK INPUT / KEY")</f>
+        <v/>
+      </c>
+      <c r="H6" s="21">
+        <f>IF(AND(OR(D6="retain",D6=""),E6="statistical_results"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="I6" s="21">
+        <f>IF(AND(OR(D6="retain",D6=""),E6="statistical_results"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="J6" s="22">
+        <f>IF(AND(OR(D6="retain",D6=""),E6="statistical_results"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="K6" s="21">
+        <f>IF(AND(OR(D6="retain",D6=""),OR(E6="report_internal_inconsistency",E6="plan_material")),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="L6" s="22">
+        <f>IF(AND(OR(D6="retain",D6=""),E6="protocol_report"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="M6" s="20" t="n"/>
+      <c r="N6" s="23" t="n"/>
+      <c r="O6" s="23" t="n"/>
+      <c r="P6" s="23" t="n"/>
+      <c r="Q6" s="23" t="n"/>
+      <c r="R6" s="22" t="n"/>
+    </row>
+    <row r="7" ht="92" customFormat="1" customHeight="1" s="14">
+      <c r="A7" s="24" t="inlineStr">
+        <is>
+          <t>2019::jama.2019.17380::C006</t>
+        </is>
+      </c>
+      <c r="B7" s="24" t="inlineStr">
+        <is>
+          <t>Standalone categorical ACR analysis is called prespecified</t>
+        </is>
+      </c>
+      <c r="C7" s="24" t="inlineStr">
+        <is>
+          <t>joi190122supp1_prod.pdf — p.17 original composite; joi190122supp1_prod.pdf — p.32 §15b/e; joi190122supp1_prod.pdf — p.33 categorical-model continuation; jama_de_boer_2019_oi_190122.pdf — p.3 Outcomes; jama_de_boer_2019_oi_190122.pdf — p.4 secondary narrative; jama_de_boer_2019_oi_190122.pdf — p.9 Table 3 and footnote a.</t>
+        </is>
+      </c>
+      <c r="D7" s="21" t="n"/>
+      <c r="E7" s="21" t="inlineStr">
+        <is>
+          <t>protocol_report</t>
+        </is>
+      </c>
+      <c r="F7" s="21" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G7" s="24">
+        <f>IFERROR(IF(LEN(TRIM(CLEAN(SUBSTITUTE(Setup!$B$2,CHAR(160)," "))))=0,"CHECK REVIEWER ID",IF(OR(A7="",COUNTIF($A$2:$A$19,A7)&lt;&gt;1,LEFT(A7,LEN("2019::jama.2019.17380::"))&lt;&gt;"2019::jama.2019.17380::"),"CHECK KEY",IF(OR(AND(NOT(AND(D7="retain",E7="statistical_results")),H7&lt;&gt;"",NOT(EXACT(H7,"not_applicable"))),AND(NOT(AND(D7="retain",E7="statistical_results")),I7&lt;&gt;"",NOT(EXACT(I7,"not_applicable"))),AND(NOT(AND(D7="retain",E7="statistical_results")),J7&lt;&gt;"",NOT(EXACT(J7,"not_applicable"))),AND(NOT(AND(D7="retain",OR(E7="report_internal_inconsistency",E7="plan_material"))),K7&lt;&gt;"",NOT(EXACT(K7,"not_applicable"))),AND(NOT(AND(D7="retain",E7="protocol_report")),L7&lt;&gt;"",NOT(EXACT(L7,"not_applicable")))),"CLEAR INACTIVE VALUES",IF(OR(NOT(OR(EXACT(D7,"retain"),EXACT(D7,"exclude"),EXACT(D7,"discuss"))),NOT(OR(EXACT(E7,"statistical_results"),EXACT(E7,"report_internal_inconsistency"),EXACT(E7,"plan_material"),EXACT(E7,"protocol_report"))),AND(AND(D7="retain",E7="statistical_results"),NOT(OR(EXACT(H7,"confirmed_issue"),EXACT(H7,"probable_issue"),EXACT(H7,"not_issue"),EXACT(H7,"indeterminate")))),AND(AND(D7="retain",E7="statistical_results"),NOT(OR(EXACT(I7,"substantive"),EXACT(I7,"minor_presentation"),EXACT(I7,"indeterminate")))),AND(AND(D7="retain",E7="statistical_results"),J7&lt;&gt;"",NOT(OR(EXACT(J7,"direct"),EXACT(J7,"possible"),EXACT(J7,"unlikely"),EXACT(J7,"unknown")))),AND(AND(D7="retain",OR(E7="report_internal_inconsistency",E7="plan_material")),NOT(OR(EXACT(K7,"substantive_inconsistency"),EXACT(K7,"minor_presentation"),EXACT(K7,"non_inconsistency"),EXACT(K7,"indeterminate")))),AND(AND(D7="retain",E7="protocol_report"),L7&lt;&gt;"",NOT(OR(EXACT(L7,"substantive_difference"),EXACT(L7,"minor_presentation"),EXACT(L7,"version_timing"),EXACT(L7,"non_inconsistency"),EXACT(L7,"indeterminate"))))),"CHECK FIELDS",IF(AND(F7&lt;&gt;"",NOT(OR(EXACT(F7,"no"),EXACT(F7,"primary_done")))),"CHECK COMPLETE",IF(EXACT(F7,"primary_done"),"PRIMARY READY","PRIMARY DRAFT")))))),"CHECK INPUT / KEY")</f>
+        <v/>
+      </c>
+      <c r="H7" s="21">
+        <f>IF(AND(OR(D7="retain",D7=""),E7="statistical_results"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="I7" s="21">
+        <f>IF(AND(OR(D7="retain",D7=""),E7="statistical_results"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="J7" s="22">
+        <f>IF(AND(OR(D7="retain",D7=""),E7="statistical_results"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="K7" s="21">
+        <f>IF(AND(OR(D7="retain",D7=""),OR(E7="report_internal_inconsistency",E7="plan_material")),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="L7" s="22">
+        <f>IF(AND(OR(D7="retain",D7=""),E7="protocol_report"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="M7" s="24" t="n"/>
+      <c r="N7" s="23" t="n"/>
+      <c r="O7" s="23" t="n"/>
+      <c r="P7" s="23" t="n"/>
+      <c r="Q7" s="23" t="n"/>
+      <c r="R7" s="22" t="n"/>
+    </row>
+    <row r="8" ht="92" customFormat="1" customHeight="1" s="14">
+      <c r="A8" s="20" t="inlineStr">
+        <is>
+          <t>2019::jama.2019.17380::C007</t>
+        </is>
+      </c>
+      <c r="B8" s="20" t="inlineStr">
+        <is>
+          <t>Adherence sensitivity populations use different criteria</t>
+        </is>
+      </c>
+      <c r="C8" s="20" t="inlineStr">
+        <is>
+          <t>joi190122supp1_prod.pdf — p.19 VI.g; joi190122supp1_prod.pdf — p.33 §15g; jama_de_boer_2019_oi_190122.pdf — p.3 Covariates/Data Analysis; jama_de_boer_2019_oi_190122.pdf — p.4 sensitivity narrative; joi190122supp2_prod.pdf — p.6 eTable 1 footnote; joi190122supp2_prod.pdf — p.10 eTable 5 definition; joi190122supp2_prod.pdf — p.13 eTable 8 definition.</t>
+        </is>
+      </c>
+      <c r="D8" s="21" t="n"/>
+      <c r="E8" s="21" t="inlineStr">
+        <is>
+          <t>protocol_report</t>
+        </is>
+      </c>
+      <c r="F8" s="21" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G8" s="20">
+        <f>IFERROR(IF(LEN(TRIM(CLEAN(SUBSTITUTE(Setup!$B$2,CHAR(160)," "))))=0,"CHECK REVIEWER ID",IF(OR(A8="",COUNTIF($A$2:$A$19,A8)&lt;&gt;1,LEFT(A8,LEN("2019::jama.2019.17380::"))&lt;&gt;"2019::jama.2019.17380::"),"CHECK KEY",IF(OR(AND(NOT(AND(D8="retain",E8="statistical_results")),H8&lt;&gt;"",NOT(EXACT(H8,"not_applicable"))),AND(NOT(AND(D8="retain",E8="statistical_results")),I8&lt;&gt;"",NOT(EXACT(I8,"not_applicable"))),AND(NOT(AND(D8="retain",E8="statistical_results")),J8&lt;&gt;"",NOT(EXACT(J8,"not_applicable"))),AND(NOT(AND(D8="retain",OR(E8="report_internal_inconsistency",E8="plan_material"))),K8&lt;&gt;"",NOT(EXACT(K8,"not_applicable"))),AND(NOT(AND(D8="retain",E8="protocol_report")),L8&lt;&gt;"",NOT(EXACT(L8,"not_applicable")))),"CLEAR INACTIVE VALUES",IF(OR(NOT(OR(EXACT(D8,"retain"),EXACT(D8,"exclude"),EXACT(D8,"discuss"))),NOT(OR(EXACT(E8,"statistical_results"),EXACT(E8,"report_internal_inconsistency"),EXACT(E8,"plan_material"),EXACT(E8,"protocol_report"))),AND(AND(D8="retain",E8="statistical_results"),NOT(OR(EXACT(H8,"confirmed_issue"),EXACT(H8,"probable_issue"),EXACT(H8,"not_issue"),EXACT(H8,"indeterminate")))),AND(AND(D8="retain",E8="statistical_results"),NOT(OR(EXACT(I8,"substantive"),EXACT(I8,"minor_presentation"),EXACT(I8,"indeterminate")))),AND(AND(D8="retain",E8="statistical_results"),J8&lt;&gt;"",NOT(OR(EXACT(J8,"direct"),EXACT(J8,"possible"),EXACT(J8,"unlikely"),EXACT(J8,"unknown")))),AND(AND(D8="retain",OR(E8="report_internal_inconsistency",E8="plan_material")),NOT(OR(EXACT(K8,"substantive_inconsistency"),EXACT(K8,"minor_presentation"),EXACT(K8,"non_inconsistency"),EXACT(K8,"indeterminate")))),AND(AND(D8="retain",E8="protocol_report"),L8&lt;&gt;"",NOT(OR(EXACT(L8,"substantive_difference"),EXACT(L8,"minor_presentation"),EXACT(L8,"version_timing"),EXACT(L8,"non_inconsistency"),EXACT(L8,"indeterminate"))))),"CHECK FIELDS",IF(AND(F8&lt;&gt;"",NOT(OR(EXACT(F8,"no"),EXACT(F8,"primary_done")))),"CHECK COMPLETE",IF(EXACT(F8,"primary_done"),"PRIMARY READY","PRIMARY DRAFT")))))),"CHECK INPUT / KEY")</f>
+        <v/>
+      </c>
+      <c r="H8" s="21">
+        <f>IF(AND(OR(D8="retain",D8=""),E8="statistical_results"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="I8" s="21">
+        <f>IF(AND(OR(D8="retain",D8=""),E8="statistical_results"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="J8" s="22">
+        <f>IF(AND(OR(D8="retain",D8=""),E8="statistical_results"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="K8" s="21">
+        <f>IF(AND(OR(D8="retain",D8=""),OR(E8="report_internal_inconsistency",E8="plan_material")),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="L8" s="22">
+        <f>IF(AND(OR(D8="retain",D8=""),E8="protocol_report"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="M8" s="20" t="n"/>
+      <c r="N8" s="23" t="n"/>
+      <c r="O8" s="23" t="n"/>
+      <c r="P8" s="23" t="n"/>
+      <c r="Q8" s="23" t="n"/>
+      <c r="R8" s="22" t="n"/>
+    </row>
+    <row r="9" ht="92" customFormat="1" customHeight="1" s="14">
+      <c r="A9" s="24" t="inlineStr">
+        <is>
+          <t>2019::jama.2019.17380::C008</t>
+        </is>
+      </c>
+      <c r="B9" s="24" t="inlineStr">
+        <is>
+          <t>Primary analysis population drops the planned follow-up condition</t>
+        </is>
+      </c>
+      <c r="C9" s="24" t="inlineStr">
+        <is>
+          <t>joi190122supp1_prod.pdf — p.32 §15c; jama_de_boer_2019_oi_190122.pdf — p.3 Data Analysis; jama_de_boer_2019_oi_190122.pdf — p.4 Retention; jama_de_boer_2019_oi_190122.pdf — p.6 Figure 1; jama_de_boer_2019_oi_190122.pdf — p.8 Table 2 footnotes.</t>
+        </is>
+      </c>
+      <c r="D9" s="21" t="n"/>
+      <c r="E9" s="21" t="inlineStr">
+        <is>
+          <t>protocol_report</t>
+        </is>
+      </c>
+      <c r="F9" s="21" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G9" s="24">
+        <f>IFERROR(IF(LEN(TRIM(CLEAN(SUBSTITUTE(Setup!$B$2,CHAR(160)," "))))=0,"CHECK REVIEWER ID",IF(OR(A9="",COUNTIF($A$2:$A$19,A9)&lt;&gt;1,LEFT(A9,LEN("2019::jama.2019.17380::"))&lt;&gt;"2019::jama.2019.17380::"),"CHECK KEY",IF(OR(AND(NOT(AND(D9="retain",E9="statistical_results")),H9&lt;&gt;"",NOT(EXACT(H9,"not_applicable"))),AND(NOT(AND(D9="retain",E9="statistical_results")),I9&lt;&gt;"",NOT(EXACT(I9,"not_applicable"))),AND(NOT(AND(D9="retain",E9="statistical_results")),J9&lt;&gt;"",NOT(EXACT(J9,"not_applicable"))),AND(NOT(AND(D9="retain",OR(E9="report_internal_inconsistency",E9="plan_material"))),K9&lt;&gt;"",NOT(EXACT(K9,"not_applicable"))),AND(NOT(AND(D9="retain",E9="protocol_report")),L9&lt;&gt;"",NOT(EXACT(L9,"not_applicable")))),"CLEAR INACTIVE VALUES",IF(OR(NOT(OR(EXACT(D9,"retain"),EXACT(D9,"exclude"),EXACT(D9,"discuss"))),NOT(OR(EXACT(E9,"statistical_results"),EXACT(E9,"report_internal_inconsistency"),EXACT(E9,"plan_material"),EXACT(E9,"protocol_report"))),AND(AND(D9="retain",E9="statistical_results"),NOT(OR(EXACT(H9,"confirmed_issue"),EXACT(H9,"probable_issue"),EXACT(H9,"not_issue"),EXACT(H9,"indeterminate")))),AND(AND(D9="retain",E9="statistical_results"),NOT(OR(EXACT(I9,"substantive"),EXACT(I9,"minor_presentation"),EXACT(I9,"indeterminate")))),AND(AND(D9="retain",E9="statistical_results"),J9&lt;&gt;"",NOT(OR(EXACT(J9,"direct"),EXACT(J9,"possible"),EXACT(J9,"unlikely"),EXACT(J9,"unknown")))),AND(AND(D9="retain",OR(E9="report_internal_inconsistency",E9="plan_material")),NOT(OR(EXACT(K9,"substantive_inconsistency"),EXACT(K9,"minor_presentation"),EXACT(K9,"non_inconsistency"),EXACT(K9,"indeterminate")))),AND(AND(D9="retain",E9="protocol_report"),L9&lt;&gt;"",NOT(OR(EXACT(L9,"substantive_difference"),EXACT(L9,"minor_presentation"),EXACT(L9,"version_timing"),EXACT(L9,"non_inconsistency"),EXACT(L9,"indeterminate"))))),"CHECK FIELDS",IF(AND(F9&lt;&gt;"",NOT(OR(EXACT(F9,"no"),EXACT(F9,"primary_done")))),"CHECK COMPLETE",IF(EXACT(F9,"primary_done"),"PRIMARY READY","PRIMARY DRAFT")))))),"CHECK INPUT / KEY")</f>
+        <v/>
+      </c>
+      <c r="H9" s="21">
+        <f>IF(AND(OR(D9="retain",D9=""),E9="statistical_results"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="I9" s="21">
+        <f>IF(AND(OR(D9="retain",D9=""),E9="statistical_results"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="J9" s="22">
+        <f>IF(AND(OR(D9="retain",D9=""),E9="statistical_results"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="K9" s="21">
+        <f>IF(AND(OR(D9="retain",D9=""),OR(E9="report_internal_inconsistency",E9="plan_material")),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="L9" s="22">
+        <f>IF(AND(OR(D9="retain",D9=""),E9="protocol_report"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="M9" s="24" t="n"/>
+      <c r="N9" s="23" t="n"/>
+      <c r="O9" s="23" t="n"/>
+      <c r="P9" s="23" t="n"/>
+      <c r="Q9" s="23" t="n"/>
+      <c r="R9" s="22" t="n"/>
+    </row>
+    <row r="10" ht="92" customFormat="1" customHeight="1" s="14">
+      <c r="A10" s="20" t="inlineStr">
+        <is>
+          <t>2019::jama.2019.17380::C009</t>
+        </is>
+      </c>
+      <c r="B10" s="20" t="inlineStr">
+        <is>
+          <t>Primary imputation count differs between plan and report</t>
+        </is>
+      </c>
+      <c r="C10" s="20" t="inlineStr">
+        <is>
+          <t>joi190122supp1_prod.pdf — p.32 §15c; jama_de_boer_2019_oi_190122.pdf — p.3 Data Analysis; jama_de_boer_2019_oi_190122.pdf — p.8 Table 2 footnotes.</t>
+        </is>
+      </c>
+      <c r="D10" s="21" t="n"/>
+      <c r="E10" s="21" t="inlineStr">
+        <is>
+          <t>protocol_report</t>
+        </is>
+      </c>
+      <c r="F10" s="21" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G10" s="20">
+        <f>IFERROR(IF(LEN(TRIM(CLEAN(SUBSTITUTE(Setup!$B$2,CHAR(160)," "))))=0,"CHECK REVIEWER ID",IF(OR(A10="",COUNTIF($A$2:$A$19,A10)&lt;&gt;1,LEFT(A10,LEN("2019::jama.2019.17380::"))&lt;&gt;"2019::jama.2019.17380::"),"CHECK KEY",IF(OR(AND(NOT(AND(D10="retain",E10="statistical_results")),H10&lt;&gt;"",NOT(EXACT(H10,"not_applicable"))),AND(NOT(AND(D10="retain",E10="statistical_results")),I10&lt;&gt;"",NOT(EXACT(I10,"not_applicable"))),AND(NOT(AND(D10="retain",E10="statistical_results")),J10&lt;&gt;"",NOT(EXACT(J10,"not_applicable"))),AND(NOT(AND(D10="retain",OR(E10="report_internal_inconsistency",E10="plan_material"))),K10&lt;&gt;"",NOT(EXACT(K10,"not_applicable"))),AND(NOT(AND(D10="retain",E10="protocol_report")),L10&lt;&gt;"",NOT(EXACT(L10,"not_applicable")))),"CLEAR INACTIVE VALUES",IF(OR(NOT(OR(EXACT(D10,"retain"),EXACT(D10,"exclude"),EXACT(D10,"discuss"))),NOT(OR(EXACT(E10,"statistical_results"),EXACT(E10,"report_internal_inconsistency"),EXACT(E10,"plan_material"),EXACT(E10,"protocol_report"))),AND(AND(D10="retain",E10="statistical_results"),NOT(OR(EXACT(H10,"confirmed_issue"),EXACT(H10,"probable_issue"),EXACT(H10,"not_issue"),EXACT(H10,"indeterminate")))),AND(AND(D10="retain",E10="statistical_results"),NOT(OR(EXACT(I10,"substantive"),EXACT(I10,"minor_presentation"),EXACT(I10,"indeterminate")))),AND(AND(D10="retain",E10="statistical_results"),J10&lt;&gt;"",NOT(OR(EXACT(J10,"direct"),EXACT(J10,"possible"),EXACT(J10,"unlikely"),EXACT(J10,"unknown")))),AND(AND(D10="retain",OR(E10="report_internal_inconsistency",E10="plan_material")),NOT(OR(EXACT(K10,"substantive_inconsistency"),EXACT(K10,"minor_presentation"),EXACT(K10,"non_inconsistency"),EXACT(K10,"indeterminate")))),AND(AND(D10="retain",E10="protocol_report"),L10&lt;&gt;"",NOT(OR(EXACT(L10,"substantive_difference"),EXACT(L10,"minor_presentation"),EXACT(L10,"version_timing"),EXACT(L10,"non_inconsistency"),EXACT(L10,"indeterminate"))))),"CHECK FIELDS",IF(AND(F10&lt;&gt;"",NOT(OR(EXACT(F10,"no"),EXACT(F10,"primary_done")))),"CHECK COMPLETE",IF(EXACT(F10,"primary_done"),"PRIMARY READY","PRIMARY DRAFT")))))),"CHECK INPUT / KEY")</f>
+        <v/>
+      </c>
+      <c r="H10" s="21">
+        <f>IF(AND(OR(D10="retain",D10=""),E10="statistical_results"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="I10" s="21">
+        <f>IF(AND(OR(D10="retain",D10=""),E10="statistical_results"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="J10" s="22">
+        <f>IF(AND(OR(D10="retain",D10=""),E10="statistical_results"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="K10" s="21">
+        <f>IF(AND(OR(D10="retain",D10=""),OR(E10="report_internal_inconsistency",E10="plan_material")),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="L10" s="22">
+        <f>IF(AND(OR(D10="retain",D10=""),E10="protocol_report"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="M10" s="20" t="n"/>
+      <c r="N10" s="23" t="n"/>
+      <c r="O10" s="23" t="n"/>
+      <c r="P10" s="23" t="n"/>
+      <c r="Q10" s="23" t="n"/>
+      <c r="R10" s="22" t="n"/>
+    </row>
+    <row r="11" ht="92" customFormat="1" customHeight="1" s="14">
+      <c r="A11" s="24" t="inlineStr">
+        <is>
+          <t>2019::jama.2019.17380::C010</t>
+        </is>
+      </c>
+      <c r="B11" s="24" t="inlineStr">
+        <is>
+          <t>Reported primary covariates differ from the planned primary model</t>
+        </is>
+      </c>
+      <c r="C11" s="24" t="inlineStr">
+        <is>
+          <t>joi190122supp1_prod.pdf — p.32 §15e Equation 2 and conditional sensitivity clause; joi190122supp1_prod.pdf — p.33; jama_de_boer_2019_oi_190122.pdf — p.3 Data Analysis; jama_de_boer_2019_oi_190122.pdf — p.8 Table 2 footnote a; joi190122supp2_prod.pdf — p.9 eTable 4; joi190122supp2_prod.pdf — p.10 eTable 5.</t>
+        </is>
+      </c>
+      <c r="D11" s="21" t="n"/>
+      <c r="E11" s="21" t="inlineStr">
+        <is>
+          <t>protocol_report</t>
+        </is>
+      </c>
+      <c r="F11" s="21" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G11" s="24">
+        <f>IFERROR(IF(LEN(TRIM(CLEAN(SUBSTITUTE(Setup!$B$2,CHAR(160)," "))))=0,"CHECK REVIEWER ID",IF(OR(A11="",COUNTIF($A$2:$A$19,A11)&lt;&gt;1,LEFT(A11,LEN("2019::jama.2019.17380::"))&lt;&gt;"2019::jama.2019.17380::"),"CHECK KEY",IF(OR(AND(NOT(AND(D11="retain",E11="statistical_results")),H11&lt;&gt;"",NOT(EXACT(H11,"not_applicable"))),AND(NOT(AND(D11="retain",E11="statistical_results")),I11&lt;&gt;"",NOT(EXACT(I11,"not_applicable"))),AND(NOT(AND(D11="retain",E11="statistical_results")),J11&lt;&gt;"",NOT(EXACT(J11,"not_applicable"))),AND(NOT(AND(D11="retain",OR(E11="report_internal_inconsistency",E11="plan_material"))),K11&lt;&gt;"",NOT(EXACT(K11,"not_applicable"))),AND(NOT(AND(D11="retain",E11="protocol_report")),L11&lt;&gt;"",NOT(EXACT(L11,"not_applicable")))),"CLEAR INACTIVE VALUES",IF(OR(NOT(OR(EXACT(D11,"retain"),EXACT(D11,"exclude"),EXACT(D11,"discuss"))),NOT(OR(EXACT(E11,"statistical_results"),EXACT(E11,"report_internal_inconsistency"),EXACT(E11,"plan_material"),EXACT(E11,"protocol_report"))),AND(AND(D11="retain",E11="statistical_results"),NOT(OR(EXACT(H11,"confirmed_issue"),EXACT(H11,"probable_issue"),EXACT(H11,"not_issue"),EXACT(H11,"indeterminate")))),AND(AND(D11="retain",E11="statistical_results"),NOT(OR(EXACT(I11,"substantive"),EXACT(I11,"minor_presentation"),EXACT(I11,"indeterminate")))),AND(AND(D11="retain",E11="statistical_results"),J11&lt;&gt;"",NOT(OR(EXACT(J11,"direct"),EXACT(J11,"possible"),EXACT(J11,"unlikely"),EXACT(J11,"unknown")))),AND(AND(D11="retain",OR(E11="report_internal_inconsistency",E11="plan_material")),NOT(OR(EXACT(K11,"substantive_inconsistency"),EXACT(K11,"minor_presentation"),EXACT(K11,"non_inconsistency"),EXACT(K11,"indeterminate")))),AND(AND(D11="retain",E11="protocol_report"),L11&lt;&gt;"",NOT(OR(EXACT(L11,"substantive_difference"),EXACT(L11,"minor_presentation"),EXACT(L11,"version_timing"),EXACT(L11,"non_inconsistency"),EXACT(L11,"indeterminate"))))),"CHECK FIELDS",IF(AND(F11&lt;&gt;"",NOT(OR(EXACT(F11,"no"),EXACT(F11,"primary_done")))),"CHECK COMPLETE",IF(EXACT(F11,"primary_done"),"PRIMARY READY","PRIMARY DRAFT")))))),"CHECK INPUT / KEY")</f>
+        <v/>
+      </c>
+      <c r="H11" s="21">
+        <f>IF(AND(OR(D11="retain",D11=""),E11="statistical_results"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="I11" s="21">
+        <f>IF(AND(OR(D11="retain",D11=""),E11="statistical_results"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="J11" s="22">
+        <f>IF(AND(OR(D11="retain",D11=""),E11="statistical_results"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="K11" s="21">
+        <f>IF(AND(OR(D11="retain",D11=""),OR(E11="report_internal_inconsistency",E11="plan_material")),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="L11" s="22">
+        <f>IF(AND(OR(D11="retain",D11=""),E11="protocol_report"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="M11" s="24" t="n"/>
+      <c r="N11" s="23" t="n"/>
+      <c r="O11" s="23" t="n"/>
+      <c r="P11" s="23" t="n"/>
+      <c r="Q11" s="23" t="n"/>
+      <c r="R11" s="22" t="n"/>
+    </row>
+    <row r="12" ht="92" customFormat="1" customHeight="1" s="14">
+      <c r="A12" s="20" t="inlineStr">
+        <is>
+          <t>2019::jama.2019.17380::C011</t>
+        </is>
+      </c>
+      <c r="B12" s="20" t="inlineStr">
+        <is>
+          <t>Planned bioavailable vitamin-D subgroup result is absent</t>
+        </is>
+      </c>
+      <c r="C12" s="20" t="inlineStr">
+        <is>
+          <t>joi190122supp1_prod.pdf — p.33 §15f; jama_de_boer_2019_oi_190122.pdf — p.3 subgroup methods; jama_de_boer_2019_oi_190122.pdf — p.8 Figure 3; jama_de_boer_2019_oi_190122.pdf — p.9 interpretation; jama_de_boer_2019_oi_190122.pdf — p.10 interpretation/disclosure; joi190122supp2_prod.pdf — p.18 eFigure 2; joi190122supp2_prod.pdf — p.17 eFigure 1; joi190122supp3_prod.pdf — data-sharing statement p.1.</t>
+        </is>
+      </c>
+      <c r="D12" s="21" t="n"/>
+      <c r="E12" s="21" t="inlineStr">
+        <is>
+          <t>protocol_report</t>
+        </is>
+      </c>
+      <c r="F12" s="21" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G12" s="20">
+        <f>IFERROR(IF(LEN(TRIM(CLEAN(SUBSTITUTE(Setup!$B$2,CHAR(160)," "))))=0,"CHECK REVIEWER ID",IF(OR(A12="",COUNTIF($A$2:$A$19,A12)&lt;&gt;1,LEFT(A12,LEN("2019::jama.2019.17380::"))&lt;&gt;"2019::jama.2019.17380::"),"CHECK KEY",IF(OR(AND(NOT(AND(D12="retain",E12="statistical_results")),H12&lt;&gt;"",NOT(EXACT(H12,"not_applicable"))),AND(NOT(AND(D12="retain",E12="statistical_results")),I12&lt;&gt;"",NOT(EXACT(I12,"not_applicable"))),AND(NOT(AND(D12="retain",E12="statistical_results")),J12&lt;&gt;"",NOT(EXACT(J12,"not_applicable"))),AND(NOT(AND(D12="retain",OR(E12="report_internal_inconsistency",E12="plan_material"))),K12&lt;&gt;"",NOT(EXACT(K12,"not_applicable"))),AND(NOT(AND(D12="retain",E12="protocol_report")),L12&lt;&gt;"",NOT(EXACT(L12,"not_applicable")))),"CLEAR INACTIVE VALUES",IF(OR(NOT(OR(EXACT(D12,"retain"),EXACT(D12,"exclude"),EXACT(D12,"discuss"))),NOT(OR(EXACT(E12,"statistical_results"),EXACT(E12,"report_internal_inconsistency"),EXACT(E12,"plan_material"),EXACT(E12,"protocol_report"))),AND(AND(D12="retain",E12="statistical_results"),NOT(OR(EXACT(H12,"confirmed_issue"),EXACT(H12,"probable_issue"),EXACT(H12,"not_issue"),EXACT(H12,"indeterminate")))),AND(AND(D12="retain",E12="statistical_results"),NOT(OR(EXACT(I12,"substantive"),EXACT(I12,"minor_presentation"),EXACT(I12,"indeterminate")))),AND(AND(D12="retain",E12="statistical_results"),J12&lt;&gt;"",NOT(OR(EXACT(J12,"direct"),EXACT(J12,"possible"),EXACT(J12,"unlikely"),EXACT(J12,"unknown")))),AND(AND(D12="retain",OR(E12="report_internal_inconsistency",E12="plan_material")),NOT(OR(EXACT(K12,"substantive_inconsistency"),EXACT(K12,"minor_presentation"),EXACT(K12,"non_inconsistency"),EXACT(K12,"indeterminate")))),AND(AND(D12="retain",E12="protocol_report"),L12&lt;&gt;"",NOT(OR(EXACT(L12,"substantive_difference"),EXACT(L12,"minor_presentation"),EXACT(L12,"version_timing"),EXACT(L12,"non_inconsistency"),EXACT(L12,"indeterminate"))))),"CHECK FIELDS",IF(AND(F12&lt;&gt;"",NOT(OR(EXACT(F12,"no"),EXACT(F12,"primary_done")))),"CHECK COMPLETE",IF(EXACT(F12,"primary_done"),"PRIMARY READY","PRIMARY DRAFT")))))),"CHECK INPUT / KEY")</f>
+        <v/>
+      </c>
+      <c r="H12" s="21">
+        <f>IF(AND(OR(D12="retain",D12=""),E12="statistical_results"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="I12" s="21">
+        <f>IF(AND(OR(D12="retain",D12=""),E12="statistical_results"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="J12" s="22">
+        <f>IF(AND(OR(D12="retain",D12=""),E12="statistical_results"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="K12" s="21">
+        <f>IF(AND(OR(D12="retain",D12=""),OR(E12="report_internal_inconsistency",E12="plan_material")),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="L12" s="22">
+        <f>IF(AND(OR(D12="retain",D12=""),E12="protocol_report"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="M12" s="20" t="n"/>
+      <c r="N12" s="23" t="n"/>
+      <c r="O12" s="23" t="n"/>
+      <c r="P12" s="23" t="n"/>
+      <c r="Q12" s="23" t="n"/>
+      <c r="R12" s="22" t="n"/>
+    </row>
+    <row r="13" ht="92" customFormat="1" customHeight="1" s="14">
+      <c r="A13" s="24" t="inlineStr">
+        <is>
+          <t>2019::jama.2019.17380::C012</t>
+        </is>
+      </c>
+      <c r="B13" s="24" t="inlineStr">
+        <is>
+          <t>Forest figures associate counts with opposite treatment columns</t>
+        </is>
+      </c>
+      <c r="C13" s="24" t="inlineStr">
+        <is>
+          <t>jama_de_boer_2019_oi_190122.pdf — main p.8 Figure 3 and Table 2; jama_de_boer_2019_oi_190122.pdf — main p.9 Figure 4; joi190122supp2_prod.pdf — supplement p.18 eFigure 2; joi190122supp2_prod.pdf — supplement p.19 eFigure 3; jama_de_boer_2019_oi_190122.pdf — main p.1 allocation; jama_de_boer_2019_oi_190122.pdf — p.5 Table 1; jama_de_boer_2019_oi_190122.pdf — p.6 Figure 1; joi190122supp2_prod.pdf — supplement p.11 eTable 6; joi190122supp2_prod.pdf — p.16 eTable 11 marginal allocations.</t>
+        </is>
+      </c>
+      <c r="D13" s="21" t="n"/>
+      <c r="E13" s="21" t="inlineStr">
+        <is>
+          <t>statistical_results</t>
+        </is>
+      </c>
+      <c r="F13" s="21" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G13" s="24">
+        <f>IFERROR(IF(LEN(TRIM(CLEAN(SUBSTITUTE(Setup!$B$2,CHAR(160)," "))))=0,"CHECK REVIEWER ID",IF(OR(A13="",COUNTIF($A$2:$A$19,A13)&lt;&gt;1,LEFT(A13,LEN("2019::jama.2019.17380::"))&lt;&gt;"2019::jama.2019.17380::"),"CHECK KEY",IF(OR(AND(NOT(AND(D13="retain",E13="statistical_results")),H13&lt;&gt;"",NOT(EXACT(H13,"not_applicable"))),AND(NOT(AND(D13="retain",E13="statistical_results")),I13&lt;&gt;"",NOT(EXACT(I13,"not_applicable"))),AND(NOT(AND(D13="retain",E13="statistical_results")),J13&lt;&gt;"",NOT(EXACT(J13,"not_applicable"))),AND(NOT(AND(D13="retain",OR(E13="report_internal_inconsistency",E13="plan_material"))),K13&lt;&gt;"",NOT(EXACT(K13,"not_applicable"))),AND(NOT(AND(D13="retain",E13="protocol_report")),L13&lt;&gt;"",NOT(EXACT(L13,"not_applicable")))),"CLEAR INACTIVE VALUES",IF(OR(NOT(OR(EXACT(D13,"retain"),EXACT(D13,"exclude"),EXACT(D13,"discuss"))),NOT(OR(EXACT(E13,"statistical_results"),EXACT(E13,"report_internal_inconsistency"),EXACT(E13,"plan_material"),EXACT(E13,"protocol_report"))),AND(AND(D13="retain",E13="statistical_results"),NOT(OR(EXACT(H13,"confirmed_issue"),EXACT(H13,"probable_issue"),EXACT(H13,"not_issue"),EXACT(H13,"indeterminate")))),AND(AND(D13="retain",E13="statistical_results"),NOT(OR(EXACT(I13,"substantive"),EXACT(I13,"minor_presentation"),EXACT(I13,"indeterminate")))),AND(AND(D13="retain",E13="statistical_results"),J13&lt;&gt;"",NOT(OR(EXACT(J13,"direct"),EXACT(J13,"possible"),EXACT(J13,"unlikely"),EXACT(J13,"unknown")))),AND(AND(D13="retain",OR(E13="report_internal_inconsistency",E13="plan_material")),NOT(OR(EXACT(K13,"substantive_inconsistency"),EXACT(K13,"minor_presentation"),EXACT(K13,"non_inconsistency"),EXACT(K13,"indeterminate")))),AND(AND(D13="retain",E13="protocol_report"),L13&lt;&gt;"",NOT(OR(EXACT(L13,"substantive_difference"),EXACT(L13,"minor_presentation"),EXACT(L13,"version_timing"),EXACT(L13,"non_inconsistency"),EXACT(L13,"indeterminate"))))),"CHECK FIELDS",IF(AND(F13&lt;&gt;"",NOT(OR(EXACT(F13,"no"),EXACT(F13,"primary_done")))),"CHECK COMPLETE",IF(EXACT(F13,"primary_done"),"PRIMARY READY","PRIMARY DRAFT")))))),"CHECK INPUT / KEY")</f>
+        <v/>
+      </c>
+      <c r="H13" s="21">
+        <f>IF(AND(OR(D13="retain",D13=""),E13="statistical_results"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="I13" s="21">
+        <f>IF(AND(OR(D13="retain",D13=""),E13="statistical_results"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="J13" s="22">
+        <f>IF(AND(OR(D13="retain",D13=""),E13="statistical_results"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="K13" s="21">
+        <f>IF(AND(OR(D13="retain",D13=""),OR(E13="report_internal_inconsistency",E13="plan_material")),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="L13" s="22">
+        <f>IF(AND(OR(D13="retain",D13=""),E13="protocol_report"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="M13" s="24" t="n"/>
+      <c r="N13" s="23" t="n"/>
+      <c r="O13" s="23" t="n"/>
+      <c r="P13" s="23" t="n"/>
+      <c r="Q13" s="23" t="n"/>
+      <c r="R13" s="22" t="n"/>
+    </row>
+    <row r="14" ht="92" customFormat="1" customHeight="1" s="14">
+      <c r="A14" s="20" t="inlineStr">
+        <is>
+          <t>2019::jama.2019.17380::C013</t>
+        </is>
+      </c>
+      <c r="B14" s="20" t="inlineStr">
+        <is>
+          <t>Omega-3 contributor rows repeat vitamin-D counts</t>
+        </is>
+      </c>
+      <c r="C14" s="20" t="inlineStr">
+        <is>
+          <t>jama_de_boer_2019_oi_190122.pdf — main p.7 Figure 2 A–D and caption; jama_de_boer_2019_oi_190122.pdf — main p.8 Table 2; joi190122supp2_prod.pdf — supplement p.11 eTable 6; jama_de_boer_2019_oi_190122.pdf — main p.1 allocation.</t>
+        </is>
+      </c>
+      <c r="D14" s="21" t="n"/>
+      <c r="E14" s="21" t="inlineStr">
+        <is>
+          <t>statistical_results</t>
+        </is>
+      </c>
+      <c r="F14" s="21" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G14" s="20">
+        <f>IFERROR(IF(LEN(TRIM(CLEAN(SUBSTITUTE(Setup!$B$2,CHAR(160)," "))))=0,"CHECK REVIEWER ID",IF(OR(A14="",COUNTIF($A$2:$A$19,A14)&lt;&gt;1,LEFT(A14,LEN("2019::jama.2019.17380::"))&lt;&gt;"2019::jama.2019.17380::"),"CHECK KEY",IF(OR(AND(NOT(AND(D14="retain",E14="statistical_results")),H14&lt;&gt;"",NOT(EXACT(H14,"not_applicable"))),AND(NOT(AND(D14="retain",E14="statistical_results")),I14&lt;&gt;"",NOT(EXACT(I14,"not_applicable"))),AND(NOT(AND(D14="retain",E14="statistical_results")),J14&lt;&gt;"",NOT(EXACT(J14,"not_applicable"))),AND(NOT(AND(D14="retain",OR(E14="report_internal_inconsistency",E14="plan_material"))),K14&lt;&gt;"",NOT(EXACT(K14,"not_applicable"))),AND(NOT(AND(D14="retain",E14="protocol_report")),L14&lt;&gt;"",NOT(EXACT(L14,"not_applicable")))),"CLEAR INACTIVE VALUES",IF(OR(NOT(OR(EXACT(D14,"retain"),EXACT(D14,"exclude"),EXACT(D14,"discuss"))),NOT(OR(EXACT(E14,"statistical_results"),EXACT(E14,"report_internal_inconsistency"),EXACT(E14,"plan_material"),EXACT(E14,"protocol_report"))),AND(AND(D14="retain",E14="statistical_results"),NOT(OR(EXACT(H14,"confirmed_issue"),EXACT(H14,"probable_issue"),EXACT(H14,"not_issue"),EXACT(H14,"indeterminate")))),AND(AND(D14="retain",E14="statistical_results"),NOT(OR(EXACT(I14,"substantive"),EXACT(I14,"minor_presentation"),EXACT(I14,"indeterminate")))),AND(AND(D14="retain",E14="statistical_results"),J14&lt;&gt;"",NOT(OR(EXACT(J14,"direct"),EXACT(J14,"possible"),EXACT(J14,"unlikely"),EXACT(J14,"unknown")))),AND(AND(D14="retain",OR(E14="report_internal_inconsistency",E14="plan_material")),NOT(OR(EXACT(K14,"substantive_inconsistency"),EXACT(K14,"minor_presentation"),EXACT(K14,"non_inconsistency"),EXACT(K14,"indeterminate")))),AND(AND(D14="retain",E14="protocol_report"),L14&lt;&gt;"",NOT(OR(EXACT(L14,"substantive_difference"),EXACT(L14,"minor_presentation"),EXACT(L14,"version_timing"),EXACT(L14,"non_inconsistency"),EXACT(L14,"indeterminate"))))),"CHECK FIELDS",IF(AND(F14&lt;&gt;"",NOT(OR(EXACT(F14,"no"),EXACT(F14,"primary_done")))),"CHECK COMPLETE",IF(EXACT(F14,"primary_done"),"PRIMARY READY","PRIMARY DRAFT")))))),"CHECK INPUT / KEY")</f>
+        <v/>
+      </c>
+      <c r="H14" s="21">
+        <f>IF(AND(OR(D14="retain",D14=""),E14="statistical_results"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="I14" s="21">
+        <f>IF(AND(OR(D14="retain",D14=""),E14="statistical_results"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="J14" s="22">
+        <f>IF(AND(OR(D14="retain",D14=""),E14="statistical_results"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="K14" s="21">
+        <f>IF(AND(OR(D14="retain",D14=""),OR(E14="report_internal_inconsistency",E14="plan_material")),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="L14" s="22">
+        <f>IF(AND(OR(D14="retain",D14=""),E14="protocol_report"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="M14" s="20" t="n"/>
+      <c r="N14" s="23" t="n"/>
+      <c r="O14" s="23" t="n"/>
+      <c r="P14" s="23" t="n"/>
+      <c r="Q14" s="23" t="n"/>
+      <c r="R14" s="22" t="n"/>
+    </row>
+    <row r="15" ht="92" customFormat="1" customHeight="1" s="14">
+      <c r="A15" s="24" t="inlineStr">
+        <is>
+          <t>2019::jama.2019.17380::C014</t>
+        </is>
+      </c>
+      <c r="B15" s="24" t="inlineStr">
+        <is>
+          <t>Plan gives two microgram equivalents for the same vitamin-D dose</t>
+        </is>
+      </c>
+      <c r="C15" s="24" t="inlineStr">
+        <is>
+          <t>joi190122supp1_prod.pdf — p.15 V.e.1; joi190122supp1_prod.pdf — p.21 VII.a; jama_de_boer_2019_oi_190122.pdf — main p.2 intervention.</t>
+        </is>
+      </c>
+      <c r="D15" s="21" t="n"/>
+      <c r="E15" s="21" t="inlineStr">
+        <is>
+          <t>plan_material</t>
+        </is>
+      </c>
+      <c r="F15" s="21" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G15" s="24">
+        <f>IFERROR(IF(LEN(TRIM(CLEAN(SUBSTITUTE(Setup!$B$2,CHAR(160)," "))))=0,"CHECK REVIEWER ID",IF(OR(A15="",COUNTIF($A$2:$A$19,A15)&lt;&gt;1,LEFT(A15,LEN("2019::jama.2019.17380::"))&lt;&gt;"2019::jama.2019.17380::"),"CHECK KEY",IF(OR(AND(NOT(AND(D15="retain",E15="statistical_results")),H15&lt;&gt;"",NOT(EXACT(H15,"not_applicable"))),AND(NOT(AND(D15="retain",E15="statistical_results")),I15&lt;&gt;"",NOT(EXACT(I15,"not_applicable"))),AND(NOT(AND(D15="retain",E15="statistical_results")),J15&lt;&gt;"",NOT(EXACT(J15,"not_applicable"))),AND(NOT(AND(D15="retain",OR(E15="report_internal_inconsistency",E15="plan_material"))),K15&lt;&gt;"",NOT(EXACT(K15,"not_applicable"))),AND(NOT(AND(D15="retain",E15="protocol_report")),L15&lt;&gt;"",NOT(EXACT(L15,"not_applicable")))),"CLEAR INACTIVE VALUES",IF(OR(NOT(OR(EXACT(D15,"retain"),EXACT(D15,"exclude"),EXACT(D15,"discuss"))),NOT(OR(EXACT(E15,"statistical_results"),EXACT(E15,"report_internal_inconsistency"),EXACT(E15,"plan_material"),EXACT(E15,"protocol_report"))),AND(AND(D15="retain",E15="statistical_results"),NOT(OR(EXACT(H15,"confirmed_issue"),EXACT(H15,"probable_issue"),EXACT(H15,"not_issue"),EXACT(H15,"indeterminate")))),AND(AND(D15="retain",E15="statistical_results"),NOT(OR(EXACT(I15,"substantive"),EXACT(I15,"minor_presentation"),EXACT(I15,"indeterminate")))),AND(AND(D15="retain",E15="statistical_results"),J15&lt;&gt;"",NOT(OR(EXACT(J15,"direct"),EXACT(J15,"possible"),EXACT(J15,"unlikely"),EXACT(J15,"unknown")))),AND(AND(D15="retain",OR(E15="report_internal_inconsistency",E15="plan_material")),NOT(OR(EXACT(K15,"substantive_inconsistency"),EXACT(K15,"minor_presentation"),EXACT(K15,"non_inconsistency"),EXACT(K15,"indeterminate")))),AND(AND(D15="retain",E15="protocol_report"),L15&lt;&gt;"",NOT(OR(EXACT(L15,"substantive_difference"),EXACT(L15,"minor_presentation"),EXACT(L15,"version_timing"),EXACT(L15,"non_inconsistency"),EXACT(L15,"indeterminate"))))),"CHECK FIELDS",IF(AND(F15&lt;&gt;"",NOT(OR(EXACT(F15,"no"),EXACT(F15,"primary_done")))),"CHECK COMPLETE",IF(EXACT(F15,"primary_done"),"PRIMARY READY","PRIMARY DRAFT")))))),"CHECK INPUT / KEY")</f>
+        <v/>
+      </c>
+      <c r="H15" s="21">
+        <f>IF(AND(OR(D15="retain",D15=""),E15="statistical_results"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="I15" s="21">
+        <f>IF(AND(OR(D15="retain",D15=""),E15="statistical_results"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="J15" s="22">
+        <f>IF(AND(OR(D15="retain",D15=""),E15="statistical_results"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="K15" s="21">
+        <f>IF(AND(OR(D15="retain",D15=""),OR(E15="report_internal_inconsistency",E15="plan_material")),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="L15" s="22">
+        <f>IF(AND(OR(D15="retain",D15=""),E15="protocol_report"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="M15" s="24" t="n"/>
+      <c r="N15" s="23" t="n"/>
+      <c r="O15" s="23" t="n"/>
+      <c r="P15" s="23" t="n"/>
+      <c r="Q15" s="23" t="n"/>
+      <c r="R15" s="22" t="n"/>
+    </row>
+    <row r="16" ht="92" customFormat="1" customHeight="1" s="14">
+      <c r="A16" s="20" t="inlineStr">
+        <is>
+          <t>2019::jama.2019.17380::C015</t>
+        </is>
+      </c>
+      <c r="B16" s="20" t="inlineStr">
+        <is>
+          <t>Plan interaction and primary models specify different time terms</t>
+        </is>
+      </c>
+      <c r="C16" s="20" t="inlineStr">
+        <is>
+          <t>joi190122supp1_prod.pdf — p.32 §15d Equation 1 and §15e Equation 2; jama_de_boer_2019_oi_190122.pdf — main p.3; jama_de_boer_2019_oi_190122.pdf — p.4.</t>
+        </is>
+      </c>
+      <c r="D16" s="21" t="n"/>
+      <c r="E16" s="21" t="inlineStr">
+        <is>
+          <t>plan_material</t>
+        </is>
+      </c>
+      <c r="F16" s="21" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G16" s="20">
+        <f>IFERROR(IF(LEN(TRIM(CLEAN(SUBSTITUTE(Setup!$B$2,CHAR(160)," "))))=0,"CHECK REVIEWER ID",IF(OR(A16="",COUNTIF($A$2:$A$19,A16)&lt;&gt;1,LEFT(A16,LEN("2019::jama.2019.17380::"))&lt;&gt;"2019::jama.2019.17380::"),"CHECK KEY",IF(OR(AND(NOT(AND(D16="retain",E16="statistical_results")),H16&lt;&gt;"",NOT(EXACT(H16,"not_applicable"))),AND(NOT(AND(D16="retain",E16="statistical_results")),I16&lt;&gt;"",NOT(EXACT(I16,"not_applicable"))),AND(NOT(AND(D16="retain",E16="statistical_results")),J16&lt;&gt;"",NOT(EXACT(J16,"not_applicable"))),AND(NOT(AND(D16="retain",OR(E16="report_internal_inconsistency",E16="plan_material"))),K16&lt;&gt;"",NOT(EXACT(K16,"not_applicable"))),AND(NOT(AND(D16="retain",E16="protocol_report")),L16&lt;&gt;"",NOT(EXACT(L16,"not_applicable")))),"CLEAR INACTIVE VALUES",IF(OR(NOT(OR(EXACT(D16,"retain"),EXACT(D16,"exclude"),EXACT(D16,"discuss"))),NOT(OR(EXACT(E16,"statistical_results"),EXACT(E16,"report_internal_inconsistency"),EXACT(E16,"plan_material"),EXACT(E16,"protocol_report"))),AND(AND(D16="retain",E16="statistical_results"),NOT(OR(EXACT(H16,"confirmed_issue"),EXACT(H16,"probable_issue"),EXACT(H16,"not_issue"),EXACT(H16,"indeterminate")))),AND(AND(D16="retain",E16="statistical_results"),NOT(OR(EXACT(I16,"substantive"),EXACT(I16,"minor_presentation"),EXACT(I16,"indeterminate")))),AND(AND(D16="retain",E16="statistical_results"),J16&lt;&gt;"",NOT(OR(EXACT(J16,"direct"),EXACT(J16,"possible"),EXACT(J16,"unlikely"),EXACT(J16,"unknown")))),AND(AND(D16="retain",OR(E16="report_internal_inconsistency",E16="plan_material")),NOT(OR(EXACT(K16,"substantive_inconsistency"),EXACT(K16,"minor_presentation"),EXACT(K16,"non_inconsistency"),EXACT(K16,"indeterminate")))),AND(AND(D16="retain",E16="protocol_report"),L16&lt;&gt;"",NOT(OR(EXACT(L16,"substantive_difference"),EXACT(L16,"minor_presentation"),EXACT(L16,"version_timing"),EXACT(L16,"non_inconsistency"),EXACT(L16,"indeterminate"))))),"CHECK FIELDS",IF(AND(F16&lt;&gt;"",NOT(OR(EXACT(F16,"no"),EXACT(F16,"primary_done")))),"CHECK COMPLETE",IF(EXACT(F16,"primary_done"),"PRIMARY READY","PRIMARY DRAFT")))))),"CHECK INPUT / KEY")</f>
+        <v/>
+      </c>
+      <c r="H16" s="21">
+        <f>IF(AND(OR(D16="retain",D16=""),E16="statistical_results"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="I16" s="21">
+        <f>IF(AND(OR(D16="retain",D16=""),E16="statistical_results"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="J16" s="22">
+        <f>IF(AND(OR(D16="retain",D16=""),E16="statistical_results"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="K16" s="21">
+        <f>IF(AND(OR(D16="retain",D16=""),OR(E16="report_internal_inconsistency",E16="plan_material")),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="L16" s="22">
+        <f>IF(AND(OR(D16="retain",D16=""),E16="protocol_report"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="M16" s="20" t="n"/>
+      <c r="N16" s="23" t="n"/>
+      <c r="O16" s="23" t="n"/>
+      <c r="P16" s="23" t="n"/>
+      <c r="Q16" s="23" t="n"/>
+      <c r="R16" s="22" t="n"/>
+    </row>
+    <row r="17" ht="92" customFormat="1" customHeight="1" s="14">
+      <c r="A17" s="24" t="inlineStr">
+        <is>
+          <t>2019::jama.2019.17380::C016</t>
+        </is>
+      </c>
+      <c r="B17" s="24" t="inlineStr">
+        <is>
+          <t>Year-5 SGLT2 count and percentage do not reconcile</t>
+        </is>
+      </c>
+      <c r="C17" s="24" t="inlineStr">
+        <is>
+          <t>joi190122supp2_prod.pdf — supplement p.7 eTable 2.</t>
+        </is>
+      </c>
+      <c r="D17" s="21" t="n"/>
+      <c r="E17" s="21" t="inlineStr">
+        <is>
+          <t>statistical_results</t>
+        </is>
+      </c>
+      <c r="F17" s="21" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G17" s="24">
+        <f>IFERROR(IF(LEN(TRIM(CLEAN(SUBSTITUTE(Setup!$B$2,CHAR(160)," "))))=0,"CHECK REVIEWER ID",IF(OR(A17="",COUNTIF($A$2:$A$19,A17)&lt;&gt;1,LEFT(A17,LEN("2019::jama.2019.17380::"))&lt;&gt;"2019::jama.2019.17380::"),"CHECK KEY",IF(OR(AND(NOT(AND(D17="retain",E17="statistical_results")),H17&lt;&gt;"",NOT(EXACT(H17,"not_applicable"))),AND(NOT(AND(D17="retain",E17="statistical_results")),I17&lt;&gt;"",NOT(EXACT(I17,"not_applicable"))),AND(NOT(AND(D17="retain",E17="statistical_results")),J17&lt;&gt;"",NOT(EXACT(J17,"not_applicable"))),AND(NOT(AND(D17="retain",OR(E17="report_internal_inconsistency",E17="plan_material"))),K17&lt;&gt;"",NOT(EXACT(K17,"not_applicable"))),AND(NOT(AND(D17="retain",E17="protocol_report")),L17&lt;&gt;"",NOT(EXACT(L17,"not_applicable")))),"CLEAR INACTIVE VALUES",IF(OR(NOT(OR(EXACT(D17,"retain"),EXACT(D17,"exclude"),EXACT(D17,"discuss"))),NOT(OR(EXACT(E17,"statistical_results"),EXACT(E17,"report_internal_inconsistency"),EXACT(E17,"plan_material"),EXACT(E17,"protocol_report"))),AND(AND(D17="retain",E17="statistical_results"),NOT(OR(EXACT(H17,"confirmed_issue"),EXACT(H17,"probable_issue"),EXACT(H17,"not_issue"),EXACT(H17,"indeterminate")))),AND(AND(D17="retain",E17="statistical_results"),NOT(OR(EXACT(I17,"substantive"),EXACT(I17,"minor_presentation"),EXACT(I17,"indeterminate")))),AND(AND(D17="retain",E17="statistical_results"),J17&lt;&gt;"",NOT(OR(EXACT(J17,"direct"),EXACT(J17,"possible"),EXACT(J17,"unlikely"),EXACT(J17,"unknown")))),AND(AND(D17="retain",OR(E17="report_internal_inconsistency",E17="plan_material")),NOT(OR(EXACT(K17,"substantive_inconsistency"),EXACT(K17,"minor_presentation"),EXACT(K17,"non_inconsistency"),EXACT(K17,"indeterminate")))),AND(AND(D17="retain",E17="protocol_report"),L17&lt;&gt;"",NOT(OR(EXACT(L17,"substantive_difference"),EXACT(L17,"minor_presentation"),EXACT(L17,"version_timing"),EXACT(L17,"non_inconsistency"),EXACT(L17,"indeterminate"))))),"CHECK FIELDS",IF(AND(F17&lt;&gt;"",NOT(OR(EXACT(F17,"no"),EXACT(F17,"primary_done")))),"CHECK COMPLETE",IF(EXACT(F17,"primary_done"),"PRIMARY READY","PRIMARY DRAFT")))))),"CHECK INPUT / KEY")</f>
+        <v/>
+      </c>
+      <c r="H17" s="21">
+        <f>IF(AND(OR(D17="retain",D17=""),E17="statistical_results"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="I17" s="21">
+        <f>IF(AND(OR(D17="retain",D17=""),E17="statistical_results"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="J17" s="22">
+        <f>IF(AND(OR(D17="retain",D17=""),E17="statistical_results"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="K17" s="21">
+        <f>IF(AND(OR(D17="retain",D17=""),OR(E17="report_internal_inconsistency",E17="plan_material")),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="L17" s="22">
+        <f>IF(AND(OR(D17="retain",D17=""),E17="protocol_report"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="M17" s="24" t="n"/>
+      <c r="N17" s="23" t="n"/>
+      <c r="O17" s="23" t="n"/>
+      <c r="P17" s="23" t="n"/>
+      <c r="Q17" s="23" t="n"/>
+      <c r="R17" s="22" t="n"/>
+    </row>
+    <row r="18" ht="92" customFormat="1" customHeight="1" s="14">
+      <c r="A18" s="20" t="inlineStr">
+        <is>
+          <t>2019::jama.2019.17380::C017</t>
+        </is>
+      </c>
+      <c r="B18" s="20" t="inlineStr">
+        <is>
+          <t>Paired-urine exclusion accounting does not reconcile</t>
+        </is>
+      </c>
+      <c r="C18" s="20" t="inlineStr">
+        <is>
+          <t>joi190122supp2_prod.pdf — supplement p.12 eTable 7.</t>
+        </is>
+      </c>
+      <c r="D18" s="21" t="n"/>
+      <c r="E18" s="21" t="inlineStr">
+        <is>
+          <t>statistical_results</t>
+        </is>
+      </c>
+      <c r="F18" s="21" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G18" s="20">
+        <f>IFERROR(IF(LEN(TRIM(CLEAN(SUBSTITUTE(Setup!$B$2,CHAR(160)," "))))=0,"CHECK REVIEWER ID",IF(OR(A18="",COUNTIF($A$2:$A$19,A18)&lt;&gt;1,LEFT(A18,LEN("2019::jama.2019.17380::"))&lt;&gt;"2019::jama.2019.17380::"),"CHECK KEY",IF(OR(AND(NOT(AND(D18="retain",E18="statistical_results")),H18&lt;&gt;"",NOT(EXACT(H18,"not_applicable"))),AND(NOT(AND(D18="retain",E18="statistical_results")),I18&lt;&gt;"",NOT(EXACT(I18,"not_applicable"))),AND(NOT(AND(D18="retain",E18="statistical_results")),J18&lt;&gt;"",NOT(EXACT(J18,"not_applicable"))),AND(NOT(AND(D18="retain",OR(E18="report_internal_inconsistency",E18="plan_material"))),K18&lt;&gt;"",NOT(EXACT(K18,"not_applicable"))),AND(NOT(AND(D18="retain",E18="protocol_report")),L18&lt;&gt;"",NOT(EXACT(L18,"not_applicable")))),"CLEAR INACTIVE VALUES",IF(OR(NOT(OR(EXACT(D18,"retain"),EXACT(D18,"exclude"),EXACT(D18,"discuss"))),NOT(OR(EXACT(E18,"statistical_results"),EXACT(E18,"report_internal_inconsistency"),EXACT(E18,"plan_material"),EXACT(E18,"protocol_report"))),AND(AND(D18="retain",E18="statistical_results"),NOT(OR(EXACT(H18,"confirmed_issue"),EXACT(H18,"probable_issue"),EXACT(H18,"not_issue"),EXACT(H18,"indeterminate")))),AND(AND(D18="retain",E18="statistical_results"),NOT(OR(EXACT(I18,"substantive"),EXACT(I18,"minor_presentation"),EXACT(I18,"indeterminate")))),AND(AND(D18="retain",E18="statistical_results"),J18&lt;&gt;"",NOT(OR(EXACT(J18,"direct"),EXACT(J18,"possible"),EXACT(J18,"unlikely"),EXACT(J18,"unknown")))),AND(AND(D18="retain",OR(E18="report_internal_inconsistency",E18="plan_material")),NOT(OR(EXACT(K18,"substantive_inconsistency"),EXACT(K18,"minor_presentation"),EXACT(K18,"non_inconsistency"),EXACT(K18,"indeterminate")))),AND(AND(D18="retain",E18="protocol_report"),L18&lt;&gt;"",NOT(OR(EXACT(L18,"substantive_difference"),EXACT(L18,"minor_presentation"),EXACT(L18,"version_timing"),EXACT(L18,"non_inconsistency"),EXACT(L18,"indeterminate"))))),"CHECK FIELDS",IF(AND(F18&lt;&gt;"",NOT(OR(EXACT(F18,"no"),EXACT(F18,"primary_done")))),"CHECK COMPLETE",IF(EXACT(F18,"primary_done"),"PRIMARY READY","PRIMARY DRAFT")))))),"CHECK INPUT / KEY")</f>
+        <v/>
+      </c>
+      <c r="H18" s="21">
+        <f>IF(AND(OR(D18="retain",D18=""),E18="statistical_results"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="I18" s="21">
+        <f>IF(AND(OR(D18="retain",D18=""),E18="statistical_results"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="J18" s="22">
+        <f>IF(AND(OR(D18="retain",D18=""),E18="statistical_results"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="K18" s="21">
+        <f>IF(AND(OR(D18="retain",D18=""),OR(E18="report_internal_inconsistency",E18="plan_material")),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="L18" s="22">
+        <f>IF(AND(OR(D18="retain",D18=""),E18="protocol_report"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="M18" s="20" t="n"/>
+      <c r="N18" s="23" t="n"/>
+      <c r="O18" s="23" t="n"/>
+      <c r="P18" s="23" t="n"/>
+      <c r="Q18" s="23" t="n"/>
+      <c r="R18" s="22" t="n"/>
+    </row>
+    <row r="19" ht="92" customFormat="1" customHeight="1" s="14">
+      <c r="A19" s="24" t="inlineStr">
+        <is>
+          <t>2019::jama.2019.17380::C018</t>
+        </is>
+      </c>
+      <c r="B19" s="24" t="inlineStr">
+        <is>
+          <t>Albuminuria forest favor labels reverse the ratio direction</t>
+        </is>
+      </c>
+      <c r="C19" s="24" t="inlineStr">
+        <is>
+          <t>joi190122supp2_prod.pdf — supplement p.18 eFigure 2; joi190122supp2_prod.pdf — p.19 eFigure 3; joi190122supp2_prod.pdf — supplement p.11 eTable 6; jama_de_boer_2019_oi_190122.pdf — main p.3 ACR progression definition; jama_de_boer_2019_oi_190122.pdf — p.4 threefold increase narrative; joi190122supp1_prod.pdf — p.11 slower-progression hypotheses; joi190122supp1_prod.pdf — p.17 ACR definition.</t>
+        </is>
+      </c>
+      <c r="D19" s="21" t="n"/>
+      <c r="E19" s="21" t="inlineStr">
+        <is>
+          <t>statistical_results</t>
+        </is>
+      </c>
+      <c r="F19" s="21" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G19" s="24">
+        <f>IFERROR(IF(LEN(TRIM(CLEAN(SUBSTITUTE(Setup!$B$2,CHAR(160)," "))))=0,"CHECK REVIEWER ID",IF(OR(A19="",COUNTIF($A$2:$A$19,A19)&lt;&gt;1,LEFT(A19,LEN("2019::jama.2019.17380::"))&lt;&gt;"2019::jama.2019.17380::"),"CHECK KEY",IF(OR(AND(NOT(AND(D19="retain",E19="statistical_results")),H19&lt;&gt;"",NOT(EXACT(H19,"not_applicable"))),AND(NOT(AND(D19="retain",E19="statistical_results")),I19&lt;&gt;"",NOT(EXACT(I19,"not_applicable"))),AND(NOT(AND(D19="retain",E19="statistical_results")),J19&lt;&gt;"",NOT(EXACT(J19,"not_applicable"))),AND(NOT(AND(D19="retain",OR(E19="report_internal_inconsistency",E19="plan_material"))),K19&lt;&gt;"",NOT(EXACT(K19,"not_applicable"))),AND(NOT(AND(D19="retain",E19="protocol_report")),L19&lt;&gt;"",NOT(EXACT(L19,"not_applicable")))),"CLEAR INACTIVE VALUES",IF(OR(NOT(OR(EXACT(D19,"retain"),EXACT(D19,"exclude"),EXACT(D19,"discuss"))),NOT(OR(EXACT(E19,"statistical_results"),EXACT(E19,"report_internal_inconsistency"),EXACT(E19,"plan_material"),EXACT(E19,"protocol_report"))),AND(AND(D19="retain",E19="statistical_results"),NOT(OR(EXACT(H19,"confirmed_issue"),EXACT(H19,"probable_issue"),EXACT(H19,"not_issue"),EXACT(H19,"indeterminate")))),AND(AND(D19="retain",E19="statistical_results"),NOT(OR(EXACT(I19,"substantive"),EXACT(I19,"minor_presentation"),EXACT(I19,"indeterminate")))),AND(AND(D19="retain",E19="statistical_results"),J19&lt;&gt;"",NOT(OR(EXACT(J19,"direct"),EXACT(J19,"possible"),EXACT(J19,"unlikely"),EXACT(J19,"unknown")))),AND(AND(D19="retain",OR(E19="report_internal_inconsistency",E19="plan_material")),NOT(OR(EXACT(K19,"substantive_inconsistency"),EXACT(K19,"minor_presentation"),EXACT(K19,"non_inconsistency"),EXACT(K19,"indeterminate")))),AND(AND(D19="retain",E19="protocol_report"),L19&lt;&gt;"",NOT(OR(EXACT(L19,"substantive_difference"),EXACT(L19,"minor_presentation"),EXACT(L19,"version_timing"),EXACT(L19,"non_inconsistency"),EXACT(L19,"indeterminate"))))),"CHECK FIELDS",IF(AND(F19&lt;&gt;"",NOT(OR(EXACT(F19,"no"),EXACT(F19,"primary_done")))),"CHECK COMPLETE",IF(EXACT(F19,"primary_done"),"PRIMARY READY","PRIMARY DRAFT")))))),"CHECK INPUT / KEY")</f>
+        <v/>
+      </c>
+      <c r="H19" s="21">
+        <f>IF(AND(OR(D19="retain",D19=""),E19="statistical_results"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="I19" s="21">
+        <f>IF(AND(OR(D19="retain",D19=""),E19="statistical_results"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="J19" s="22">
+        <f>IF(AND(OR(D19="retain",D19=""),E19="statistical_results"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="K19" s="21">
+        <f>IF(AND(OR(D19="retain",D19=""),OR(E19="report_internal_inconsistency",E19="plan_material")),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="L19" s="22">
+        <f>IF(AND(OR(D19="retain",D19=""),E19="protocol_report"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="M19" s="24" t="n"/>
+      <c r="N19" s="23" t="n"/>
+      <c r="O19" s="23" t="n"/>
+      <c r="P19" s="23" t="n"/>
+      <c r="Q19" s="23" t="n"/>
+      <c r="R19" s="22" t="n"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:R19"/>
+  <conditionalFormatting sqref="H2:H19">
+    <cfRule type="expression" priority="8" dxfId="70">
+      <formula>NOT(AND(OR($D2="retain",$D2=""),$E2="statistical_results"))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I2:I19">
+    <cfRule type="expression" priority="9" dxfId="70">
+      <formula>NOT(AND(OR($D2="retain",$D2=""),$E2="statistical_results"))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J2:J19">
+    <cfRule type="expression" priority="10" dxfId="70">
+      <formula>NOT(AND(OR($D2="retain",$D2=""),$E2="statistical_results"))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K2:K19">
+    <cfRule type="expression" priority="11" dxfId="70">
+      <formula>NOT(AND(OR($D2="retain",$D2=""),OR($E2="report_internal_inconsistency",$E2="plan_material")))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L2:L19">
+    <cfRule type="expression" priority="12" dxfId="70">
+      <formula>NOT(AND(OR($D2="retain",$D2=""),$E2="protocol_report"))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G2:G19">
+    <cfRule type="expression" priority="13" dxfId="71">
+      <formula>G2&lt;&gt;"PRIMARY READY"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="8">
+    <dataValidation sqref="D2:D19" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Use a listed option" error="Choose an option; G also checks pasted entries." type="list" errorStyle="stop">
+      <formula1>"retain,exclude,discuss"</formula1>
+    </dataValidation>
+    <dataValidation sqref="E2:E19" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Use a listed option" error="Choose an option; G also checks pasted entries." type="list" errorStyle="stop">
+      <formula1>"statistical_results,report_internal_inconsistency,plan_material,protocol_report"</formula1>
+    </dataValidation>
+    <dataValidation sqref="F2:F19" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Use a listed option" error="Choose an option; G also checks pasted entries." type="list" errorStyle="stop">
+      <formula1>"no,primary_done"</formula1>
+    </dataValidation>
+    <dataValidation sqref="H2:H19" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Use a listed option" error="Choose an option; G also checks pasted entries." type="list" errorStyle="stop">
+      <formula1>"confirmed_issue,probable_issue,not_issue,indeterminate,not_applicable"</formula1>
+    </dataValidation>
+    <dataValidation sqref="I2:I19" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Use a listed option" error="Choose an option; G also checks pasted entries." type="list" errorStyle="stop">
+      <formula1>"substantive,minor_presentation,indeterminate,not_applicable"</formula1>
+    </dataValidation>
+    <dataValidation sqref="J2:J19" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Use a listed option" error="Choose an option; G also checks pasted entries." type="list" errorStyle="stop">
+      <formula1>"direct,possible,unlikely,unknown,not_applicable"</formula1>
+    </dataValidation>
+    <dataValidation sqref="K2:K19" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Use a listed option" error="Choose an option; G also checks pasted entries." type="list" errorStyle="stop">
+      <formula1>"substantive_inconsistency,minor_presentation,non_inconsistency,indeterminate,not_applicable"</formula1>
+    </dataValidation>
+    <dataValidation sqref="L2:L19" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Use a listed option" error="Choose an option; G also checks pasted entries." type="list" errorStyle="stop">
+      <formula1>"substantive_difference,minor_presentation,version_timing,non_inconsistency,indeterminate,not_applicable"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>